--- a/data/data_prep_input/ucc_categories.xlsx
+++ b/data/data_prep_input/ucc_categories.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamrynmansfield/College/UTK/BLS_CE/data/CE_data/2024/data_prep_input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B394A4EE-21F7-FB4E-BCA6-00BF70E32053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8665BD28-2E22-9041-9B2C-D13A2B31E9F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16720" xr2:uid="{7A9D0787-2D4A-AE43-A29D-439136587B88}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{7A9D0787-2D4A-AE43-A29D-439136587B88}"/>
   </bookViews>
   <sheets>
     <sheet name="ucc_categories_current" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2571" uniqueCount="1369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2571" uniqueCount="1368">
   <si>
     <t>ucc_code</t>
   </si>
@@ -4136,9 +4136,6 @@
   </si>
   <si>
     <t>Car Fuel</t>
-  </si>
-  <si>
-    <t>Car Other</t>
   </si>
   <si>
     <t>Car Payment</t>
@@ -5044,14 +5041,14 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>6</v>
+      <c r="A2">
+        <v>520901</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>145</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>1354</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -5125,13 +5122,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>340906</v>
+        <v>530110</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>152</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>1354</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -5165,13 +5162,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>580000</v>
+        <v>200310</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>942</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>939</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -5585,13 +5582,13 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>580901</v>
+        <v>790420</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>966</v>
       </c>
       <c r="C29" t="s">
-        <v>8</v>
+        <v>939</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -5765,19 +5762,19 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>610310</v>
+        <v>200119</v>
       </c>
       <c r="B38" t="s">
-        <v>44</v>
+        <v>1336</v>
       </c>
       <c r="C38" t="s">
-        <v>8</v>
+        <v>939</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38">
         <v>1</v>
@@ -5785,19 +5782,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>610320</v>
+        <v>200219</v>
       </c>
       <c r="B39" t="s">
-        <v>45</v>
+        <v>1337</v>
       </c>
       <c r="C39" t="s">
-        <v>8</v>
+        <v>939</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39">
         <v>1</v>
@@ -5805,13 +5802,13 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>620112</v>
+        <v>270000</v>
       </c>
       <c r="B40" t="s">
-        <v>46</v>
+        <v>967</v>
       </c>
       <c r="C40" t="s">
-        <v>8</v>
+        <v>968</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -5865,13 +5862,13 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>670320</v>
+        <v>270310</v>
       </c>
       <c r="B43" t="s">
-        <v>49</v>
+        <v>973</v>
       </c>
       <c r="C43" t="s">
-        <v>8</v>
+        <v>968</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -5945,13 +5942,13 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>450110</v>
+        <v>270311</v>
       </c>
       <c r="B47" t="s">
-        <v>53</v>
+        <v>974</v>
       </c>
       <c r="C47" t="s">
-        <v>1363</v>
+        <v>968</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -5985,13 +5982,13 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49">
-        <v>450210</v>
+        <v>310140</v>
       </c>
       <c r="B49" t="s">
-        <v>55</v>
+        <v>978</v>
       </c>
       <c r="C49" t="s">
-        <v>1363</v>
+        <v>968</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -6165,13 +6162,13 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58">
-        <v>450350</v>
+        <v>310210</v>
       </c>
       <c r="B58" t="s">
-        <v>64</v>
+        <v>979</v>
       </c>
       <c r="C58" t="s">
-        <v>1367</v>
+        <v>968</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -6365,13 +6362,13 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68">
-        <v>460110</v>
+        <v>310220</v>
       </c>
       <c r="B68" t="s">
-        <v>74</v>
+        <v>980</v>
       </c>
       <c r="C68" t="s">
-        <v>1363</v>
+        <v>968</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -6405,13 +6402,13 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70">
-        <v>460901</v>
+        <v>310230</v>
       </c>
       <c r="B70" t="s">
-        <v>76</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>1363</v>
+        <v>981</v>
+      </c>
+      <c r="C70" t="s">
+        <v>968</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -6425,13 +6422,13 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71">
-        <v>460902</v>
+        <v>310231</v>
       </c>
       <c r="B71" t="s">
-        <v>77</v>
+        <v>982</v>
       </c>
       <c r="C71" t="s">
-        <v>1361</v>
+        <v>968</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -6485,13 +6482,13 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74">
-        <v>470111</v>
+        <v>310232</v>
       </c>
       <c r="B74" t="s">
-        <v>80</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>1365</v>
+        <v>983</v>
+      </c>
+      <c r="C74" t="s">
+        <v>968</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -6505,13 +6502,13 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75">
-        <v>470112</v>
+        <v>310241</v>
       </c>
       <c r="B75" t="s">
-        <v>82</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>1365</v>
+        <v>985</v>
+      </c>
+      <c r="C75" t="s">
+        <v>968</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -6545,13 +6542,13 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77">
-        <v>470114</v>
+        <v>310242</v>
       </c>
       <c r="B77" t="s">
-        <v>84</v>
+        <v>986</v>
       </c>
       <c r="C77" t="s">
-        <v>1365</v>
+        <v>968</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -6645,13 +6642,13 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82">
-        <v>480100</v>
+        <v>310314</v>
       </c>
       <c r="B82" t="s">
-        <v>89</v>
+        <v>991</v>
       </c>
       <c r="C82" t="s">
-        <v>1364</v>
+        <v>968</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -6665,13 +6662,13 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83">
-        <v>480110</v>
+        <v>310315</v>
       </c>
       <c r="B83" t="s">
-        <v>90</v>
+        <v>992</v>
       </c>
       <c r="C83" t="s">
-        <v>1364</v>
+        <v>968</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -6805,13 +6802,13 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90">
-        <v>490000</v>
+        <v>310316</v>
       </c>
       <c r="B90" t="s">
-        <v>97</v>
+        <v>993</v>
       </c>
       <c r="C90" t="s">
-        <v>1364</v>
+        <v>968</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -7065,13 +7062,13 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103">
-        <v>490315</v>
+        <v>310331</v>
       </c>
       <c r="B103" t="s">
-        <v>110</v>
+        <v>996</v>
       </c>
       <c r="C103" t="s">
-        <v>1364</v>
+        <v>968</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -7305,13 +7302,13 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115">
-        <v>500110</v>
+        <v>310332</v>
       </c>
       <c r="B115" t="s">
-        <v>122</v>
+        <v>997</v>
       </c>
       <c r="C115" t="s">
-        <v>1366</v>
+        <v>968</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -7345,13 +7342,13 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117">
-        <v>510115</v>
+        <v>310334</v>
       </c>
       <c r="B117" t="s">
-        <v>124</v>
+        <v>999</v>
       </c>
       <c r="C117" t="s">
-        <v>1366</v>
+        <v>968</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -7465,13 +7462,13 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123">
-        <v>520310</v>
+        <v>310335</v>
       </c>
       <c r="B123" t="s">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="C123" t="s">
-        <v>1366</v>
+        <v>968</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -7485,13 +7482,13 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124">
-        <v>520410</v>
+        <v>310340</v>
       </c>
       <c r="B124" t="s">
-        <v>131</v>
+        <v>1001</v>
       </c>
       <c r="C124" t="s">
-        <v>1366</v>
+        <v>968</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -7545,13 +7542,13 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127">
-        <v>520516</v>
+        <v>310351</v>
       </c>
       <c r="B127" t="s">
-        <v>134</v>
+        <v>1005</v>
       </c>
       <c r="C127" t="s">
-        <v>1366</v>
+        <v>968</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -7645,13 +7642,13 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132">
-        <v>520531</v>
+        <v>310352</v>
       </c>
       <c r="B132" t="s">
-        <v>139</v>
+        <v>1006</v>
       </c>
       <c r="C132" t="s">
-        <v>1366</v>
+        <v>968</v>
       </c>
       <c r="D132">
         <v>1</v>
@@ -7685,13 +7682,13 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134">
-        <v>520541</v>
+        <v>310400</v>
       </c>
       <c r="B134" t="s">
-        <v>141</v>
+        <v>1007</v>
       </c>
       <c r="C134" t="s">
-        <v>1366</v>
+        <v>968</v>
       </c>
       <c r="D134">
         <v>1</v>
@@ -7725,13 +7722,13 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136">
-        <v>520550</v>
+        <v>310900</v>
       </c>
       <c r="B136" t="s">
-        <v>143</v>
+        <v>1008</v>
       </c>
       <c r="C136" t="s">
-        <v>1366</v>
+        <v>968</v>
       </c>
       <c r="D136">
         <v>1</v>
@@ -7765,13 +7762,13 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138">
-        <v>520901</v>
+        <v>340610</v>
       </c>
       <c r="B138" t="s">
-        <v>145</v>
+        <v>1010</v>
       </c>
       <c r="C138" t="s">
-        <v>1354</v>
+        <v>968</v>
       </c>
       <c r="D138">
         <v>1</v>
@@ -7785,13 +7782,13 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A139">
-        <v>520902</v>
+        <v>340909</v>
       </c>
       <c r="B139" t="s">
-        <v>146</v>
+        <v>1013</v>
       </c>
       <c r="C139" t="s">
-        <v>1361</v>
+        <v>968</v>
       </c>
       <c r="D139">
         <v>1</v>
@@ -7825,13 +7822,13 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A141">
-        <v>520904</v>
+        <v>590110</v>
       </c>
       <c r="B141" t="s">
-        <v>148</v>
+        <v>1014</v>
       </c>
       <c r="C141" t="s">
-        <v>1122</v>
+        <v>968</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -7905,13 +7902,13 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A145">
-        <v>530110</v>
+        <v>590210</v>
       </c>
       <c r="B145" t="s">
-        <v>152</v>
+        <v>1017</v>
       </c>
       <c r="C145" t="s">
-        <v>1354</v>
+        <v>968</v>
       </c>
       <c r="D145">
         <v>1</v>
@@ -7945,13 +7942,13 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A147">
-        <v>530412</v>
+        <v>590220</v>
       </c>
       <c r="B147" t="s">
-        <v>154</v>
+        <v>1020</v>
       </c>
       <c r="C147" t="s">
-        <v>1356</v>
+        <v>968</v>
       </c>
       <c r="D147">
         <v>1</v>
@@ -7965,13 +7962,13 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A148">
-        <v>530901</v>
+        <v>590230</v>
       </c>
       <c r="B148" t="s">
-        <v>155</v>
+        <v>1021</v>
       </c>
       <c r="C148" t="s">
-        <v>1368</v>
+        <v>968</v>
       </c>
       <c r="D148">
         <v>1</v>
@@ -7985,13 +7982,13 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A149">
-        <v>530902</v>
+        <v>620930</v>
       </c>
       <c r="B149" t="s">
-        <v>156</v>
+        <v>1025</v>
       </c>
       <c r="C149" t="s">
-        <v>1357</v>
+        <v>968</v>
       </c>
       <c r="D149">
         <v>1</v>
@@ -8005,13 +8002,13 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A150">
-        <v>530903</v>
+        <v>680904</v>
       </c>
       <c r="B150" t="s">
-        <v>157</v>
+        <v>1026</v>
       </c>
       <c r="C150" t="s">
-        <v>1366</v>
+        <v>968</v>
       </c>
       <c r="D150">
         <v>1</v>
@@ -8025,13 +8022,13 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A151">
-        <v>600310</v>
+        <v>690111</v>
       </c>
       <c r="B151" t="s">
-        <v>158</v>
+        <v>1028</v>
       </c>
       <c r="C151" t="s">
-        <v>1359</v>
+        <v>968</v>
       </c>
       <c r="D151">
         <v>1</v>
@@ -8065,13 +8062,13 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A153">
-        <v>620114</v>
+        <v>690114</v>
       </c>
       <c r="B153" t="s">
-        <v>160</v>
+        <v>1031</v>
       </c>
       <c r="C153" t="s">
-        <v>1364</v>
+        <v>968</v>
       </c>
       <c r="D153">
         <v>1</v>
@@ -8725,13 +8722,13 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A186">
-        <v>530210</v>
+        <v>690116</v>
       </c>
       <c r="B186" t="s">
-        <v>195</v>
+        <v>1033</v>
       </c>
       <c r="C186" t="s">
-        <v>1357</v>
+        <v>968</v>
       </c>
       <c r="D186">
         <v>1</v>
@@ -8745,13 +8742,13 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A187">
-        <v>530311</v>
+        <v>690117</v>
       </c>
       <c r="B187" t="s">
-        <v>196</v>
+        <v>1034</v>
       </c>
       <c r="C187" t="s">
-        <v>1358</v>
+        <v>968</v>
       </c>
       <c r="D187">
         <v>1</v>
@@ -8785,13 +8782,13 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A189">
-        <v>530510</v>
+        <v>690118</v>
       </c>
       <c r="B189" t="s">
-        <v>198</v>
+        <v>1035</v>
       </c>
       <c r="C189" t="s">
-        <v>1358</v>
+        <v>968</v>
       </c>
       <c r="D189">
         <v>1</v>
@@ -8805,13 +8802,13 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A190">
-        <v>190400</v>
+        <v>690119</v>
       </c>
       <c r="B190" t="s">
-        <v>199</v>
+        <v>1036</v>
       </c>
       <c r="C190" t="s">
-        <v>200</v>
+        <v>968</v>
       </c>
       <c r="D190">
         <v>1</v>
@@ -8825,13 +8822,13 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A191">
-        <v>190500</v>
+        <v>690120</v>
       </c>
       <c r="B191" t="s">
-        <v>201</v>
+        <v>1037</v>
       </c>
       <c r="C191" t="s">
-        <v>200</v>
+        <v>968</v>
       </c>
       <c r="D191">
         <v>1</v>
@@ -8845,13 +8842,13 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A192">
-        <v>190600</v>
+        <v>600310</v>
       </c>
       <c r="B192" t="s">
-        <v>202</v>
+        <v>158</v>
       </c>
       <c r="C192" t="s">
-        <v>200</v>
+        <v>1359</v>
       </c>
       <c r="D192">
         <v>1</v>
@@ -8865,19 +8862,19 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A193">
-        <v>190700</v>
+        <v>600315</v>
       </c>
       <c r="B193" t="s">
-        <v>203</v>
+        <v>1350</v>
       </c>
       <c r="C193" t="s">
-        <v>200</v>
+        <v>1359</v>
       </c>
       <c r="D193">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F193">
         <v>1</v>
@@ -8905,19 +8902,19 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A195">
-        <v>190902</v>
+        <v>600311</v>
       </c>
       <c r="B195" t="s">
-        <v>205</v>
+        <v>1351</v>
       </c>
       <c r="C195" t="s">
-        <v>200</v>
+        <v>1359</v>
       </c>
       <c r="D195">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F195">
         <v>1</v>
@@ -8944,14 +8941,14 @@
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A197" s="1" t="s">
-        <v>208</v>
+      <c r="A197">
+        <v>530902</v>
       </c>
       <c r="B197" t="s">
-        <v>209</v>
+        <v>156</v>
       </c>
       <c r="C197" t="s">
-        <v>200</v>
+        <v>1357</v>
       </c>
       <c r="D197">
         <v>1</v>
@@ -8984,14 +8981,14 @@
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A199" s="1" t="s">
-        <v>212</v>
+      <c r="A199">
+        <v>530210</v>
       </c>
       <c r="B199" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="C199" t="s">
-        <v>200</v>
+        <v>1357</v>
       </c>
       <c r="D199">
         <v>1</v>
@@ -9004,14 +9001,14 @@
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A200" s="1" t="s">
-        <v>214</v>
+      <c r="A200">
+        <v>470111</v>
       </c>
       <c r="B200" t="s">
-        <v>215</v>
-      </c>
-      <c r="C200" t="s">
-        <v>200</v>
+        <v>80</v>
+      </c>
+      <c r="C200" s="3" t="s">
+        <v>1365</v>
       </c>
       <c r="D200">
         <v>1</v>
@@ -9024,14 +9021,14 @@
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A201" s="1" t="s">
-        <v>216</v>
+      <c r="A201">
+        <v>470112</v>
       </c>
       <c r="B201" t="s">
-        <v>217</v>
-      </c>
-      <c r="C201" t="s">
-        <v>200</v>
+        <v>82</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>1365</v>
       </c>
       <c r="D201">
         <v>1</v>
@@ -9084,14 +9081,14 @@
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A204" s="1" t="s">
-        <v>222</v>
+      <c r="A204">
+        <v>470114</v>
       </c>
       <c r="B204" t="s">
-        <v>223</v>
+        <v>84</v>
       </c>
       <c r="C204" t="s">
-        <v>200</v>
+        <v>1365</v>
       </c>
       <c r="D204">
         <v>1</v>
@@ -9104,14 +9101,14 @@
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A205" s="1" t="s">
-        <v>224</v>
+      <c r="A205">
+        <v>480100</v>
       </c>
       <c r="B205" t="s">
-        <v>225</v>
+        <v>89</v>
       </c>
       <c r="C205" t="s">
-        <v>200</v>
+        <v>1364</v>
       </c>
       <c r="D205">
         <v>1</v>
@@ -9124,14 +9121,14 @@
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A206" s="1" t="s">
-        <v>226</v>
+      <c r="A206">
+        <v>480110</v>
       </c>
       <c r="B206" t="s">
-        <v>227</v>
+        <v>90</v>
       </c>
       <c r="C206" t="s">
-        <v>200</v>
+        <v>1364</v>
       </c>
       <c r="D206">
         <v>1</v>
@@ -9144,14 +9141,14 @@
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A207" s="1" t="s">
-        <v>228</v>
+      <c r="A207">
+        <v>490000</v>
       </c>
       <c r="B207" t="s">
-        <v>229</v>
+        <v>97</v>
       </c>
       <c r="C207" t="s">
-        <v>200</v>
+        <v>1364</v>
       </c>
       <c r="D207">
         <v>1</v>
@@ -9164,14 +9161,14 @@
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A208" s="1" t="s">
-        <v>230</v>
+      <c r="A208">
+        <v>490315</v>
       </c>
       <c r="B208" t="s">
-        <v>231</v>
+        <v>110</v>
       </c>
       <c r="C208" t="s">
-        <v>200</v>
+        <v>1364</v>
       </c>
       <c r="D208">
         <v>1</v>
@@ -9184,14 +9181,14 @@
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A209" s="1" t="s">
-        <v>232</v>
+      <c r="A209">
+        <v>620114</v>
       </c>
       <c r="B209" t="s">
-        <v>233</v>
+        <v>160</v>
       </c>
       <c r="C209" t="s">
-        <v>200</v>
+        <v>1364</v>
       </c>
       <c r="D209">
         <v>1</v>
@@ -9204,34 +9201,34 @@
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A210" s="1" t="s">
-        <v>234</v>
+      <c r="A210">
+        <v>490100</v>
       </c>
       <c r="B210" t="s">
-        <v>235</v>
+        <v>1348</v>
       </c>
       <c r="C210" t="s">
-        <v>200</v>
+        <v>1364</v>
       </c>
       <c r="D210">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E210">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F210">
         <v>1</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A211" s="1" t="s">
-        <v>236</v>
+      <c r="A211">
+        <v>500110</v>
       </c>
       <c r="B211" t="s">
-        <v>237</v>
+        <v>122</v>
       </c>
       <c r="C211" t="s">
-        <v>200</v>
+        <v>1364</v>
       </c>
       <c r="D211">
         <v>1</v>
@@ -9244,14 +9241,14 @@
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A212" s="1" t="s">
-        <v>238</v>
+      <c r="A212">
+        <v>510115</v>
       </c>
       <c r="B212" t="s">
-        <v>239</v>
+        <v>124</v>
       </c>
       <c r="C212" t="s">
-        <v>200</v>
+        <v>1364</v>
       </c>
       <c r="D212">
         <v>1</v>
@@ -9284,14 +9281,14 @@
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A214" s="1" t="s">
-        <v>242</v>
+      <c r="A214">
+        <v>520310</v>
       </c>
       <c r="B214" t="s">
-        <v>243</v>
+        <v>130</v>
       </c>
       <c r="C214" t="s">
-        <v>200</v>
+        <v>1364</v>
       </c>
       <c r="D214">
         <v>1</v>
@@ -9364,14 +9361,14 @@
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A218" s="1" t="s">
-        <v>250</v>
+      <c r="A218">
+        <v>520410</v>
       </c>
       <c r="B218" t="s">
-        <v>251</v>
+        <v>131</v>
       </c>
       <c r="C218" t="s">
-        <v>200</v>
+        <v>1364</v>
       </c>
       <c r="D218">
         <v>1</v>
@@ -9424,14 +9421,14 @@
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A221" s="1" t="s">
-        <v>256</v>
+      <c r="A221">
+        <v>520516</v>
       </c>
       <c r="B221" t="s">
-        <v>257</v>
+        <v>134</v>
       </c>
       <c r="C221" t="s">
-        <v>200</v>
+        <v>1363</v>
       </c>
       <c r="D221">
         <v>1</v>
@@ -9464,14 +9461,14 @@
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A223" s="1" t="s">
-        <v>260</v>
+      <c r="A223">
+        <v>520531</v>
       </c>
       <c r="B223" t="s">
-        <v>261</v>
+        <v>139</v>
       </c>
       <c r="C223" t="s">
-        <v>200</v>
+        <v>1365</v>
       </c>
       <c r="D223">
         <v>1</v>
@@ -9484,14 +9481,14 @@
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A224" s="1" t="s">
-        <v>262</v>
+      <c r="A224">
+        <v>520541</v>
       </c>
       <c r="B224" t="s">
-        <v>263</v>
+        <v>141</v>
       </c>
       <c r="C224" t="s">
-        <v>200</v>
+        <v>1365</v>
       </c>
       <c r="D224">
         <v>1</v>
@@ -9524,14 +9521,14 @@
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A226" s="1" t="s">
-        <v>266</v>
+      <c r="A226">
+        <v>520550</v>
       </c>
       <c r="B226" t="s">
-        <v>267</v>
+        <v>143</v>
       </c>
       <c r="C226" t="s">
-        <v>200</v>
+        <v>1365</v>
       </c>
       <c r="D226">
         <v>1</v>
@@ -9544,14 +9541,14 @@
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A227" s="1" t="s">
-        <v>268</v>
+      <c r="A227">
+        <v>530903</v>
       </c>
       <c r="B227" t="s">
-        <v>269</v>
+        <v>157</v>
       </c>
       <c r="C227" t="s">
-        <v>200</v>
+        <v>1363</v>
       </c>
       <c r="D227">
         <v>1</v>
@@ -9604,14 +9601,14 @@
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A230" s="1" t="s">
-        <v>274</v>
+      <c r="A230">
+        <v>450350</v>
       </c>
       <c r="B230" t="s">
-        <v>275</v>
+        <v>64</v>
       </c>
       <c r="C230" t="s">
-        <v>200</v>
+        <v>1366</v>
       </c>
       <c r="D230">
         <v>1</v>
@@ -9724,14 +9721,14 @@
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A236" s="1" t="s">
-        <v>286</v>
+      <c r="A236">
+        <v>450110</v>
       </c>
       <c r="B236" t="s">
-        <v>287</v>
+        <v>53</v>
       </c>
       <c r="C236" t="s">
-        <v>200</v>
+        <v>1363</v>
       </c>
       <c r="D236">
         <v>1</v>
@@ -9764,14 +9761,14 @@
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A238" s="1" t="s">
-        <v>290</v>
+      <c r="A238">
+        <v>450210</v>
       </c>
       <c r="B238" t="s">
-        <v>291</v>
+        <v>55</v>
       </c>
       <c r="C238" t="s">
-        <v>200</v>
+        <v>1363</v>
       </c>
       <c r="D238">
         <v>1</v>
@@ -9804,14 +9801,14 @@
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A240" s="1" t="s">
-        <v>294</v>
+      <c r="A240">
+        <v>460110</v>
       </c>
       <c r="B240" t="s">
-        <v>295</v>
+        <v>74</v>
       </c>
       <c r="C240" t="s">
-        <v>200</v>
+        <v>1363</v>
       </c>
       <c r="D240">
         <v>1</v>
@@ -9864,14 +9861,14 @@
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A243" s="1" t="s">
-        <v>300</v>
+      <c r="A243">
+        <v>460901</v>
       </c>
       <c r="B243" t="s">
-        <v>301</v>
-      </c>
-      <c r="C243" t="s">
-        <v>200</v>
+        <v>76</v>
+      </c>
+      <c r="C243" s="3" t="s">
+        <v>1363</v>
       </c>
       <c r="D243">
         <v>1</v>
@@ -9904,14 +9901,14 @@
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A245" s="1" t="s">
-        <v>304</v>
+      <c r="A245">
+        <v>360110</v>
       </c>
       <c r="B245" t="s">
-        <v>305</v>
+        <v>747</v>
       </c>
       <c r="C245" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D245">
         <v>1</v>
@@ -9924,14 +9921,14 @@
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A246" s="1" t="s">
-        <v>306</v>
+      <c r="A246">
+        <v>360120</v>
       </c>
       <c r="B246" t="s">
-        <v>307</v>
+        <v>749</v>
       </c>
       <c r="C246" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D246">
         <v>1</v>
@@ -9985,13 +9982,13 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A249">
-        <v>100119</v>
+        <v>360210</v>
       </c>
       <c r="B249" t="s">
-        <v>311</v>
+        <v>750</v>
       </c>
       <c r="C249" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D249">
         <v>1</v>
@@ -10005,13 +10002,13 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A250">
-        <v>100210</v>
+        <v>360330</v>
       </c>
       <c r="B250" t="s">
-        <v>312</v>
+        <v>754</v>
       </c>
       <c r="C250" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D250">
         <v>1</v>
@@ -10025,13 +10022,13 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A251">
-        <v>100410</v>
+        <v>360420</v>
       </c>
       <c r="B251" t="s">
-        <v>313</v>
+        <v>758</v>
       </c>
       <c r="C251" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D251">
         <v>1</v>
@@ -10065,13 +10062,13 @@
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A253">
-        <v>110110</v>
+        <v>360513</v>
       </c>
       <c r="B253" t="s">
-        <v>315</v>
+        <v>761</v>
       </c>
       <c r="C253" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D253">
         <v>1</v>
@@ -10085,13 +10082,13 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A254">
-        <v>110210</v>
+        <v>360901</v>
       </c>
       <c r="B254" t="s">
-        <v>316</v>
+        <v>762</v>
       </c>
       <c r="C254" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D254">
         <v>1</v>
@@ -10125,13 +10122,13 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A256">
-        <v>110319</v>
+        <v>360902</v>
       </c>
       <c r="B256" t="s">
-        <v>318</v>
+        <v>763</v>
       </c>
       <c r="C256" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D256">
         <v>1</v>
@@ -10145,13 +10142,13 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A257">
-        <v>110410</v>
+        <v>370110</v>
       </c>
       <c r="B257" t="s">
-        <v>319</v>
+        <v>764</v>
       </c>
       <c r="C257" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D257">
         <v>1</v>
@@ -10185,13 +10182,13 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A259">
-        <v>120110</v>
+        <v>370125</v>
       </c>
       <c r="B259" t="s">
-        <v>321</v>
+        <v>766</v>
       </c>
       <c r="C259" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D259">
         <v>1</v>
@@ -10205,13 +10202,13 @@
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A260">
-        <v>120210</v>
+        <v>370220</v>
       </c>
       <c r="B260" t="s">
-        <v>322</v>
+        <v>771</v>
       </c>
       <c r="C260" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D260">
         <v>1</v>
@@ -10225,13 +10222,13 @@
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A261">
-        <v>120310</v>
+        <v>370902</v>
       </c>
       <c r="B261" t="s">
-        <v>323</v>
+        <v>777</v>
       </c>
       <c r="C261" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D261">
         <v>1</v>
@@ -10245,13 +10242,13 @@
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A262">
-        <v>120410</v>
+        <v>370903</v>
       </c>
       <c r="B262" t="s">
-        <v>324</v>
+        <v>778</v>
       </c>
       <c r="C262" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D262">
         <v>1</v>
@@ -10285,13 +10282,13 @@
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A264">
-        <v>130119</v>
+        <v>380110</v>
       </c>
       <c r="B264" t="s">
-        <v>326</v>
+        <v>780</v>
       </c>
       <c r="C264" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D264">
         <v>1</v>
@@ -10365,13 +10362,13 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A268">
-        <v>130129</v>
+        <v>380210</v>
       </c>
       <c r="B268" t="s">
-        <v>330</v>
+        <v>782</v>
       </c>
       <c r="C268" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D268">
         <v>1</v>
@@ -10625,13 +10622,13 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A281">
-        <v>150110</v>
+        <v>380430</v>
       </c>
       <c r="B281" t="s">
-        <v>343</v>
+        <v>794</v>
       </c>
       <c r="C281" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D281">
         <v>1</v>
@@ -10685,13 +10682,13 @@
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A284">
-        <v>150219</v>
+        <v>380510</v>
       </c>
       <c r="B284" t="s">
-        <v>346</v>
+        <v>795</v>
       </c>
       <c r="C284" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D284">
         <v>1</v>
@@ -10705,13 +10702,13 @@
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A285">
-        <v>150310</v>
+        <v>380901</v>
       </c>
       <c r="B285" t="s">
-        <v>347</v>
+        <v>796</v>
       </c>
       <c r="C285" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D285">
         <v>1</v>
@@ -10765,13 +10762,13 @@
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A288">
-        <v>160211</v>
+        <v>390110</v>
       </c>
       <c r="B288" t="s">
-        <v>350</v>
+        <v>799</v>
       </c>
       <c r="C288" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D288">
         <v>1</v>
@@ -10785,13 +10782,13 @@
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A289">
-        <v>160212</v>
+        <v>390120</v>
       </c>
       <c r="B289" t="s">
-        <v>351</v>
+        <v>800</v>
       </c>
       <c r="C289" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D289">
         <v>1</v>
@@ -10825,13 +10822,13 @@
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A291">
-        <v>160320</v>
+        <v>390210</v>
       </c>
       <c r="B291" t="s">
-        <v>353</v>
+        <v>801</v>
       </c>
       <c r="C291" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D291">
         <v>1</v>
@@ -10845,13 +10842,13 @@
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A292">
-        <v>170110</v>
+        <v>390223</v>
       </c>
       <c r="B292" t="s">
-        <v>354</v>
+        <v>804</v>
       </c>
       <c r="C292" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D292">
         <v>1</v>
@@ -10865,13 +10862,13 @@
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A293">
-        <v>170210</v>
+        <v>390322</v>
       </c>
       <c r="B293" t="s">
-        <v>355</v>
+        <v>808</v>
       </c>
       <c r="C293" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D293">
         <v>1</v>
@@ -10945,13 +10942,13 @@
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A297">
-        <v>170520</v>
+        <v>390901</v>
       </c>
       <c r="B297" t="s">
-        <v>359</v>
+        <v>809</v>
       </c>
       <c r="C297" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D297">
         <v>1</v>
@@ -10985,13 +10982,13 @@
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A299">
-        <v>170531</v>
+        <v>390902</v>
       </c>
       <c r="B299" t="s">
-        <v>361</v>
+        <v>810</v>
       </c>
       <c r="C299" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D299">
         <v>1</v>
@@ -11045,13 +11042,13 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A302">
-        <v>170539</v>
+        <v>400110</v>
       </c>
       <c r="B302" t="s">
-        <v>364</v>
+        <v>811</v>
       </c>
       <c r="C302" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D302">
         <v>1</v>
@@ -11065,13 +11062,13 @@
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A303">
-        <v>180110</v>
+        <v>400210</v>
       </c>
       <c r="B303" t="s">
-        <v>365</v>
+        <v>812</v>
       </c>
       <c r="C303" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D303">
         <v>1</v>
@@ -11085,13 +11082,13 @@
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A304">
-        <v>180210</v>
+        <v>400220</v>
       </c>
       <c r="B304" t="s">
-        <v>366</v>
+        <v>813</v>
       </c>
       <c r="C304" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D304">
         <v>1</v>
@@ -11105,13 +11102,13 @@
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A305">
-        <v>180220</v>
+        <v>400310</v>
       </c>
       <c r="B305" t="s">
-        <v>367</v>
+        <v>814</v>
       </c>
       <c r="C305" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D305">
         <v>1</v>
@@ -11125,13 +11122,13 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A306">
-        <v>180310</v>
+        <v>410110</v>
       </c>
       <c r="B306" t="s">
-        <v>368</v>
+        <v>815</v>
       </c>
       <c r="C306" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D306">
         <v>1</v>
@@ -11145,13 +11142,13 @@
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A307">
-        <v>180320</v>
+        <v>410130</v>
       </c>
       <c r="B307" t="s">
-        <v>369</v>
+        <v>821</v>
       </c>
       <c r="C307" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D307">
         <v>1</v>
@@ -11165,13 +11162,13 @@
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A308">
-        <v>180410</v>
+        <v>430110</v>
       </c>
       <c r="B308" t="s">
-        <v>370</v>
+        <v>832</v>
       </c>
       <c r="C308" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D308">
         <v>1</v>
@@ -11185,13 +11182,13 @@
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A309">
-        <v>180420</v>
+        <v>430120</v>
       </c>
       <c r="B309" t="s">
-        <v>371</v>
+        <v>833</v>
       </c>
       <c r="C309" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D309">
         <v>1</v>
@@ -11205,13 +11202,13 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A310">
-        <v>180510</v>
+        <v>440110</v>
       </c>
       <c r="B310" t="s">
-        <v>372</v>
+        <v>834</v>
       </c>
       <c r="C310" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D310">
         <v>1</v>
@@ -11225,13 +11222,13 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A311">
-        <v>180520</v>
+        <v>440120</v>
       </c>
       <c r="B311" t="s">
-        <v>373</v>
+        <v>835</v>
       </c>
       <c r="C311" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D311">
         <v>1</v>
@@ -11265,13 +11262,13 @@
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A313">
-        <v>180611</v>
+        <v>440130</v>
       </c>
       <c r="B313" t="s">
-        <v>375</v>
+        <v>836</v>
       </c>
       <c r="C313" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D313">
         <v>1</v>
@@ -11285,13 +11282,13 @@
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A314">
-        <v>180612</v>
+        <v>440140</v>
       </c>
       <c r="B314" t="s">
-        <v>376</v>
+        <v>837</v>
       </c>
       <c r="C314" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D314">
         <v>1</v>
@@ -11305,13 +11302,13 @@
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A315">
-        <v>180620</v>
+        <v>440150</v>
       </c>
       <c r="B315" t="s">
-        <v>377</v>
+        <v>838</v>
       </c>
       <c r="C315" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D315">
         <v>1</v>
@@ -11325,13 +11322,13 @@
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A316">
-        <v>180710</v>
+        <v>440210</v>
       </c>
       <c r="B316" t="s">
-        <v>378</v>
+        <v>839</v>
       </c>
       <c r="C316" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D316">
         <v>1</v>
@@ -11965,13 +11962,13 @@
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A348">
-        <v>190905</v>
+        <v>440900</v>
       </c>
       <c r="B348" t="s">
-        <v>410</v>
+        <v>840</v>
       </c>
       <c r="C348" t="s">
-        <v>200</v>
+        <v>748</v>
       </c>
       <c r="D348">
         <v>1</v>
@@ -12384,40 +12381,40 @@
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A369" s="1" t="s">
-        <v>431</v>
+      <c r="A369">
+        <v>360319</v>
       </c>
       <c r="B369" t="s">
-        <v>432</v>
+        <v>1339</v>
       </c>
       <c r="C369" t="s">
-        <v>433</v>
+        <v>748</v>
       </c>
       <c r="D369">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E369">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F369">
         <v>1</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A370" s="1" t="s">
-        <v>434</v>
+      <c r="A370">
+        <v>370219</v>
       </c>
       <c r="B370" t="s">
-        <v>435</v>
+        <v>1340</v>
       </c>
       <c r="C370" t="s">
-        <v>433</v>
+        <v>748</v>
       </c>
       <c r="D370">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E370">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F370">
         <v>1</v>
@@ -12425,19 +12422,19 @@
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A371">
-        <v>210110</v>
+        <v>370319</v>
       </c>
       <c r="B371" t="s">
-        <v>436</v>
+        <v>1341</v>
       </c>
       <c r="C371" t="s">
-        <v>433</v>
+        <v>748</v>
       </c>
       <c r="D371">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E371">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F371">
         <v>1</v>
@@ -12485,19 +12482,19 @@
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A374">
-        <v>220000</v>
+        <v>380319</v>
       </c>
       <c r="B374" t="s">
-        <v>439</v>
+        <v>1342</v>
       </c>
       <c r="C374" t="s">
-        <v>433</v>
+        <v>748</v>
       </c>
       <c r="D374">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E374">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F374">
         <v>1</v>
@@ -12505,19 +12502,19 @@
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A375">
-        <v>220110</v>
+        <v>380339</v>
       </c>
       <c r="B375" t="s">
-        <v>440</v>
+        <v>1343</v>
       </c>
       <c r="C375" t="s">
-        <v>433</v>
+        <v>748</v>
       </c>
       <c r="D375">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E375">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F375">
         <v>1</v>
@@ -12545,19 +12542,19 @@
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A377">
-        <v>220120</v>
+        <v>380429</v>
       </c>
       <c r="B377" t="s">
-        <v>442</v>
+        <v>1344</v>
       </c>
       <c r="C377" t="s">
-        <v>433</v>
+        <v>748</v>
       </c>
       <c r="D377">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E377">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F377">
         <v>1</v>
@@ -12565,19 +12562,19 @@
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A378">
-        <v>220210</v>
+        <v>380909</v>
       </c>
       <c r="B378" t="s">
-        <v>443</v>
+        <v>1345</v>
       </c>
       <c r="C378" t="s">
-        <v>433</v>
+        <v>748</v>
       </c>
       <c r="D378">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E378">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F378">
         <v>1</v>
@@ -12725,19 +12722,19 @@
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A386">
-        <v>220610</v>
+        <v>390319</v>
       </c>
       <c r="B386" t="s">
-        <v>451</v>
+        <v>1346</v>
       </c>
       <c r="C386" t="s">
-        <v>433</v>
+        <v>748</v>
       </c>
       <c r="D386">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E386">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F386">
         <v>1</v>
@@ -12865,19 +12862,19 @@
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A393">
-        <v>230000</v>
+        <v>410119</v>
       </c>
       <c r="B393" t="s">
-        <v>458</v>
+        <v>1347</v>
       </c>
       <c r="C393" t="s">
-        <v>433</v>
+        <v>748</v>
       </c>
       <c r="D393">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E393">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F393">
         <v>1</v>
@@ -12885,13 +12882,13 @@
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A394">
-        <v>230110</v>
+        <v>670410</v>
       </c>
       <c r="B394" t="s">
-        <v>459</v>
+        <v>1100</v>
       </c>
       <c r="C394" t="s">
-        <v>433</v>
+        <v>1101</v>
       </c>
       <c r="D394">
         <v>1</v>
@@ -13225,13 +13222,13 @@
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A411">
-        <v>230140</v>
+        <v>670903</v>
       </c>
       <c r="B411" t="s">
-        <v>476</v>
+        <v>1104</v>
       </c>
       <c r="C411" t="s">
-        <v>433</v>
+        <v>1101</v>
       </c>
       <c r="D411">
         <v>1</v>
@@ -13324,14 +13321,14 @@
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A416">
-        <v>230900</v>
+      <c r="A416" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B416" t="s">
-        <v>481</v>
+        <v>7</v>
       </c>
       <c r="C416" t="s">
-        <v>433</v>
+        <v>8</v>
       </c>
       <c r="D416">
         <v>1</v>
@@ -13385,13 +13382,13 @@
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A419">
-        <v>240110</v>
+        <v>340906</v>
       </c>
       <c r="B419" t="s">
-        <v>484</v>
+        <v>12</v>
       </c>
       <c r="C419" t="s">
-        <v>433</v>
+        <v>8</v>
       </c>
       <c r="D419">
         <v>1</v>
@@ -13465,13 +13462,13 @@
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A423">
-        <v>240120</v>
+        <v>580000</v>
       </c>
       <c r="B423" t="s">
-        <v>488</v>
+        <v>14</v>
       </c>
       <c r="C423" t="s">
-        <v>433</v>
+        <v>8</v>
       </c>
       <c r="D423">
         <v>1</v>
@@ -13545,13 +13542,13 @@
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A427">
-        <v>240210</v>
+        <v>580901</v>
       </c>
       <c r="B427" t="s">
-        <v>492</v>
+        <v>35</v>
       </c>
       <c r="C427" t="s">
-        <v>433</v>
+        <v>8</v>
       </c>
       <c r="D427">
         <v>1</v>
@@ -13645,13 +13642,13 @@
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A432">
-        <v>240220</v>
+        <v>610310</v>
       </c>
       <c r="B432" t="s">
-        <v>497</v>
+        <v>44</v>
       </c>
       <c r="C432" t="s">
-        <v>433</v>
+        <v>8</v>
       </c>
       <c r="D432">
         <v>1</v>
@@ -13705,13 +13702,13 @@
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A435">
-        <v>240310</v>
+        <v>610320</v>
       </c>
       <c r="B435" t="s">
-        <v>500</v>
+        <v>45</v>
       </c>
       <c r="C435" t="s">
-        <v>433</v>
+        <v>8</v>
       </c>
       <c r="D435">
         <v>1</v>
@@ -13765,13 +13762,13 @@
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A438">
-        <v>240320</v>
+        <v>620112</v>
       </c>
       <c r="B438" t="s">
-        <v>503</v>
+        <v>46</v>
       </c>
       <c r="C438" t="s">
-        <v>433</v>
+        <v>8</v>
       </c>
       <c r="D438">
         <v>1</v>
@@ -13825,13 +13822,13 @@
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A441">
-        <v>240900</v>
+        <v>670320</v>
       </c>
       <c r="B441" t="s">
-        <v>506</v>
+        <v>49</v>
       </c>
       <c r="C441" t="s">
-        <v>433</v>
+        <v>8</v>
       </c>
       <c r="D441">
         <v>1</v>
@@ -13845,13 +13842,13 @@
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A442">
-        <v>250110</v>
+        <v>190400</v>
       </c>
       <c r="B442" t="s">
-        <v>507</v>
+        <v>199</v>
       </c>
       <c r="C442" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D442">
         <v>1</v>
@@ -14025,13 +14022,13 @@
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A451">
-        <v>250220</v>
+        <v>190500</v>
       </c>
       <c r="B451" t="s">
-        <v>516</v>
+        <v>201</v>
       </c>
       <c r="C451" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D451">
         <v>1</v>
@@ -14105,13 +14102,13 @@
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A455">
-        <v>250900</v>
+        <v>190600</v>
       </c>
       <c r="B455" t="s">
-        <v>520</v>
+        <v>202</v>
       </c>
       <c r="C455" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D455">
         <v>1</v>
@@ -14285,13 +14282,13 @@
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A464">
-        <v>260110</v>
+        <v>190700</v>
       </c>
       <c r="B464" t="s">
-        <v>529</v>
+        <v>203</v>
       </c>
       <c r="C464" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D464">
         <v>1</v>
@@ -14385,13 +14382,13 @@
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A469">
-        <v>260210</v>
+        <v>190902</v>
       </c>
       <c r="B469" t="s">
-        <v>534</v>
+        <v>205</v>
       </c>
       <c r="C469" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D469">
         <v>1</v>
@@ -14484,14 +14481,14 @@
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A474">
-        <v>270210</v>
+      <c r="A474" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="B474" t="s">
-        <v>539</v>
+        <v>209</v>
       </c>
       <c r="C474" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D474">
         <v>1</v>
@@ -14584,14 +14581,14 @@
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A479">
-        <v>270410</v>
+      <c r="A479" s="1" t="s">
+        <v>212</v>
       </c>
       <c r="B479" t="s">
-        <v>544</v>
+        <v>213</v>
       </c>
       <c r="C479" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D479">
         <v>1</v>
@@ -14684,14 +14681,14 @@
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A484">
-        <v>270900</v>
+      <c r="A484" s="1" t="s">
+        <v>214</v>
       </c>
       <c r="B484" t="s">
-        <v>549</v>
+        <v>215</v>
       </c>
       <c r="C484" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D484">
         <v>1</v>
@@ -14784,14 +14781,14 @@
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A489">
-        <v>280110</v>
+      <c r="A489" s="1" t="s">
+        <v>216</v>
       </c>
       <c r="B489" t="s">
-        <v>554</v>
+        <v>217</v>
       </c>
       <c r="C489" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D489">
         <v>1</v>
@@ -14804,14 +14801,14 @@
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A490">
-        <v>280120</v>
+      <c r="A490" s="1" t="s">
+        <v>222</v>
       </c>
       <c r="B490" t="s">
-        <v>555</v>
+        <v>223</v>
       </c>
       <c r="C490" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D490">
         <v>1</v>
@@ -14844,14 +14841,14 @@
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A492">
-        <v>280140</v>
+      <c r="A492" s="1" t="s">
+        <v>224</v>
       </c>
       <c r="B492" t="s">
-        <v>557</v>
+        <v>225</v>
       </c>
       <c r="C492" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D492">
         <v>1</v>
@@ -14864,14 +14861,14 @@
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A493">
-        <v>280210</v>
+      <c r="A493" s="1" t="s">
+        <v>226</v>
       </c>
       <c r="B493" t="s">
-        <v>558</v>
+        <v>227</v>
       </c>
       <c r="C493" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D493">
         <v>1</v>
@@ -14884,14 +14881,14 @@
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A494">
-        <v>280220</v>
+      <c r="A494" s="1" t="s">
+        <v>228</v>
       </c>
       <c r="B494" t="s">
-        <v>559</v>
+        <v>229</v>
       </c>
       <c r="C494" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D494">
         <v>1</v>
@@ -14944,14 +14941,14 @@
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A497">
-        <v>290110</v>
+      <c r="A497" s="1" t="s">
+        <v>230</v>
       </c>
       <c r="B497" t="s">
-        <v>562</v>
+        <v>231</v>
       </c>
       <c r="C497" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D497">
         <v>1</v>
@@ -14964,14 +14961,14 @@
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A498">
-        <v>290120</v>
+      <c r="A498" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="B498" t="s">
-        <v>563</v>
+        <v>233</v>
       </c>
       <c r="C498" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D498">
         <v>1</v>
@@ -14984,14 +14981,14 @@
       </c>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A499">
-        <v>290210</v>
+      <c r="A499" s="1" t="s">
+        <v>234</v>
       </c>
       <c r="B499" t="s">
-        <v>564</v>
+        <v>235</v>
       </c>
       <c r="C499" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D499">
         <v>1</v>
@@ -15004,14 +15001,14 @@
       </c>
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A500">
-        <v>290310</v>
+      <c r="A500" s="1" t="s">
+        <v>236</v>
       </c>
       <c r="B500" t="s">
-        <v>565</v>
+        <v>237</v>
       </c>
       <c r="C500" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D500">
         <v>1</v>
@@ -15024,14 +15021,14 @@
       </c>
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A501">
-        <v>290320</v>
+      <c r="A501" s="1" t="s">
+        <v>238</v>
       </c>
       <c r="B501" t="s">
-        <v>566</v>
+        <v>239</v>
       </c>
       <c r="C501" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D501">
         <v>1</v>
@@ -15044,14 +15041,14 @@
       </c>
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A502">
-        <v>290410</v>
+      <c r="A502" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="B502" t="s">
-        <v>567</v>
+        <v>243</v>
       </c>
       <c r="C502" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D502">
         <v>1</v>
@@ -15064,14 +15061,14 @@
       </c>
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A503">
-        <v>290420</v>
+      <c r="A503" s="1" t="s">
+        <v>250</v>
       </c>
       <c r="B503" t="s">
-        <v>568</v>
+        <v>251</v>
       </c>
       <c r="C503" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D503">
         <v>1</v>
@@ -15084,14 +15081,14 @@
       </c>
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A504">
-        <v>290430</v>
+      <c r="A504" s="1" t="s">
+        <v>256</v>
       </c>
       <c r="B504" t="s">
-        <v>569</v>
+        <v>257</v>
       </c>
       <c r="C504" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D504">
         <v>1</v>
@@ -15104,14 +15101,14 @@
       </c>
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A505">
-        <v>290440</v>
+      <c r="A505" s="1" t="s">
+        <v>260</v>
       </c>
       <c r="B505" t="s">
-        <v>570</v>
+        <v>261</v>
       </c>
       <c r="C505" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D505">
         <v>1</v>
@@ -15124,14 +15121,14 @@
       </c>
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A506">
-        <v>300110</v>
+      <c r="A506" s="1" t="s">
+        <v>262</v>
       </c>
       <c r="B506" t="s">
-        <v>571</v>
+        <v>263</v>
       </c>
       <c r="C506" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D506">
         <v>1</v>
@@ -15284,14 +15281,14 @@
       </c>
     </row>
     <row r="514" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A514">
-        <v>300218</v>
+      <c r="A514" s="1" t="s">
+        <v>266</v>
       </c>
       <c r="B514" t="s">
-        <v>579</v>
+        <v>267</v>
       </c>
       <c r="C514" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D514">
         <v>1</v>
@@ -15364,14 +15361,14 @@
       </c>
     </row>
     <row r="518" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A518">
-        <v>300310</v>
+      <c r="A518" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B518" t="s">
-        <v>583</v>
+        <v>269</v>
       </c>
       <c r="C518" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D518">
         <v>1</v>
@@ -15424,14 +15421,14 @@
       </c>
     </row>
     <row r="521" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A521">
-        <v>300320</v>
+      <c r="A521" s="1" t="s">
+        <v>274</v>
       </c>
       <c r="B521" t="s">
-        <v>586</v>
+        <v>275</v>
       </c>
       <c r="C521" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D521">
         <v>1</v>
@@ -15484,14 +15481,14 @@
       </c>
     </row>
     <row r="524" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A524">
-        <v>300330</v>
+      <c r="A524" s="1" t="s">
+        <v>286</v>
       </c>
       <c r="B524" t="s">
-        <v>589</v>
+        <v>287</v>
       </c>
       <c r="C524" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D524">
         <v>1</v>
@@ -15544,14 +15541,14 @@
       </c>
     </row>
     <row r="527" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A527">
-        <v>300410</v>
+      <c r="A527" s="1" t="s">
+        <v>290</v>
       </c>
       <c r="B527" t="s">
-        <v>592</v>
+        <v>291</v>
       </c>
       <c r="C527" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D527">
         <v>1</v>
@@ -15604,14 +15601,14 @@
       </c>
     </row>
     <row r="530" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A530">
-        <v>300900</v>
+      <c r="A530" s="1" t="s">
+        <v>294</v>
       </c>
       <c r="B530" t="s">
-        <v>595</v>
+        <v>295</v>
       </c>
       <c r="C530" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D530">
         <v>1</v>
@@ -15624,14 +15621,14 @@
       </c>
     </row>
     <row r="531" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A531">
-        <v>320110</v>
+      <c r="A531" s="1" t="s">
+        <v>300</v>
       </c>
       <c r="B531" t="s">
-        <v>596</v>
+        <v>301</v>
       </c>
       <c r="C531" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D531">
         <v>1</v>
@@ -15664,14 +15661,14 @@
       </c>
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A533">
-        <v>320120</v>
+      <c r="A533" s="1" t="s">
+        <v>304</v>
       </c>
       <c r="B533" t="s">
-        <v>598</v>
+        <v>305</v>
       </c>
       <c r="C533" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D533">
         <v>1</v>
@@ -15684,14 +15681,14 @@
       </c>
     </row>
     <row r="534" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A534">
-        <v>320130</v>
+      <c r="A534" s="1" t="s">
+        <v>306</v>
       </c>
       <c r="B534" t="s">
-        <v>599</v>
+        <v>307</v>
       </c>
       <c r="C534" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D534">
         <v>1</v>
@@ -15705,13 +15702,13 @@
     </row>
     <row r="535" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A535">
-        <v>320140</v>
+        <v>100119</v>
       </c>
       <c r="B535" t="s">
-        <v>600</v>
+        <v>311</v>
       </c>
       <c r="C535" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D535">
         <v>1</v>
@@ -15725,13 +15722,13 @@
     </row>
     <row r="536" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A536">
-        <v>320150</v>
+        <v>100210</v>
       </c>
       <c r="B536" t="s">
-        <v>601</v>
+        <v>312</v>
       </c>
       <c r="C536" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D536">
         <v>1</v>
@@ -15845,13 +15842,13 @@
     </row>
     <row r="542" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A542">
-        <v>320221</v>
+        <v>100410</v>
       </c>
       <c r="B542" t="s">
-        <v>607</v>
+        <v>313</v>
       </c>
       <c r="C542" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D542">
         <v>1</v>
@@ -15905,13 +15902,13 @@
     </row>
     <row r="545" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A545">
-        <v>320233</v>
+        <v>110110</v>
       </c>
       <c r="B545" t="s">
-        <v>610</v>
+        <v>315</v>
       </c>
       <c r="C545" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D545">
         <v>1</v>
@@ -15965,13 +15962,13 @@
     </row>
     <row r="548" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A548">
-        <v>320330</v>
+        <v>110210</v>
       </c>
       <c r="B548" t="s">
-        <v>613</v>
+        <v>316</v>
       </c>
       <c r="C548" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D548">
         <v>1</v>
@@ -16005,13 +16002,13 @@
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A550">
-        <v>320345</v>
+        <v>110319</v>
       </c>
       <c r="B550" t="s">
-        <v>615</v>
+        <v>318</v>
       </c>
       <c r="C550" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D550">
         <v>1</v>
@@ -16065,13 +16062,13 @@
     </row>
     <row r="553" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A553">
-        <v>320370</v>
+        <v>110410</v>
       </c>
       <c r="B553" t="s">
-        <v>618</v>
+        <v>319</v>
       </c>
       <c r="C553" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D553">
         <v>1</v>
@@ -16085,13 +16082,13 @@
     </row>
     <row r="554" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A554">
-        <v>320380</v>
+        <v>120110</v>
       </c>
       <c r="B554" t="s">
-        <v>619</v>
+        <v>321</v>
       </c>
       <c r="C554" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D554">
         <v>1</v>
@@ -16105,13 +16102,13 @@
     </row>
     <row r="555" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A555">
-        <v>320410</v>
+        <v>120210</v>
       </c>
       <c r="B555" t="s">
-        <v>620</v>
+        <v>322</v>
       </c>
       <c r="C555" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D555">
         <v>1</v>
@@ -16125,13 +16122,13 @@
     </row>
     <row r="556" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A556">
-        <v>320420</v>
+        <v>120310</v>
       </c>
       <c r="B556" t="s">
-        <v>621</v>
+        <v>323</v>
       </c>
       <c r="C556" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D556">
         <v>1</v>
@@ -16145,13 +16142,13 @@
     </row>
     <row r="557" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A557">
-        <v>320430</v>
+        <v>120410</v>
       </c>
       <c r="B557" t="s">
-        <v>622</v>
+        <v>324</v>
       </c>
       <c r="C557" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D557">
         <v>1</v>
@@ -16165,13 +16162,13 @@
     </row>
     <row r="558" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A558">
-        <v>320511</v>
+        <v>130119</v>
       </c>
       <c r="B558" t="s">
-        <v>623</v>
+        <v>326</v>
       </c>
       <c r="C558" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D558">
         <v>1</v>
@@ -16185,13 +16182,13 @@
     </row>
     <row r="559" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A559">
-        <v>320512</v>
+        <v>130129</v>
       </c>
       <c r="B559" t="s">
-        <v>624</v>
+        <v>330</v>
       </c>
       <c r="C559" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D559">
         <v>1</v>
@@ -16205,13 +16202,13 @@
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A560">
-        <v>320521</v>
+        <v>150110</v>
       </c>
       <c r="B560" t="s">
-        <v>625</v>
+        <v>343</v>
       </c>
       <c r="C560" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D560">
         <v>1</v>
@@ -16225,13 +16222,13 @@
     </row>
     <row r="561" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A561">
-        <v>320522</v>
+        <v>150219</v>
       </c>
       <c r="B561" t="s">
-        <v>626</v>
+        <v>346</v>
       </c>
       <c r="C561" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D561">
         <v>1</v>
@@ -16245,13 +16242,13 @@
     </row>
     <row r="562" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A562">
-        <v>320610</v>
+        <v>150310</v>
       </c>
       <c r="B562" t="s">
-        <v>627</v>
+        <v>347</v>
       </c>
       <c r="C562" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D562">
         <v>1</v>
@@ -16405,13 +16402,13 @@
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A570">
-        <v>320627</v>
+        <v>160211</v>
       </c>
       <c r="B570" t="s">
-        <v>635</v>
+        <v>350</v>
       </c>
       <c r="C570" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D570">
         <v>1</v>
@@ -16425,13 +16422,13 @@
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A571">
-        <v>320630</v>
+        <v>160212</v>
       </c>
       <c r="B571" t="s">
-        <v>636</v>
+        <v>351</v>
       </c>
       <c r="C571" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D571">
         <v>1</v>
@@ -16485,13 +16482,13 @@
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A574">
-        <v>320901</v>
+        <v>160320</v>
       </c>
       <c r="B574" t="s">
-        <v>639</v>
+        <v>353</v>
       </c>
       <c r="C574" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D574">
         <v>1</v>
@@ -16505,13 +16502,13 @@
     </row>
     <row r="575" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A575">
-        <v>320902</v>
+        <v>170110</v>
       </c>
       <c r="B575" t="s">
-        <v>640</v>
+        <v>354</v>
       </c>
       <c r="C575" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D575">
         <v>1</v>
@@ -16525,13 +16522,13 @@
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A576">
-        <v>320903</v>
+        <v>170210</v>
       </c>
       <c r="B576" t="s">
-        <v>641</v>
+        <v>355</v>
       </c>
       <c r="C576" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D576">
         <v>1</v>
@@ -16545,13 +16542,13 @@
     </row>
     <row r="577" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A577">
-        <v>320904</v>
+        <v>170520</v>
       </c>
       <c r="B577" t="s">
-        <v>642</v>
+        <v>359</v>
       </c>
       <c r="C577" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D577">
         <v>1</v>
@@ -16565,13 +16562,13 @@
     </row>
     <row r="578" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A578">
-        <v>320905</v>
+        <v>170531</v>
       </c>
       <c r="B578" t="s">
-        <v>643</v>
+        <v>361</v>
       </c>
       <c r="C578" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D578">
         <v>1</v>
@@ -16625,13 +16622,13 @@
     </row>
     <row r="581" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A581">
-        <v>330310</v>
+        <v>170539</v>
       </c>
       <c r="B581" t="s">
-        <v>646</v>
+        <v>364</v>
       </c>
       <c r="C581" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D581">
         <v>1</v>
@@ -16645,13 +16642,13 @@
     </row>
     <row r="582" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A582">
-        <v>330410</v>
+        <v>180110</v>
       </c>
       <c r="B582" t="s">
-        <v>647</v>
+        <v>365</v>
       </c>
       <c r="C582" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D582">
         <v>1</v>
@@ -16665,13 +16662,13 @@
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A583">
-        <v>330510</v>
+        <v>180210</v>
       </c>
       <c r="B583" t="s">
-        <v>648</v>
+        <v>366</v>
       </c>
       <c r="C583" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D583">
         <v>1</v>
@@ -16705,13 +16702,13 @@
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A585">
-        <v>330610</v>
+        <v>180220</v>
       </c>
       <c r="B585" t="s">
-        <v>650</v>
+        <v>367</v>
       </c>
       <c r="C585" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D585">
         <v>1</v>
@@ -16725,13 +16722,13 @@
     </row>
     <row r="586" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A586">
-        <v>340310</v>
+        <v>180310</v>
       </c>
       <c r="B586" t="s">
-        <v>651</v>
+        <v>368</v>
       </c>
       <c r="C586" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D586">
         <v>1</v>
@@ -16745,13 +16742,13 @@
     </row>
     <row r="587" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A587">
-        <v>340410</v>
+        <v>180320</v>
       </c>
       <c r="B587" t="s">
-        <v>652</v>
+        <v>369</v>
       </c>
       <c r="C587" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D587">
         <v>1</v>
@@ -16785,13 +16782,13 @@
     </row>
     <row r="589" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A589">
-        <v>340510</v>
+        <v>180410</v>
       </c>
       <c r="B589" t="s">
-        <v>654</v>
+        <v>370</v>
       </c>
       <c r="C589" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D589">
         <v>1</v>
@@ -16805,13 +16802,13 @@
     </row>
     <row r="590" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A590">
-        <v>340520</v>
+        <v>180420</v>
       </c>
       <c r="B590" t="s">
-        <v>655</v>
+        <v>371</v>
       </c>
       <c r="C590" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D590">
         <v>1</v>
@@ -16825,13 +16822,13 @@
     </row>
     <row r="591" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A591">
-        <v>340530</v>
+        <v>180510</v>
       </c>
       <c r="B591" t="s">
-        <v>656</v>
+        <v>372</v>
       </c>
       <c r="C591" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D591">
         <v>1</v>
@@ -16845,13 +16842,13 @@
     </row>
     <row r="592" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A592">
-        <v>340620</v>
+        <v>180520</v>
       </c>
       <c r="B592" t="s">
-        <v>657</v>
+        <v>373</v>
       </c>
       <c r="C592" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D592">
         <v>1</v>
@@ -16865,13 +16862,13 @@
     </row>
     <row r="593" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A593">
-        <v>340630</v>
+        <v>180611</v>
       </c>
       <c r="B593" t="s">
-        <v>658</v>
+        <v>375</v>
       </c>
       <c r="C593" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D593">
         <v>1</v>
@@ -16885,13 +16882,13 @@
     </row>
     <row r="594" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A594">
-        <v>340901</v>
+        <v>180612</v>
       </c>
       <c r="B594" t="s">
-        <v>659</v>
+        <v>376</v>
       </c>
       <c r="C594" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D594">
         <v>1</v>
@@ -16905,13 +16902,13 @@
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A595">
-        <v>340903</v>
+        <v>180620</v>
       </c>
       <c r="B595" t="s">
-        <v>660</v>
+        <v>377</v>
       </c>
       <c r="C595" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D595">
         <v>1</v>
@@ -16925,13 +16922,13 @@
     </row>
     <row r="596" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A596">
-        <v>340904</v>
+        <v>180710</v>
       </c>
       <c r="B596" t="s">
-        <v>661</v>
+        <v>378</v>
       </c>
       <c r="C596" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D596">
         <v>1</v>
@@ -16945,13 +16942,13 @@
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A597">
-        <v>340907</v>
+        <v>190905</v>
       </c>
       <c r="B597" t="s">
-        <v>662</v>
+        <v>410</v>
       </c>
       <c r="C597" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D597">
         <v>1</v>
@@ -17024,20 +17021,20 @@
       </c>
     </row>
     <row r="601" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A601">
-        <v>340913</v>
+      <c r="A601" s="1" t="s">
+        <v>1326</v>
       </c>
       <c r="B601" t="s">
-        <v>666</v>
+        <v>1327</v>
       </c>
       <c r="C601" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D601">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E601">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F601">
         <v>1</v>
@@ -17064,40 +17061,40 @@
       </c>
     </row>
     <row r="603" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A603">
-        <v>340915</v>
+      <c r="A603" s="1" t="s">
+        <v>1328</v>
       </c>
       <c r="B603" t="s">
-        <v>668</v>
+        <v>1329</v>
       </c>
       <c r="C603" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D603">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E603">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F603">
         <v>1</v>
       </c>
     </row>
     <row r="604" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A604">
-        <v>350110</v>
+      <c r="A604" s="1" t="s">
+        <v>1330</v>
       </c>
       <c r="B604" t="s">
-        <v>669</v>
+        <v>1331</v>
       </c>
       <c r="C604" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D604">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E604">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F604">
         <v>1</v>
@@ -18625,19 +18622,19 @@
     </row>
     <row r="681" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A681">
-        <v>999000</v>
+        <v>100519</v>
       </c>
       <c r="B681" t="s">
-        <v>746</v>
+        <v>1332</v>
       </c>
       <c r="C681" t="s">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="D681">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E681">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F681">
         <v>1</v>
@@ -18645,19 +18642,19 @@
     </row>
     <row r="682" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A682">
-        <v>360110</v>
+        <v>140219</v>
       </c>
       <c r="B682" t="s">
-        <v>747</v>
+        <v>1333</v>
       </c>
       <c r="C682" t="s">
-        <v>748</v>
+        <v>200</v>
       </c>
       <c r="D682">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E682">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F682">
         <v>1</v>
@@ -18665,19 +18662,19 @@
     </row>
     <row r="683" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A683">
-        <v>360120</v>
+        <v>140349</v>
       </c>
       <c r="B683" t="s">
-        <v>749</v>
+        <v>1334</v>
       </c>
       <c r="C683" t="s">
-        <v>748</v>
+        <v>200</v>
       </c>
       <c r="D683">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E683">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F683">
         <v>1</v>
@@ -18685,19 +18682,19 @@
     </row>
     <row r="684" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A684">
-        <v>360210</v>
+        <v>170319</v>
       </c>
       <c r="B684" t="s">
-        <v>750</v>
+        <v>1335</v>
       </c>
       <c r="C684" t="s">
-        <v>748</v>
+        <v>200</v>
       </c>
       <c r="D684">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E684">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F684">
         <v>1</v>
@@ -18764,14 +18761,14 @@
       </c>
     </row>
     <row r="688" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A688">
-        <v>360330</v>
+      <c r="A688" s="1" t="s">
+        <v>431</v>
       </c>
       <c r="B688" t="s">
-        <v>754</v>
+        <v>432</v>
       </c>
       <c r="C688" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D688">
         <v>1</v>
@@ -18844,14 +18841,14 @@
       </c>
     </row>
     <row r="692" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A692">
-        <v>360420</v>
+      <c r="A692" s="1" t="s">
+        <v>434</v>
       </c>
       <c r="B692" t="s">
-        <v>758</v>
+        <v>435</v>
       </c>
       <c r="C692" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D692">
         <v>1</v>
@@ -18905,13 +18902,13 @@
     </row>
     <row r="695" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A695">
-        <v>360513</v>
+        <v>210110</v>
       </c>
       <c r="B695" t="s">
-        <v>761</v>
+        <v>436</v>
       </c>
       <c r="C695" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D695">
         <v>1</v>
@@ -18925,13 +18922,13 @@
     </row>
     <row r="696" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A696">
-        <v>360901</v>
+        <v>220000</v>
       </c>
       <c r="B696" t="s">
-        <v>762</v>
+        <v>439</v>
       </c>
       <c r="C696" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D696">
         <v>1</v>
@@ -18945,13 +18942,13 @@
     </row>
     <row r="697" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A697">
-        <v>360902</v>
+        <v>220110</v>
       </c>
       <c r="B697" t="s">
-        <v>763</v>
+        <v>440</v>
       </c>
       <c r="C697" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D697">
         <v>1</v>
@@ -18965,13 +18962,13 @@
     </row>
     <row r="698" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A698">
-        <v>370110</v>
+        <v>220120</v>
       </c>
       <c r="B698" t="s">
-        <v>764</v>
+        <v>442</v>
       </c>
       <c r="C698" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D698">
         <v>1</v>
@@ -19005,13 +19002,13 @@
     </row>
     <row r="700" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A700">
-        <v>370125</v>
+        <v>220210</v>
       </c>
       <c r="B700" t="s">
-        <v>766</v>
+        <v>443</v>
       </c>
       <c r="C700" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D700">
         <v>1</v>
@@ -19105,13 +19102,13 @@
     </row>
     <row r="705" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A705">
-        <v>370220</v>
+        <v>220610</v>
       </c>
       <c r="B705" t="s">
-        <v>771</v>
+        <v>451</v>
       </c>
       <c r="C705" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D705">
         <v>1</v>
@@ -19225,13 +19222,13 @@
     </row>
     <row r="711" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A711">
-        <v>370902</v>
+        <v>230000</v>
       </c>
       <c r="B711" t="s">
-        <v>777</v>
+        <v>458</v>
       </c>
       <c r="C711" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D711">
         <v>1</v>
@@ -19245,13 +19242,13 @@
     </row>
     <row r="712" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A712">
-        <v>370903</v>
+        <v>230110</v>
       </c>
       <c r="B712" t="s">
-        <v>778</v>
+        <v>459</v>
       </c>
       <c r="C712" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D712">
         <v>1</v>
@@ -19285,13 +19282,13 @@
     </row>
     <row r="714" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A714">
-        <v>380110</v>
+        <v>230140</v>
       </c>
       <c r="B714" t="s">
-        <v>780</v>
+        <v>476</v>
       </c>
       <c r="C714" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D714">
         <v>1</v>
@@ -19325,13 +19322,13 @@
     </row>
     <row r="716" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A716">
-        <v>380210</v>
+        <v>230900</v>
       </c>
       <c r="B716" t="s">
-        <v>782</v>
+        <v>481</v>
       </c>
       <c r="C716" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D716">
         <v>1</v>
@@ -19565,13 +19562,13 @@
     </row>
     <row r="728" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A728">
-        <v>380430</v>
+        <v>240110</v>
       </c>
       <c r="B728" t="s">
-        <v>794</v>
+        <v>484</v>
       </c>
       <c r="C728" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D728">
         <v>1</v>
@@ -19585,13 +19582,13 @@
     </row>
     <row r="729" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A729">
-        <v>380510</v>
+        <v>240120</v>
       </c>
       <c r="B729" t="s">
-        <v>795</v>
+        <v>488</v>
       </c>
       <c r="C729" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D729">
         <v>1</v>
@@ -19605,13 +19602,13 @@
     </row>
     <row r="730" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A730">
-        <v>380901</v>
+        <v>240210</v>
       </c>
       <c r="B730" t="s">
-        <v>796</v>
+        <v>492</v>
       </c>
       <c r="C730" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D730">
         <v>1</v>
@@ -19665,13 +19662,13 @@
     </row>
     <row r="733" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A733">
-        <v>390110</v>
+        <v>240220</v>
       </c>
       <c r="B733" t="s">
-        <v>799</v>
+        <v>497</v>
       </c>
       <c r="C733" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D733">
         <v>1</v>
@@ -19685,13 +19682,13 @@
     </row>
     <row r="734" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A734">
-        <v>390120</v>
+        <v>240310</v>
       </c>
       <c r="B734" t="s">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="C734" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D734">
         <v>1</v>
@@ -19705,13 +19702,13 @@
     </row>
     <row r="735" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A735">
-        <v>390210</v>
+        <v>240320</v>
       </c>
       <c r="B735" t="s">
-        <v>801</v>
+        <v>503</v>
       </c>
       <c r="C735" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D735">
         <v>1</v>
@@ -19765,13 +19762,13 @@
     </row>
     <row r="738" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A738">
-        <v>390223</v>
+        <v>240900</v>
       </c>
       <c r="B738" t="s">
-        <v>804</v>
+        <v>506</v>
       </c>
       <c r="C738" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D738">
         <v>1</v>
@@ -19845,13 +19842,13 @@
     </row>
     <row r="742" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A742">
-        <v>390322</v>
+        <v>250110</v>
       </c>
       <c r="B742" t="s">
-        <v>808</v>
+        <v>507</v>
       </c>
       <c r="C742" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D742">
         <v>1</v>
@@ -19865,13 +19862,13 @@
     </row>
     <row r="743" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A743">
-        <v>390901</v>
+        <v>250220</v>
       </c>
       <c r="B743" t="s">
-        <v>809</v>
+        <v>516</v>
       </c>
       <c r="C743" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D743">
         <v>1</v>
@@ -19885,13 +19882,13 @@
     </row>
     <row r="744" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A744">
-        <v>390902</v>
+        <v>250900</v>
       </c>
       <c r="B744" t="s">
-        <v>810</v>
+        <v>520</v>
       </c>
       <c r="C744" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D744">
         <v>1</v>
@@ -19905,13 +19902,13 @@
     </row>
     <row r="745" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A745">
-        <v>400110</v>
+        <v>260110</v>
       </c>
       <c r="B745" t="s">
-        <v>811</v>
+        <v>529</v>
       </c>
       <c r="C745" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D745">
         <v>1</v>
@@ -19925,13 +19922,13 @@
     </row>
     <row r="746" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A746">
-        <v>400210</v>
+        <v>260210</v>
       </c>
       <c r="B746" t="s">
-        <v>812</v>
+        <v>534</v>
       </c>
       <c r="C746" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D746">
         <v>1</v>
@@ -19945,13 +19942,13 @@
     </row>
     <row r="747" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A747">
-        <v>400220</v>
+        <v>270210</v>
       </c>
       <c r="B747" t="s">
-        <v>813</v>
+        <v>539</v>
       </c>
       <c r="C747" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D747">
         <v>1</v>
@@ -19965,13 +19962,13 @@
     </row>
     <row r="748" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A748">
-        <v>400310</v>
+        <v>270410</v>
       </c>
       <c r="B748" t="s">
-        <v>814</v>
+        <v>544</v>
       </c>
       <c r="C748" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D748">
         <v>1</v>
@@ -19985,13 +19982,13 @@
     </row>
     <row r="749" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A749">
-        <v>410110</v>
+        <v>270900</v>
       </c>
       <c r="B749" t="s">
-        <v>815</v>
+        <v>549</v>
       </c>
       <c r="C749" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D749">
         <v>1</v>
@@ -20105,13 +20102,13 @@
     </row>
     <row r="755" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A755">
-        <v>410130</v>
+        <v>280110</v>
       </c>
       <c r="B755" t="s">
-        <v>821</v>
+        <v>554</v>
       </c>
       <c r="C755" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D755">
         <v>1</v>
@@ -20325,13 +20322,13 @@
     </row>
     <row r="766" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A766">
-        <v>430110</v>
+        <v>280120</v>
       </c>
       <c r="B766" t="s">
-        <v>832</v>
+        <v>555</v>
       </c>
       <c r="C766" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D766">
         <v>1</v>
@@ -20345,13 +20342,13 @@
     </row>
     <row r="767" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A767">
-        <v>430120</v>
+        <v>280140</v>
       </c>
       <c r="B767" t="s">
-        <v>833</v>
+        <v>557</v>
       </c>
       <c r="C767" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D767">
         <v>1</v>
@@ -20365,13 +20362,13 @@
     </row>
     <row r="768" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A768">
-        <v>440110</v>
+        <v>280210</v>
       </c>
       <c r="B768" t="s">
-        <v>834</v>
+        <v>558</v>
       </c>
       <c r="C768" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D768">
         <v>1</v>
@@ -20385,13 +20382,13 @@
     </row>
     <row r="769" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A769">
-        <v>440120</v>
+        <v>280220</v>
       </c>
       <c r="B769" t="s">
-        <v>835</v>
+        <v>559</v>
       </c>
       <c r="C769" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D769">
         <v>1</v>
@@ -20405,13 +20402,13 @@
     </row>
     <row r="770" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A770">
-        <v>440130</v>
+        <v>290110</v>
       </c>
       <c r="B770" t="s">
-        <v>836</v>
+        <v>562</v>
       </c>
       <c r="C770" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D770">
         <v>1</v>
@@ -20425,13 +20422,13 @@
     </row>
     <row r="771" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A771">
-        <v>440140</v>
+        <v>290120</v>
       </c>
       <c r="B771" t="s">
-        <v>837</v>
+        <v>563</v>
       </c>
       <c r="C771" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D771">
         <v>1</v>
@@ -20445,13 +20442,13 @@
     </row>
     <row r="772" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A772">
-        <v>440150</v>
+        <v>290210</v>
       </c>
       <c r="B772" t="s">
-        <v>838</v>
+        <v>564</v>
       </c>
       <c r="C772" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D772">
         <v>1</v>
@@ -20465,13 +20462,13 @@
     </row>
     <row r="773" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A773">
-        <v>440210</v>
+        <v>290310</v>
       </c>
       <c r="B773" t="s">
-        <v>839</v>
+        <v>565</v>
       </c>
       <c r="C773" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D773">
         <v>1</v>
@@ -20485,13 +20482,13 @@
     </row>
     <row r="774" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A774">
-        <v>440900</v>
+        <v>290320</v>
       </c>
       <c r="B774" t="s">
-        <v>840</v>
+        <v>566</v>
       </c>
       <c r="C774" t="s">
-        <v>748</v>
+        <v>433</v>
       </c>
       <c r="D774">
         <v>1</v>
@@ -20565,13 +20562,13 @@
     </row>
     <row r="778" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A778">
-        <v>600110</v>
+        <v>290410</v>
       </c>
       <c r="B778" t="s">
-        <v>844</v>
+        <v>567</v>
       </c>
       <c r="C778" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D778">
         <v>1</v>
@@ -20585,13 +20582,13 @@
     </row>
     <row r="779" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A779">
-        <v>600120</v>
+        <v>290420</v>
       </c>
       <c r="B779" t="s">
-        <v>846</v>
+        <v>568</v>
       </c>
       <c r="C779" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D779">
         <v>1</v>
@@ -20685,13 +20682,13 @@
     </row>
     <row r="784" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A784">
-        <v>600130</v>
+        <v>290430</v>
       </c>
       <c r="B784" t="s">
-        <v>851</v>
+        <v>569</v>
       </c>
       <c r="C784" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D784">
         <v>1</v>
@@ -20865,13 +20862,13 @@
     </row>
     <row r="793" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A793">
-        <v>600210</v>
+        <v>290440</v>
       </c>
       <c r="B793" t="s">
-        <v>860</v>
+        <v>570</v>
       </c>
       <c r="C793" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D793">
         <v>1</v>
@@ -20885,13 +20882,13 @@
     </row>
     <row r="794" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A794">
-        <v>600410</v>
+        <v>300110</v>
       </c>
       <c r="B794" t="s">
-        <v>861</v>
+        <v>571</v>
       </c>
       <c r="C794" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D794">
         <v>1</v>
@@ -20905,13 +20902,13 @@
     </row>
     <row r="795" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A795">
-        <v>600420</v>
+        <v>300218</v>
       </c>
       <c r="B795" t="s">
-        <v>862</v>
+        <v>579</v>
       </c>
       <c r="C795" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D795">
         <v>1</v>
@@ -20925,13 +20922,13 @@
     </row>
     <row r="796" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A796">
-        <v>600430</v>
+        <v>300310</v>
       </c>
       <c r="B796" t="s">
-        <v>863</v>
+        <v>583</v>
       </c>
       <c r="C796" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D796">
         <v>1</v>
@@ -20945,13 +20942,13 @@
     </row>
     <row r="797" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A797">
-        <v>600900</v>
+        <v>300320</v>
       </c>
       <c r="B797" t="s">
-        <v>864</v>
+        <v>586</v>
       </c>
       <c r="C797" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D797">
         <v>1</v>
@@ -21005,13 +21002,13 @@
     </row>
     <row r="800" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A800">
-        <v>600903</v>
+        <v>300330</v>
       </c>
       <c r="B800" t="s">
-        <v>867</v>
+        <v>589</v>
       </c>
       <c r="C800" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D800">
         <v>1</v>
@@ -21025,13 +21022,13 @@
     </row>
     <row r="801" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A801">
-        <v>610110</v>
+        <v>300410</v>
       </c>
       <c r="B801" t="s">
-        <v>868</v>
+        <v>592</v>
       </c>
       <c r="C801" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D801">
         <v>1</v>
@@ -21045,13 +21042,13 @@
     </row>
     <row r="802" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A802">
-        <v>610120</v>
+        <v>300900</v>
       </c>
       <c r="B802" t="s">
-        <v>869</v>
+        <v>595</v>
       </c>
       <c r="C802" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D802">
         <v>1</v>
@@ -21065,13 +21062,13 @@
     </row>
     <row r="803" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A803">
-        <v>610130</v>
+        <v>320110</v>
       </c>
       <c r="B803" t="s">
-        <v>870</v>
+        <v>596</v>
       </c>
       <c r="C803" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D803">
         <v>1</v>
@@ -21105,13 +21102,13 @@
     </row>
     <row r="805" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A805">
-        <v>610901</v>
+        <v>320120</v>
       </c>
       <c r="B805" t="s">
-        <v>872</v>
+        <v>598</v>
       </c>
       <c r="C805" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D805">
         <v>1</v>
@@ -21125,13 +21122,13 @@
     </row>
     <row r="806" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A806">
-        <v>610902</v>
+        <v>320130</v>
       </c>
       <c r="B806" t="s">
-        <v>873</v>
+        <v>599</v>
       </c>
       <c r="C806" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D806">
         <v>1</v>
@@ -21145,13 +21142,13 @@
     </row>
     <row r="807" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A807">
-        <v>610903</v>
+        <v>320140</v>
       </c>
       <c r="B807" t="s">
-        <v>874</v>
+        <v>600</v>
       </c>
       <c r="C807" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D807">
         <v>1</v>
@@ -21185,13 +21182,13 @@
     </row>
     <row r="809" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A809">
-        <v>620111</v>
+        <v>320150</v>
       </c>
       <c r="B809" t="s">
-        <v>876</v>
+        <v>601</v>
       </c>
       <c r="C809" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D809">
         <v>1</v>
@@ -21205,13 +21202,13 @@
     </row>
     <row r="810" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A810">
-        <v>620121</v>
+        <v>320221</v>
       </c>
       <c r="B810" t="s">
-        <v>877</v>
+        <v>607</v>
       </c>
       <c r="C810" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D810">
         <v>1</v>
@@ -21285,13 +21282,13 @@
     </row>
     <row r="814" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A814">
-        <v>620213</v>
+        <v>320233</v>
       </c>
       <c r="B814" t="s">
-        <v>881</v>
+        <v>610</v>
       </c>
       <c r="C814" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D814">
         <v>1</v>
@@ -21305,13 +21302,13 @@
     </row>
     <row r="815" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A815">
-        <v>620214</v>
+        <v>320330</v>
       </c>
       <c r="B815" t="s">
-        <v>882</v>
+        <v>613</v>
       </c>
       <c r="C815" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D815">
         <v>1</v>
@@ -21365,13 +21362,13 @@
     </row>
     <row r="818" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A818">
-        <v>620221</v>
+        <v>320345</v>
       </c>
       <c r="B818" t="s">
-        <v>885</v>
+        <v>615</v>
       </c>
       <c r="C818" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D818">
         <v>1</v>
@@ -21405,13 +21402,13 @@
     </row>
     <row r="820" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A820">
-        <v>620310</v>
+        <v>320370</v>
       </c>
       <c r="B820" t="s">
-        <v>887</v>
+        <v>618</v>
       </c>
       <c r="C820" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D820">
         <v>1</v>
@@ -21425,13 +21422,13 @@
     </row>
     <row r="821" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A821">
-        <v>620320</v>
+        <v>320380</v>
       </c>
       <c r="B821" t="s">
-        <v>888</v>
+        <v>619</v>
       </c>
       <c r="C821" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D821">
         <v>1</v>
@@ -21445,13 +21442,13 @@
     </row>
     <row r="822" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A822">
-        <v>620330</v>
+        <v>320410</v>
       </c>
       <c r="B822" t="s">
-        <v>889</v>
+        <v>620</v>
       </c>
       <c r="C822" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D822">
         <v>1</v>
@@ -21465,13 +21462,13 @@
     </row>
     <row r="823" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A823">
-        <v>620410</v>
+        <v>320420</v>
       </c>
       <c r="B823" t="s">
-        <v>890</v>
+        <v>621</v>
       </c>
       <c r="C823" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D823">
         <v>1</v>
@@ -21485,13 +21482,13 @@
     </row>
     <row r="824" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A824">
-        <v>620420</v>
+        <v>320430</v>
       </c>
       <c r="B824" t="s">
-        <v>891</v>
+        <v>622</v>
       </c>
       <c r="C824" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D824">
         <v>1</v>
@@ -21505,13 +21502,13 @@
     </row>
     <row r="825" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A825">
-        <v>620510</v>
+        <v>320511</v>
       </c>
       <c r="B825" t="s">
-        <v>892</v>
+        <v>623</v>
       </c>
       <c r="C825" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D825">
         <v>1</v>
@@ -21525,13 +21522,13 @@
     </row>
     <row r="826" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A826">
-        <v>620610</v>
+        <v>320512</v>
       </c>
       <c r="B826" t="s">
-        <v>893</v>
+        <v>624</v>
       </c>
       <c r="C826" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D826">
         <v>1</v>
@@ -21545,13 +21542,13 @@
     </row>
     <row r="827" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A827">
-        <v>620710</v>
+        <v>320521</v>
       </c>
       <c r="B827" t="s">
-        <v>894</v>
+        <v>625</v>
       </c>
       <c r="C827" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D827">
         <v>1</v>
@@ -21565,13 +21562,13 @@
     </row>
     <row r="828" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A828">
-        <v>620810</v>
+        <v>320522</v>
       </c>
       <c r="B828" t="s">
-        <v>895</v>
+        <v>626</v>
       </c>
       <c r="C828" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D828">
         <v>1</v>
@@ -21765,13 +21762,13 @@
     </row>
     <row r="838" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A838">
-        <v>620915</v>
+        <v>320610</v>
       </c>
       <c r="B838" t="s">
-        <v>905</v>
+        <v>627</v>
       </c>
       <c r="C838" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D838">
         <v>1</v>
@@ -21845,13 +21842,13 @@
     </row>
     <row r="842" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A842">
-        <v>620925</v>
+        <v>320627</v>
       </c>
       <c r="B842" t="s">
-        <v>909</v>
+        <v>635</v>
       </c>
       <c r="C842" t="s">
-        <v>845</v>
+        <v>433</v>
       </c>
       <c r="D842">
         <v>1</v>
@@ -22485,13 +22482,13 @@
     </row>
     <row r="874" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A874">
-        <v>200310</v>
+        <v>320630</v>
       </c>
       <c r="B874" t="s">
-        <v>942</v>
+        <v>636</v>
       </c>
       <c r="C874" t="s">
-        <v>939</v>
+        <v>433</v>
       </c>
       <c r="D874">
         <v>1</v>
@@ -22965,13 +22962,13 @@
     </row>
     <row r="898" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A898">
-        <v>790420</v>
+        <v>320901</v>
       </c>
       <c r="B898" t="s">
-        <v>966</v>
+        <v>639</v>
       </c>
       <c r="C898" t="s">
-        <v>939</v>
+        <v>433</v>
       </c>
       <c r="D898">
         <v>1</v>
@@ -22985,13 +22982,13 @@
     </row>
     <row r="899" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A899">
-        <v>270000</v>
+        <v>320902</v>
       </c>
       <c r="B899" t="s">
-        <v>967</v>
+        <v>640</v>
       </c>
       <c r="C899" t="s">
-        <v>968</v>
+        <v>433</v>
       </c>
       <c r="D899">
         <v>1</v>
@@ -23085,13 +23082,13 @@
     </row>
     <row r="904" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A904">
-        <v>270310</v>
+        <v>320903</v>
       </c>
       <c r="B904" t="s">
-        <v>973</v>
+        <v>641</v>
       </c>
       <c r="C904" t="s">
-        <v>968</v>
+        <v>433</v>
       </c>
       <c r="D904">
         <v>1</v>
@@ -23105,13 +23102,13 @@
     </row>
     <row r="905" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A905">
-        <v>270311</v>
+        <v>320904</v>
       </c>
       <c r="B905" t="s">
-        <v>974</v>
+        <v>642</v>
       </c>
       <c r="C905" t="s">
-        <v>968</v>
+        <v>433</v>
       </c>
       <c r="D905">
         <v>1</v>
@@ -23185,13 +23182,13 @@
     </row>
     <row r="909" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A909">
-        <v>310140</v>
+        <v>320905</v>
       </c>
       <c r="B909" t="s">
-        <v>978</v>
+        <v>643</v>
       </c>
       <c r="C909" t="s">
-        <v>968</v>
+        <v>433</v>
       </c>
       <c r="D909">
         <v>1</v>
@@ -23205,13 +23202,13 @@
     </row>
     <row r="910" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A910">
-        <v>310210</v>
+        <v>330310</v>
       </c>
       <c r="B910" t="s">
-        <v>979</v>
+        <v>646</v>
       </c>
       <c r="C910" t="s">
-        <v>968</v>
+        <v>433</v>
       </c>
       <c r="D910">
         <v>1</v>
@@ -23225,13 +23222,13 @@
     </row>
     <row r="911" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A911">
-        <v>310220</v>
+        <v>330410</v>
       </c>
       <c r="B911" t="s">
-        <v>980</v>
+        <v>647</v>
       </c>
       <c r="C911" t="s">
-        <v>968</v>
+        <v>433</v>
       </c>
       <c r="D911">
         <v>1</v>
@@ -23245,13 +23242,13 @@
     </row>
     <row r="912" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A912">
-        <v>310230</v>
+        <v>330510</v>
       </c>
       <c r="B912" t="s">
-        <v>981</v>
+        <v>648</v>
       </c>
       <c r="C912" t="s">
-        <v>968</v>
+        <v>433</v>
       </c>
       <c r="D912">
         <v>1</v>
@@ -23265,13 +23262,13 @@
     </row>
     <row r="913" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A913">
-        <v>310231</v>
+        <v>330610</v>
       </c>
       <c r="B913" t="s">
-        <v>982</v>
+        <v>650</v>
       </c>
       <c r="C913" t="s">
-        <v>968</v>
+        <v>433</v>
       </c>
       <c r="D913">
         <v>1</v>
@@ -23285,13 +23282,13 @@
     </row>
     <row r="914" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A914">
-        <v>310232</v>
+        <v>340310</v>
       </c>
       <c r="B914" t="s">
-        <v>983</v>
+        <v>651</v>
       </c>
       <c r="C914" t="s">
-        <v>968</v>
+        <v>433</v>
       </c>
       <c r="D914">
         <v>1</v>
@@ -23325,13 +23322,13 @@
     </row>
     <row r="916" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A916">
-        <v>310241</v>
+        <v>340410</v>
       </c>
       <c r="B916" t="s">
-        <v>985</v>
+        <v>652</v>
       </c>
       <c r="C916" t="s">
-        <v>968</v>
+        <v>433</v>
       </c>
       <c r="D916">
         <v>1</v>
@@ -23345,13 +23342,13 @@
     </row>
     <row r="917" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A917">
-        <v>310242</v>
+        <v>340510</v>
       </c>
       <c r="B917" t="s">
-        <v>986</v>
+        <v>654</v>
       </c>
       <c r="C917" t="s">
-        <v>968</v>
+        <v>433</v>
       </c>
       <c r="D917">
         <v>1</v>
@@ -23445,13 +23442,13 @@
     </row>
     <row r="922" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A922">
-        <v>310314</v>
+        <v>340520</v>
       </c>
       <c r="B922" t="s">
-        <v>991</v>
+        <v>655</v>
       </c>
       <c r="C922" t="s">
-        <v>968</v>
+        <v>433</v>
       </c>
       <c r="D922">
         <v>1</v>
@@ -23465,13 +23462,13 @@
     </row>
     <row r="923" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A923">
-        <v>310315</v>
+        <v>340530</v>
       </c>
       <c r="B923" t="s">
-        <v>992</v>
+        <v>656</v>
       </c>
       <c r="C923" t="s">
-        <v>968</v>
+        <v>433</v>
       </c>
       <c r="D923">
         <v>1</v>
@@ -23485,13 +23482,13 @@
     </row>
     <row r="924" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A924">
-        <v>310316</v>
+        <v>340620</v>
       </c>
       <c r="B924" t="s">
-        <v>993</v>
+        <v>657</v>
       </c>
       <c r="C924" t="s">
-        <v>968</v>
+        <v>433</v>
       </c>
       <c r="D924">
         <v>1</v>
@@ -23545,13 +23542,13 @@
     </row>
     <row r="927" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A927">
-        <v>310331</v>
+        <v>340630</v>
       </c>
       <c r="B927" t="s">
-        <v>996</v>
+        <v>658</v>
       </c>
       <c r="C927" t="s">
-        <v>968</v>
+        <v>433</v>
       </c>
       <c r="D927">
         <v>1</v>
@@ -23565,13 +23562,13 @@
     </row>
     <row r="928" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A928">
-        <v>310332</v>
+        <v>340901</v>
       </c>
       <c r="B928" t="s">
-        <v>997</v>
+        <v>659</v>
       </c>
       <c r="C928" t="s">
-        <v>968</v>
+        <v>433</v>
       </c>
       <c r="D928">
         <v>1</v>
@@ -23605,13 +23602,13 @@
     </row>
     <row r="930" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A930">
-        <v>310334</v>
+        <v>340903</v>
       </c>
       <c r="B930" t="s">
-        <v>999</v>
+        <v>660</v>
       </c>
       <c r="C930" t="s">
-        <v>968</v>
+        <v>433</v>
       </c>
       <c r="D930">
         <v>1</v>
@@ -23625,13 +23622,13 @@
     </row>
     <row r="931" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A931">
-        <v>310335</v>
+        <v>340904</v>
       </c>
       <c r="B931" t="s">
-        <v>1000</v>
+        <v>661</v>
       </c>
       <c r="C931" t="s">
-        <v>968</v>
+        <v>433</v>
       </c>
       <c r="D931">
         <v>1</v>
@@ -23645,13 +23642,13 @@
     </row>
     <row r="932" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A932">
-        <v>310340</v>
+        <v>340907</v>
       </c>
       <c r="B932" t="s">
-        <v>1001</v>
+        <v>662</v>
       </c>
       <c r="C932" t="s">
-        <v>968</v>
+        <v>433</v>
       </c>
       <c r="D932">
         <v>1</v>
@@ -23725,13 +23722,13 @@
     </row>
     <row r="936" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A936">
-        <v>310351</v>
+        <v>340913</v>
       </c>
       <c r="B936" t="s">
-        <v>1005</v>
+        <v>666</v>
       </c>
       <c r="C936" t="s">
-        <v>968</v>
+        <v>433</v>
       </c>
       <c r="D936">
         <v>1</v>
@@ -23745,13 +23742,13 @@
     </row>
     <row r="937" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A937">
-        <v>310352</v>
+        <v>340915</v>
       </c>
       <c r="B937" t="s">
-        <v>1006</v>
+        <v>668</v>
       </c>
       <c r="C937" t="s">
-        <v>968</v>
+        <v>433</v>
       </c>
       <c r="D937">
         <v>1</v>
@@ -23765,13 +23762,13 @@
     </row>
     <row r="938" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A938">
-        <v>310400</v>
+        <v>350110</v>
       </c>
       <c r="B938" t="s">
-        <v>1007</v>
+        <v>669</v>
       </c>
       <c r="C938" t="s">
-        <v>968</v>
+        <v>433</v>
       </c>
       <c r="D938">
         <v>1</v>
@@ -23785,13 +23782,13 @@
     </row>
     <row r="939" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A939">
-        <v>310900</v>
+        <v>999000</v>
       </c>
       <c r="B939" t="s">
-        <v>1008</v>
+        <v>746</v>
       </c>
       <c r="C939" t="s">
-        <v>968</v>
+        <v>433</v>
       </c>
       <c r="D939">
         <v>1</v>
@@ -23825,19 +23822,19 @@
     </row>
     <row r="941" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A941">
-        <v>340610</v>
+        <v>330119</v>
       </c>
       <c r="B941" t="s">
-        <v>1010</v>
+        <v>1338</v>
       </c>
       <c r="C941" t="s">
-        <v>968</v>
+        <v>433</v>
       </c>
       <c r="D941">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E941">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F941">
         <v>1</v>
@@ -23885,16 +23882,16 @@
     </row>
     <row r="944" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A944">
-        <v>340909</v>
+        <v>250210</v>
       </c>
       <c r="B944" t="s">
-        <v>1013</v>
+        <v>1360</v>
       </c>
       <c r="C944" t="s">
-        <v>968</v>
+        <v>433</v>
       </c>
       <c r="D944">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E944">
         <v>0</v>
@@ -23905,13 +23902,13 @@
     </row>
     <row r="945" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A945">
-        <v>590110</v>
+        <v>640130</v>
       </c>
       <c r="B945" t="s">
-        <v>1014</v>
+        <v>1077</v>
       </c>
       <c r="C945" t="s">
-        <v>968</v>
+        <v>1075</v>
       </c>
       <c r="D945">
         <v>1</v>
@@ -23965,13 +23962,13 @@
     </row>
     <row r="948" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A948">
-        <v>590210</v>
+        <v>640310</v>
       </c>
       <c r="B948" t="s">
-        <v>1017</v>
+        <v>1080</v>
       </c>
       <c r="C948" t="s">
-        <v>968</v>
+        <v>1075</v>
       </c>
       <c r="D948">
         <v>1</v>
@@ -24025,13 +24022,13 @@
     </row>
     <row r="951" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A951">
-        <v>590220</v>
+        <v>640410</v>
       </c>
       <c r="B951" t="s">
-        <v>1020</v>
+        <v>1081</v>
       </c>
       <c r="C951" t="s">
-        <v>968</v>
+        <v>1075</v>
       </c>
       <c r="D951">
         <v>1</v>
@@ -24045,13 +24042,13 @@
     </row>
     <row r="952" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A952">
-        <v>590230</v>
+        <v>640420</v>
       </c>
       <c r="B952" t="s">
-        <v>1021</v>
+        <v>1082</v>
       </c>
       <c r="C952" t="s">
-        <v>968</v>
+        <v>1075</v>
       </c>
       <c r="D952">
         <v>1</v>
@@ -24125,13 +24122,13 @@
     </row>
     <row r="956" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A956">
-        <v>620930</v>
+        <v>640430</v>
       </c>
       <c r="B956" t="s">
-        <v>1025</v>
+        <v>1083</v>
       </c>
       <c r="C956" t="s">
-        <v>968</v>
+        <v>1075</v>
       </c>
       <c r="D956">
         <v>1</v>
@@ -24145,13 +24142,13 @@
     </row>
     <row r="957" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A957">
-        <v>680904</v>
+        <v>650110</v>
       </c>
       <c r="B957" t="s">
-        <v>1026</v>
+        <v>1084</v>
       </c>
       <c r="C957" t="s">
-        <v>968</v>
+        <v>1075</v>
       </c>
       <c r="D957">
         <v>1</v>
@@ -24185,13 +24182,13 @@
     </row>
     <row r="959" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A959">
-        <v>690111</v>
+        <v>650210</v>
       </c>
       <c r="B959" t="s">
-        <v>1028</v>
+        <v>1085</v>
       </c>
       <c r="C959" t="s">
-        <v>968</v>
+        <v>1075</v>
       </c>
       <c r="D959">
         <v>1</v>
@@ -24245,19 +24242,19 @@
     </row>
     <row r="962" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A962">
-        <v>690114</v>
+        <v>640119</v>
       </c>
       <c r="B962" t="s">
-        <v>1031</v>
+        <v>1352</v>
       </c>
       <c r="C962" t="s">
-        <v>968</v>
+        <v>1075</v>
       </c>
       <c r="D962">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E962">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F962">
         <v>1</v>
@@ -24285,19 +24282,19 @@
     </row>
     <row r="964" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A964">
-        <v>690116</v>
+        <v>640219</v>
       </c>
       <c r="B964" t="s">
-        <v>1033</v>
+        <v>1353</v>
       </c>
       <c r="C964" t="s">
-        <v>968</v>
+        <v>1075</v>
       </c>
       <c r="D964">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E964">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F964">
         <v>1</v>
@@ -24305,13 +24302,13 @@
     </row>
     <row r="965" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A965">
-        <v>690117</v>
+        <v>540000</v>
       </c>
       <c r="B965" t="s">
-        <v>1034</v>
+        <v>1045</v>
       </c>
       <c r="C965" t="s">
-        <v>968</v>
+        <v>1046</v>
       </c>
       <c r="D965">
         <v>1</v>
@@ -24325,13 +24322,13 @@
     </row>
     <row r="966" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A966">
-        <v>690118</v>
+        <v>550110</v>
       </c>
       <c r="B966" t="s">
-        <v>1035</v>
+        <v>1047</v>
       </c>
       <c r="C966" t="s">
-        <v>968</v>
+        <v>1046</v>
       </c>
       <c r="D966">
         <v>1</v>
@@ -24345,13 +24342,13 @@
     </row>
     <row r="967" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A967">
-        <v>690119</v>
+        <v>550210</v>
       </c>
       <c r="B967" t="s">
-        <v>1036</v>
+        <v>1048</v>
       </c>
       <c r="C967" t="s">
-        <v>968</v>
+        <v>1046</v>
       </c>
       <c r="D967">
         <v>1</v>
@@ -24365,13 +24362,13 @@
     </row>
     <row r="968" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A968">
-        <v>690120</v>
+        <v>550310</v>
       </c>
       <c r="B968" t="s">
-        <v>1037</v>
+        <v>1049</v>
       </c>
       <c r="C968" t="s">
-        <v>968</v>
+        <v>1046</v>
       </c>
       <c r="D968">
         <v>1</v>
@@ -24525,10 +24522,10 @@
     </row>
     <row r="976" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A976">
-        <v>540000</v>
+        <v>550320</v>
       </c>
       <c r="B976" t="s">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="C976" t="s">
         <v>1046</v>
@@ -24545,10 +24542,10 @@
     </row>
     <row r="977" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A977">
-        <v>550110</v>
+        <v>550330</v>
       </c>
       <c r="B977" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="C977" t="s">
         <v>1046</v>
@@ -24565,10 +24562,10 @@
     </row>
     <row r="978" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A978">
-        <v>550210</v>
+        <v>550340</v>
       </c>
       <c r="B978" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="C978" t="s">
         <v>1046</v>
@@ -24585,10 +24582,10 @@
     </row>
     <row r="979" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A979">
-        <v>550310</v>
+        <v>560110</v>
       </c>
       <c r="B979" t="s">
-        <v>1049</v>
+        <v>1055</v>
       </c>
       <c r="C979" t="s">
         <v>1046</v>
@@ -24605,10 +24602,10 @@
     </row>
     <row r="980" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A980">
-        <v>550320</v>
+        <v>560210</v>
       </c>
       <c r="B980" t="s">
-        <v>1050</v>
+        <v>1056</v>
       </c>
       <c r="C980" t="s">
         <v>1046</v>
@@ -24625,10 +24622,10 @@
     </row>
     <row r="981" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A981">
-        <v>550330</v>
+        <v>560310</v>
       </c>
       <c r="B981" t="s">
-        <v>1051</v>
+        <v>1057</v>
       </c>
       <c r="C981" t="s">
         <v>1046</v>
@@ -24645,10 +24642,10 @@
     </row>
     <row r="982" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A982">
-        <v>550340</v>
+        <v>560330</v>
       </c>
       <c r="B982" t="s">
-        <v>1052</v>
+        <v>1059</v>
       </c>
       <c r="C982" t="s">
         <v>1046</v>
@@ -24705,10 +24702,10 @@
     </row>
     <row r="985" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A985">
-        <v>560110</v>
+        <v>560400</v>
       </c>
       <c r="B985" t="s">
-        <v>1055</v>
+        <v>1060</v>
       </c>
       <c r="C985" t="s">
         <v>1046</v>
@@ -24725,10 +24722,10 @@
     </row>
     <row r="986" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A986">
-        <v>560210</v>
+        <v>570000</v>
       </c>
       <c r="B986" t="s">
-        <v>1056</v>
+        <v>1064</v>
       </c>
       <c r="C986" t="s">
         <v>1046</v>
@@ -24745,10 +24742,10 @@
     </row>
     <row r="987" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A987">
-        <v>560310</v>
+        <v>570220</v>
       </c>
       <c r="B987" t="s">
-        <v>1057</v>
+        <v>1068</v>
       </c>
       <c r="C987" t="s">
         <v>1046</v>
@@ -24785,10 +24782,10 @@
     </row>
     <row r="989" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A989">
-        <v>560330</v>
+        <v>570230</v>
       </c>
       <c r="B989" t="s">
-        <v>1059</v>
+        <v>1069</v>
       </c>
       <c r="C989" t="s">
         <v>1046</v>
@@ -24805,10 +24802,10 @@
     </row>
     <row r="990" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A990">
-        <v>560400</v>
+        <v>570901</v>
       </c>
       <c r="B990" t="s">
-        <v>1060</v>
+        <v>1071</v>
       </c>
       <c r="C990" t="s">
         <v>1046</v>
@@ -24885,10 +24882,10 @@
     </row>
     <row r="994" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A994">
-        <v>570000</v>
+        <v>570902</v>
       </c>
       <c r="B994" t="s">
-        <v>1064</v>
+        <v>1072</v>
       </c>
       <c r="C994" t="s">
         <v>1046</v>
@@ -24965,19 +24962,19 @@
     </row>
     <row r="998" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A998">
-        <v>570220</v>
+        <v>550219</v>
       </c>
       <c r="B998" t="s">
-        <v>1068</v>
+        <v>1349</v>
       </c>
       <c r="C998" t="s">
         <v>1046</v>
       </c>
       <c r="D998">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E998">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F998">
         <v>1</v>
@@ -24985,13 +24982,13 @@
     </row>
     <row r="999" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A999">
-        <v>570230</v>
+        <v>460902</v>
       </c>
       <c r="B999" t="s">
-        <v>1069</v>
+        <v>77</v>
       </c>
       <c r="C999" t="s">
-        <v>1046</v>
+        <v>1363</v>
       </c>
       <c r="D999">
         <v>1</v>
@@ -25025,13 +25022,13 @@
     </row>
     <row r="1001" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1001">
-        <v>570901</v>
+        <v>520902</v>
       </c>
       <c r="B1001" t="s">
-        <v>1071</v>
+        <v>146</v>
       </c>
       <c r="C1001" t="s">
-        <v>1046</v>
+        <v>1363</v>
       </c>
       <c r="D1001">
         <v>1</v>
@@ -25045,13 +25042,13 @@
     </row>
     <row r="1002" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1002">
-        <v>570902</v>
+        <v>520904</v>
       </c>
       <c r="B1002" t="s">
-        <v>1072</v>
+        <v>148</v>
       </c>
       <c r="C1002" t="s">
-        <v>1046</v>
+        <v>1122</v>
       </c>
       <c r="D1002">
         <v>1</v>
@@ -25124,14 +25121,14 @@
       </c>
     </row>
     <row r="1006" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1006">
-        <v>640130</v>
+      <c r="A1006" s="1" t="s">
+        <v>1120</v>
       </c>
       <c r="B1006" t="s">
-        <v>1077</v>
+        <v>1121</v>
       </c>
       <c r="C1006" t="s">
-        <v>1075</v>
+        <v>1122</v>
       </c>
       <c r="D1006">
         <v>1</v>
@@ -25184,14 +25181,14 @@
       </c>
     </row>
     <row r="1009" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1009">
-        <v>640310</v>
+      <c r="A1009" s="1" t="s">
+        <v>1125</v>
       </c>
       <c r="B1009" t="s">
-        <v>1080</v>
+        <v>1126</v>
       </c>
       <c r="C1009" t="s">
-        <v>1075</v>
+        <v>1122</v>
       </c>
       <c r="D1009">
         <v>1</v>
@@ -25204,14 +25201,14 @@
       </c>
     </row>
     <row r="1010" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1010">
-        <v>640410</v>
+      <c r="A1010" s="1" t="s">
+        <v>1127</v>
       </c>
       <c r="B1010" t="s">
-        <v>1081</v>
+        <v>1128</v>
       </c>
       <c r="C1010" t="s">
-        <v>1075</v>
+        <v>1122</v>
       </c>
       <c r="D1010">
         <v>1</v>
@@ -25224,14 +25221,14 @@
       </c>
     </row>
     <row r="1011" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1011">
-        <v>640420</v>
+      <c r="A1011" s="1" t="s">
+        <v>1133</v>
       </c>
       <c r="B1011" t="s">
-        <v>1082</v>
+        <v>1134</v>
       </c>
       <c r="C1011" t="s">
-        <v>1075</v>
+        <v>1122</v>
       </c>
       <c r="D1011">
         <v>1</v>
@@ -25244,14 +25241,14 @@
       </c>
     </row>
     <row r="1012" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1012">
-        <v>640430</v>
+      <c r="A1012" s="1" t="s">
+        <v>1135</v>
       </c>
       <c r="B1012" t="s">
-        <v>1083</v>
+        <v>1136</v>
       </c>
       <c r="C1012" t="s">
-        <v>1075</v>
+        <v>1122</v>
       </c>
       <c r="D1012">
         <v>1</v>
@@ -25264,14 +25261,14 @@
       </c>
     </row>
     <row r="1013" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1013">
-        <v>650110</v>
+      <c r="A1013" s="1" t="s">
+        <v>1143</v>
       </c>
       <c r="B1013" t="s">
-        <v>1084</v>
+        <v>1144</v>
       </c>
       <c r="C1013" t="s">
-        <v>1075</v>
+        <v>1122</v>
       </c>
       <c r="D1013">
         <v>1</v>
@@ -25284,14 +25281,14 @@
       </c>
     </row>
     <row r="1014" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1014">
-        <v>650210</v>
+      <c r="A1014" s="1" t="s">
+        <v>1147</v>
       </c>
       <c r="B1014" t="s">
-        <v>1085</v>
+        <v>1148</v>
       </c>
       <c r="C1014" t="s">
-        <v>1075</v>
+        <v>1122</v>
       </c>
       <c r="D1014">
         <v>1</v>
@@ -25344,14 +25341,14 @@
       </c>
     </row>
     <row r="1017" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1017">
-        <v>660000</v>
+      <c r="A1017" s="1" t="s">
+        <v>1153</v>
       </c>
       <c r="B1017" t="s">
-        <v>1088</v>
+        <v>1154</v>
       </c>
       <c r="C1017" t="s">
-        <v>1089</v>
+        <v>1122</v>
       </c>
       <c r="D1017">
         <v>1</v>
@@ -25364,14 +25361,14 @@
       </c>
     </row>
     <row r="1018" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1018">
-        <v>660001</v>
+      <c r="A1018" s="1" t="s">
+        <v>1155</v>
       </c>
       <c r="B1018" t="s">
-        <v>1090</v>
+        <v>1156</v>
       </c>
       <c r="C1018" t="s">
-        <v>1089</v>
+        <v>1122</v>
       </c>
       <c r="D1018">
         <v>1</v>
@@ -25464,14 +25461,14 @@
       </c>
     </row>
     <row r="1023" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1023">
-        <v>660900</v>
+      <c r="A1023" s="1" t="s">
+        <v>1157</v>
       </c>
       <c r="B1023" t="s">
-        <v>1095</v>
+        <v>1158</v>
       </c>
       <c r="C1023" t="s">
-        <v>1089</v>
+        <v>1122</v>
       </c>
       <c r="D1023">
         <v>1</v>
@@ -25525,13 +25522,13 @@
     </row>
     <row r="1026" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1026">
-        <v>670110</v>
+        <v>210210</v>
       </c>
       <c r="B1026" t="s">
-        <v>1098</v>
+        <v>1207</v>
       </c>
       <c r="C1026" t="s">
-        <v>1089</v>
+        <v>1122</v>
       </c>
       <c r="D1026">
         <v>1</v>
@@ -25545,13 +25542,13 @@
     </row>
     <row r="1027" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1027">
-        <v>670210</v>
+        <v>320232</v>
       </c>
       <c r="B1027" t="s">
-        <v>1099</v>
+        <v>1208</v>
       </c>
       <c r="C1027" t="s">
-        <v>1089</v>
+        <v>1122</v>
       </c>
       <c r="D1027">
         <v>1</v>
@@ -25565,13 +25562,13 @@
     </row>
     <row r="1028" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1028">
-        <v>670410</v>
+        <v>340110</v>
       </c>
       <c r="B1028" t="s">
-        <v>1100</v>
+        <v>1210</v>
       </c>
       <c r="C1028" t="s">
-        <v>1101</v>
+        <v>1122</v>
       </c>
       <c r="D1028">
         <v>1</v>
@@ -25625,13 +25622,13 @@
     </row>
     <row r="1031" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1031">
-        <v>670903</v>
+        <v>340120</v>
       </c>
       <c r="B1031" t="s">
-        <v>1104</v>
+        <v>1211</v>
       </c>
       <c r="C1031" t="s">
-        <v>1101</v>
+        <v>1122</v>
       </c>
       <c r="D1031">
         <v>1</v>
@@ -25924,11 +25921,11 @@
       </c>
     </row>
     <row r="1046" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1046" s="1" t="s">
-        <v>1120</v>
+      <c r="A1046">
+        <v>420115</v>
       </c>
       <c r="B1046" t="s">
-        <v>1121</v>
+        <v>1212</v>
       </c>
       <c r="C1046" t="s">
         <v>1122</v>
@@ -25964,11 +25961,11 @@
       </c>
     </row>
     <row r="1048" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1048" s="1" t="s">
-        <v>1125</v>
+      <c r="A1048">
+        <v>430130</v>
       </c>
       <c r="B1048" t="s">
-        <v>1126</v>
+        <v>1214</v>
       </c>
       <c r="C1048" t="s">
         <v>1122</v>
@@ -25984,11 +25981,11 @@
       </c>
     </row>
     <row r="1049" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1049" s="1" t="s">
-        <v>1127</v>
+      <c r="A1049">
+        <v>610140</v>
       </c>
       <c r="B1049" t="s">
-        <v>1128</v>
+        <v>1215</v>
       </c>
       <c r="C1049" t="s">
         <v>1122</v>
@@ -26044,11 +26041,11 @@
       </c>
     </row>
     <row r="1052" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1052" s="1" t="s">
-        <v>1133</v>
+      <c r="A1052">
+        <v>610210</v>
       </c>
       <c r="B1052" t="s">
-        <v>1134</v>
+        <v>1216</v>
       </c>
       <c r="C1052" t="s">
         <v>1122</v>
@@ -26064,11 +26061,11 @@
       </c>
     </row>
     <row r="1053" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1053" s="1" t="s">
-        <v>1135</v>
+      <c r="A1053">
+        <v>610220</v>
       </c>
       <c r="B1053" t="s">
-        <v>1136</v>
+        <v>1217</v>
       </c>
       <c r="C1053" t="s">
         <v>1122</v>
@@ -26144,11 +26141,11 @@
       </c>
     </row>
     <row r="1057" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1057" s="1" t="s">
-        <v>1143</v>
+      <c r="A1057">
+        <v>610230</v>
       </c>
       <c r="B1057" t="s">
-        <v>1144</v>
+        <v>1218</v>
       </c>
       <c r="C1057" t="s">
         <v>1122</v>
@@ -26184,11 +26181,11 @@
       </c>
     </row>
     <row r="1059" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1059" s="1" t="s">
-        <v>1147</v>
+      <c r="A1059">
+        <v>620912</v>
       </c>
       <c r="B1059" t="s">
-        <v>1148</v>
+        <v>1219</v>
       </c>
       <c r="C1059" t="s">
         <v>1122</v>
@@ -26244,11 +26241,11 @@
       </c>
     </row>
     <row r="1062" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1062" s="1" t="s">
-        <v>1153</v>
+      <c r="A1062">
+        <v>620913</v>
       </c>
       <c r="B1062" t="s">
-        <v>1154</v>
+        <v>1220</v>
       </c>
       <c r="C1062" t="s">
         <v>1122</v>
@@ -26264,11 +26261,11 @@
       </c>
     </row>
     <row r="1063" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1063" s="1" t="s">
-        <v>1155</v>
+      <c r="A1063">
+        <v>620918</v>
       </c>
       <c r="B1063" t="s">
-        <v>1156</v>
+        <v>1223</v>
       </c>
       <c r="C1063" t="s">
         <v>1122</v>
@@ -26284,11 +26281,11 @@
       </c>
     </row>
     <row r="1064" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1064" s="1" t="s">
-        <v>1157</v>
+      <c r="A1064">
+        <v>620926</v>
       </c>
       <c r="B1064" t="s">
-        <v>1158</v>
+        <v>1224</v>
       </c>
       <c r="C1064" t="s">
         <v>1122</v>
@@ -26785,10 +26782,10 @@
     </row>
     <row r="1089" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1089">
-        <v>210210</v>
+        <v>630110</v>
       </c>
       <c r="B1089" t="s">
-        <v>1207</v>
+        <v>1225</v>
       </c>
       <c r="C1089" t="s">
         <v>1122</v>
@@ -26805,10 +26802,10 @@
     </row>
     <row r="1090" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1090">
-        <v>320232</v>
+        <v>630210</v>
       </c>
       <c r="B1090" t="s">
-        <v>1208</v>
+        <v>1226</v>
       </c>
       <c r="C1090" t="s">
         <v>1122</v>
@@ -26845,10 +26842,10 @@
     </row>
     <row r="1092" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1092">
-        <v>340110</v>
+        <v>630220</v>
       </c>
       <c r="B1092" t="s">
-        <v>1210</v>
+        <v>1227</v>
       </c>
       <c r="C1092" t="s">
         <v>1122</v>
@@ -26865,10 +26862,10 @@
     </row>
     <row r="1093" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1093">
-        <v>340120</v>
+        <v>630900</v>
       </c>
       <c r="B1093" t="s">
-        <v>1211</v>
+        <v>1228</v>
       </c>
       <c r="C1093" t="s">
         <v>1122</v>
@@ -26885,10 +26882,10 @@
     </row>
     <row r="1094" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1094">
-        <v>420115</v>
+        <v>680110</v>
       </c>
       <c r="B1094" t="s">
-        <v>1212</v>
+        <v>1229</v>
       </c>
       <c r="C1094" t="s">
         <v>1122</v>
@@ -26925,10 +26922,10 @@
     </row>
     <row r="1096" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1096">
-        <v>430130</v>
+        <v>680140</v>
       </c>
       <c r="B1096" t="s">
-        <v>1214</v>
+        <v>1230</v>
       </c>
       <c r="C1096" t="s">
         <v>1122</v>
@@ -26945,10 +26942,10 @@
     </row>
     <row r="1097" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1097">
-        <v>610140</v>
+        <v>680210</v>
       </c>
       <c r="B1097" t="s">
-        <v>1215</v>
+        <v>1231</v>
       </c>
       <c r="C1097" t="s">
         <v>1122</v>
@@ -26965,10 +26962,10 @@
     </row>
     <row r="1098" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1098">
-        <v>610210</v>
+        <v>680220</v>
       </c>
       <c r="B1098" t="s">
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="C1098" t="s">
         <v>1122</v>
@@ -26985,10 +26982,10 @@
     </row>
     <row r="1099" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1099">
-        <v>610220</v>
+        <v>680901</v>
       </c>
       <c r="B1099" t="s">
-        <v>1217</v>
+        <v>1233</v>
       </c>
       <c r="C1099" t="s">
         <v>1122</v>
@@ -27005,10 +27002,10 @@
     </row>
     <row r="1100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1100">
-        <v>610230</v>
+        <v>680902</v>
       </c>
       <c r="B1100" t="s">
-        <v>1218</v>
+        <v>1234</v>
       </c>
       <c r="C1100" t="s">
         <v>1122</v>
@@ -27025,10 +27022,10 @@
     </row>
     <row r="1101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1101">
-        <v>620912</v>
+        <v>680903</v>
       </c>
       <c r="B1101" t="s">
-        <v>1219</v>
+        <v>1235</v>
       </c>
       <c r="C1101" t="s">
         <v>1122</v>
@@ -27045,10 +27042,10 @@
     </row>
     <row r="1102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1102">
-        <v>620913</v>
+        <v>690230</v>
       </c>
       <c r="B1102" t="s">
-        <v>1220</v>
+        <v>1236</v>
       </c>
       <c r="C1102" t="s">
         <v>1122</v>
@@ -27105,10 +27102,10 @@
     </row>
     <row r="1105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1105">
-        <v>620918</v>
+        <v>999900</v>
       </c>
       <c r="B1105" t="s">
-        <v>1223</v>
+        <v>1324</v>
       </c>
       <c r="C1105" t="s">
         <v>1122</v>
@@ -27125,13 +27122,13 @@
     </row>
     <row r="1106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1106">
-        <v>620926</v>
+        <v>600110</v>
       </c>
       <c r="B1106" t="s">
-        <v>1224</v>
+        <v>844</v>
       </c>
       <c r="C1106" t="s">
-        <v>1122</v>
+        <v>845</v>
       </c>
       <c r="D1106">
         <v>1</v>
@@ -27145,13 +27142,13 @@
     </row>
     <row r="1107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1107">
-        <v>630110</v>
+        <v>600120</v>
       </c>
       <c r="B1107" t="s">
-        <v>1225</v>
+        <v>846</v>
       </c>
       <c r="C1107" t="s">
-        <v>1122</v>
+        <v>845</v>
       </c>
       <c r="D1107">
         <v>1</v>
@@ -27165,13 +27162,13 @@
     </row>
     <row r="1108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1108">
-        <v>630210</v>
+        <v>600130</v>
       </c>
       <c r="B1108" t="s">
-        <v>1226</v>
+        <v>851</v>
       </c>
       <c r="C1108" t="s">
-        <v>1122</v>
+        <v>845</v>
       </c>
       <c r="D1108">
         <v>1</v>
@@ -27185,13 +27182,13 @@
     </row>
     <row r="1109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1109">
-        <v>630220</v>
+        <v>600210</v>
       </c>
       <c r="B1109" t="s">
-        <v>1227</v>
+        <v>860</v>
       </c>
       <c r="C1109" t="s">
-        <v>1122</v>
+        <v>845</v>
       </c>
       <c r="D1109">
         <v>1</v>
@@ -27205,13 +27202,13 @@
     </row>
     <row r="1110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1110">
-        <v>630900</v>
+        <v>600410</v>
       </c>
       <c r="B1110" t="s">
-        <v>1228</v>
+        <v>861</v>
       </c>
       <c r="C1110" t="s">
-        <v>1122</v>
+        <v>845</v>
       </c>
       <c r="D1110">
         <v>1</v>
@@ -27225,13 +27222,13 @@
     </row>
     <row r="1111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1111">
-        <v>680110</v>
+        <v>600420</v>
       </c>
       <c r="B1111" t="s">
-        <v>1229</v>
+        <v>862</v>
       </c>
       <c r="C1111" t="s">
-        <v>1122</v>
+        <v>845</v>
       </c>
       <c r="D1111">
         <v>1</v>
@@ -27245,13 +27242,13 @@
     </row>
     <row r="1112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1112">
-        <v>680140</v>
+        <v>600430</v>
       </c>
       <c r="B1112" t="s">
-        <v>1230</v>
+        <v>863</v>
       </c>
       <c r="C1112" t="s">
-        <v>1122</v>
+        <v>845</v>
       </c>
       <c r="D1112">
         <v>1</v>
@@ -27265,13 +27262,13 @@
     </row>
     <row r="1113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1113">
-        <v>680210</v>
+        <v>600900</v>
       </c>
       <c r="B1113" t="s">
-        <v>1231</v>
+        <v>864</v>
       </c>
       <c r="C1113" t="s">
-        <v>1122</v>
+        <v>845</v>
       </c>
       <c r="D1113">
         <v>1</v>
@@ -27285,13 +27282,13 @@
     </row>
     <row r="1114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1114">
-        <v>680220</v>
+        <v>600903</v>
       </c>
       <c r="B1114" t="s">
-        <v>1232</v>
+        <v>867</v>
       </c>
       <c r="C1114" t="s">
-        <v>1122</v>
+        <v>845</v>
       </c>
       <c r="D1114">
         <v>1</v>
@@ -27305,13 +27302,13 @@
     </row>
     <row r="1115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1115">
-        <v>680901</v>
+        <v>610110</v>
       </c>
       <c r="B1115" t="s">
-        <v>1233</v>
+        <v>868</v>
       </c>
       <c r="C1115" t="s">
-        <v>1122</v>
+        <v>845</v>
       </c>
       <c r="D1115">
         <v>1</v>
@@ -27325,13 +27322,13 @@
     </row>
     <row r="1116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1116">
-        <v>680902</v>
+        <v>610120</v>
       </c>
       <c r="B1116" t="s">
-        <v>1234</v>
+        <v>869</v>
       </c>
       <c r="C1116" t="s">
-        <v>1122</v>
+        <v>845</v>
       </c>
       <c r="D1116">
         <v>1</v>
@@ -27345,13 +27342,13 @@
     </row>
     <row r="1117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1117">
-        <v>680903</v>
+        <v>610130</v>
       </c>
       <c r="B1117" t="s">
-        <v>1235</v>
+        <v>870</v>
       </c>
       <c r="C1117" t="s">
-        <v>1122</v>
+        <v>845</v>
       </c>
       <c r="D1117">
         <v>1</v>
@@ -27365,13 +27362,13 @@
     </row>
     <row r="1118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1118">
-        <v>690230</v>
+        <v>610901</v>
       </c>
       <c r="B1118" t="s">
-        <v>1236</v>
+        <v>872</v>
       </c>
       <c r="C1118" t="s">
-        <v>1122</v>
+        <v>845</v>
       </c>
       <c r="D1118">
         <v>1</v>
@@ -29125,13 +29122,13 @@
     </row>
     <row r="1206" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1206">
-        <v>999900</v>
+        <v>610902</v>
       </c>
       <c r="B1206" t="s">
-        <v>1324</v>
+        <v>873</v>
       </c>
       <c r="C1206" t="s">
-        <v>1122</v>
+        <v>845</v>
       </c>
       <c r="D1206">
         <v>1</v>
@@ -29164,60 +29161,60 @@
       </c>
     </row>
     <row r="1208" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1208" s="1" t="s">
-        <v>1326</v>
+      <c r="A1208">
+        <v>610903</v>
       </c>
       <c r="B1208" t="s">
-        <v>1327</v>
+        <v>874</v>
       </c>
       <c r="C1208" t="s">
-        <v>200</v>
+        <v>845</v>
       </c>
       <c r="D1208">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1208">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1208">
         <v>1</v>
       </c>
     </row>
     <row r="1209" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1209" s="1" t="s">
-        <v>1328</v>
+      <c r="A1209">
+        <v>620111</v>
       </c>
       <c r="B1209" t="s">
-        <v>1329</v>
+        <v>876</v>
       </c>
       <c r="C1209" t="s">
-        <v>200</v>
+        <v>845</v>
       </c>
       <c r="D1209">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1209">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1209">
         <v>1</v>
       </c>
     </row>
     <row r="1210" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1210" s="1" t="s">
-        <v>1330</v>
+      <c r="A1210">
+        <v>620121</v>
       </c>
       <c r="B1210" t="s">
-        <v>1331</v>
+        <v>877</v>
       </c>
       <c r="C1210" t="s">
-        <v>200</v>
+        <v>845</v>
       </c>
       <c r="D1210">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1210">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1210">
         <v>1</v>
@@ -29225,19 +29222,19 @@
     </row>
     <row r="1211" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1211">
-        <v>100519</v>
+        <v>620213</v>
       </c>
       <c r="B1211" t="s">
-        <v>1332</v>
+        <v>881</v>
       </c>
       <c r="C1211" t="s">
-        <v>200</v>
+        <v>845</v>
       </c>
       <c r="D1211">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1211">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1211">
         <v>1</v>
@@ -29245,19 +29242,19 @@
     </row>
     <row r="1212" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1212">
-        <v>140219</v>
+        <v>620214</v>
       </c>
       <c r="B1212" t="s">
-        <v>1333</v>
+        <v>882</v>
       </c>
       <c r="C1212" t="s">
-        <v>200</v>
+        <v>845</v>
       </c>
       <c r="D1212">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1212">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1212">
         <v>1</v>
@@ -29265,19 +29262,19 @@
     </row>
     <row r="1213" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1213">
-        <v>140349</v>
+        <v>620221</v>
       </c>
       <c r="B1213" t="s">
-        <v>1334</v>
+        <v>885</v>
       </c>
       <c r="C1213" t="s">
-        <v>200</v>
+        <v>845</v>
       </c>
       <c r="D1213">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1213">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1213">
         <v>1</v>
@@ -29285,19 +29282,19 @@
     </row>
     <row r="1214" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1214">
-        <v>170319</v>
+        <v>620310</v>
       </c>
       <c r="B1214" t="s">
-        <v>1335</v>
+        <v>887</v>
       </c>
       <c r="C1214" t="s">
-        <v>200</v>
+        <v>845</v>
       </c>
       <c r="D1214">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1214">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1214">
         <v>1</v>
@@ -29305,19 +29302,19 @@
     </row>
     <row r="1215" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1215">
-        <v>200119</v>
+        <v>620320</v>
       </c>
       <c r="B1215" t="s">
-        <v>1336</v>
+        <v>888</v>
       </c>
       <c r="C1215" t="s">
-        <v>939</v>
+        <v>845</v>
       </c>
       <c r="D1215">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1215">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1215">
         <v>1</v>
@@ -29326,19 +29323,19 @@
     </row>
     <row r="1216" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1216">
-        <v>200219</v>
+        <v>620330</v>
       </c>
       <c r="B1216" t="s">
-        <v>1337</v>
+        <v>889</v>
       </c>
       <c r="C1216" t="s">
-        <v>939</v>
+        <v>845</v>
       </c>
       <c r="D1216">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1216">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1216">
         <v>1</v>
@@ -29346,19 +29343,19 @@
     </row>
     <row r="1217" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1217">
-        <v>330119</v>
+        <v>620410</v>
       </c>
       <c r="B1217" t="s">
-        <v>1338</v>
+        <v>890</v>
       </c>
       <c r="C1217" t="s">
-        <v>433</v>
+        <v>845</v>
       </c>
       <c r="D1217">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1217">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1217">
         <v>1</v>
@@ -29366,19 +29363,19 @@
     </row>
     <row r="1218" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1218">
-        <v>360319</v>
+        <v>620420</v>
       </c>
       <c r="B1218" t="s">
-        <v>1339</v>
+        <v>891</v>
       </c>
       <c r="C1218" t="s">
-        <v>748</v>
+        <v>845</v>
       </c>
       <c r="D1218">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1218">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1218">
         <v>1</v>
@@ -29386,19 +29383,19 @@
     </row>
     <row r="1219" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1219">
-        <v>370219</v>
+        <v>620510</v>
       </c>
       <c r="B1219" t="s">
-        <v>1340</v>
+        <v>892</v>
       </c>
       <c r="C1219" t="s">
-        <v>748</v>
+        <v>845</v>
       </c>
       <c r="D1219">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1219">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1219">
         <v>1</v>
@@ -29406,19 +29403,19 @@
     </row>
     <row r="1220" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1220">
-        <v>370319</v>
+        <v>620610</v>
       </c>
       <c r="B1220" t="s">
-        <v>1341</v>
+        <v>893</v>
       </c>
       <c r="C1220" t="s">
-        <v>748</v>
+        <v>845</v>
       </c>
       <c r="D1220">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1220">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1220">
         <v>1</v>
@@ -29427,19 +29424,19 @@
     </row>
     <row r="1221" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1221">
-        <v>380319</v>
+        <v>620710</v>
       </c>
       <c r="B1221" t="s">
-        <v>1342</v>
+        <v>894</v>
       </c>
       <c r="C1221" t="s">
-        <v>748</v>
+        <v>845</v>
       </c>
       <c r="D1221">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1221">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1221">
         <v>1</v>
@@ -29448,19 +29445,19 @@
     </row>
     <row r="1222" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1222">
-        <v>380339</v>
+        <v>620810</v>
       </c>
       <c r="B1222" t="s">
-        <v>1343</v>
+        <v>895</v>
       </c>
       <c r="C1222" t="s">
-        <v>748</v>
+        <v>845</v>
       </c>
       <c r="D1222">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1222">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1222">
         <v>1</v>
@@ -29469,19 +29466,19 @@
     </row>
     <row r="1223" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1223">
-        <v>380429</v>
+        <v>620915</v>
       </c>
       <c r="B1223" t="s">
-        <v>1344</v>
+        <v>905</v>
       </c>
       <c r="C1223" t="s">
-        <v>748</v>
+        <v>845</v>
       </c>
       <c r="D1223">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1223">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1223">
         <v>1</v>
@@ -29490,19 +29487,19 @@
     </row>
     <row r="1224" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1224">
-        <v>380909</v>
+        <v>620925</v>
       </c>
       <c r="B1224" t="s">
-        <v>1345</v>
+        <v>909</v>
       </c>
       <c r="C1224" t="s">
-        <v>748</v>
+        <v>845</v>
       </c>
       <c r="D1224">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1224">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1224">
         <v>1</v>
@@ -29511,19 +29508,19 @@
     </row>
     <row r="1225" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1225">
-        <v>390319</v>
+        <v>660000</v>
       </c>
       <c r="B1225" t="s">
-        <v>1346</v>
+        <v>1088</v>
       </c>
       <c r="C1225" t="s">
-        <v>748</v>
+        <v>1089</v>
       </c>
       <c r="D1225">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1225">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1225">
         <v>1</v>
@@ -29532,19 +29529,19 @@
     </row>
     <row r="1226" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1226">
-        <v>410119</v>
+        <v>660001</v>
       </c>
       <c r="B1226" t="s">
-        <v>1347</v>
+        <v>1090</v>
       </c>
       <c r="C1226" t="s">
-        <v>748</v>
+        <v>1089</v>
       </c>
       <c r="D1226">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1226">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1226">
         <v>1</v>
@@ -29553,19 +29550,19 @@
     </row>
     <row r="1227" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1227">
-        <v>490100</v>
+        <v>660900</v>
       </c>
       <c r="B1227" t="s">
-        <v>1348</v>
+        <v>1095</v>
       </c>
       <c r="C1227" t="s">
-        <v>1364</v>
+        <v>1089</v>
       </c>
       <c r="D1227">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1227">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1227">
         <v>1</v>
@@ -29574,19 +29571,19 @@
     </row>
     <row r="1228" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1228">
-        <v>550219</v>
+        <v>670110</v>
       </c>
       <c r="B1228" t="s">
-        <v>1349</v>
+        <v>1098</v>
       </c>
       <c r="C1228" t="s">
-        <v>1046</v>
+        <v>1089</v>
       </c>
       <c r="D1228">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1228">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1228">
         <v>1</v>
@@ -29595,19 +29592,19 @@
     </row>
     <row r="1229" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1229">
-        <v>600315</v>
+        <v>670210</v>
       </c>
       <c r="B1229" t="s">
-        <v>1350</v>
+        <v>1099</v>
       </c>
       <c r="C1229" t="s">
-        <v>1359</v>
+        <v>1089</v>
       </c>
       <c r="D1229">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1229">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1229">
         <v>1</v>
@@ -29616,19 +29613,19 @@
     </row>
     <row r="1230" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1230">
-        <v>600311</v>
+        <v>530901</v>
       </c>
       <c r="B1230" t="s">
-        <v>1351</v>
+        <v>155</v>
       </c>
       <c r="C1230" t="s">
-        <v>1359</v>
+        <v>1367</v>
       </c>
       <c r="D1230">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1230">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1230">
         <v>1</v>
@@ -29637,19 +29634,19 @@
     </row>
     <row r="1231" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1231">
-        <v>640119</v>
+        <v>530412</v>
       </c>
       <c r="B1231" t="s">
-        <v>1352</v>
+        <v>154</v>
       </c>
       <c r="C1231" t="s">
-        <v>1075</v>
+        <v>1356</v>
       </c>
       <c r="D1231">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1231">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1231">
         <v>1</v>
@@ -29658,19 +29655,19 @@
     </row>
     <row r="1232" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1232">
-        <v>640219</v>
+        <v>530311</v>
       </c>
       <c r="B1232" t="s">
-        <v>1353</v>
+        <v>196</v>
       </c>
       <c r="C1232" t="s">
-        <v>1075</v>
+        <v>1358</v>
       </c>
       <c r="D1232">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1232">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1232">
         <v>1</v>
@@ -29679,16 +29676,16 @@
     </row>
     <row r="1233" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1233">
-        <v>250210</v>
+        <v>530510</v>
       </c>
       <c r="B1233" t="s">
-        <v>1360</v>
+        <v>198</v>
       </c>
       <c r="C1233" t="s">
-        <v>433</v>
+        <v>1358</v>
       </c>
       <c r="D1233">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1233">
         <v>0</v>
@@ -29714,7 +29711,11 @@
       <c r="K1239" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1233" xr:uid="{16315887-E99C-F647-BC9F-F16988AC1201}"/>
+  <autoFilter ref="A1:F1233" xr:uid="{16315887-E99C-F647-BC9F-F16988AC1201}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F1233">
+      <sortCondition ref="C1:C1233"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/data_prep_input/ucc_categories.xlsx
+++ b/data/data_prep_input/ucc_categories.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamrynmansfield/College/UTK/Papers/transpo_budget_ces/data/data_prep_input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A8EDCDF-EDD6-B045-8993-F38D9073D36E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC42BDB-6A05-DF43-89D2-F6470134C76E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38400" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{7A9D0787-2D4A-AE43-A29D-439136587B88}"/>
+    <workbookView xWindow="-1300" yWindow="-17400" windowWidth="32000" windowHeight="17400" xr2:uid="{7A9D0787-2D4A-AE43-A29D-439136587B88}"/>
   </bookViews>
   <sheets>
     <sheet name="ucc_categories_current" sheetId="1" r:id="rId1"/>
@@ -4108,18 +4108,6 @@
     <t>Car Travel</t>
   </si>
   <si>
-    <t>Taxi or Limo Travel</t>
-  </si>
-  <si>
-    <t>Bus Travel</t>
-  </si>
-  <si>
-    <t>Train Travel</t>
-  </si>
-  <si>
-    <t>Bike or Scooter or other Single Rider Travel</t>
-  </si>
-  <si>
     <t>Gas, btld/tank</t>
   </si>
   <si>
@@ -4163,6 +4151,18 @@
   </si>
   <si>
     <t>School</t>
+  </si>
+  <si>
+    <t>Ridesharing</t>
+  </si>
+  <si>
+    <t>Public Transit (Bus)</t>
+  </si>
+  <si>
+    <t>Public Transit (Rail)</t>
+  </si>
+  <si>
+    <t>Microtransit</t>
   </si>
 </sst>
 </file>
@@ -5054,7 +5054,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>1372</v>
+        <v>1368</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -5066,7 +5066,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>520901</v>
       </c>
@@ -5077,7 +5077,7 @@
         <v>1354</v>
       </c>
       <c r="D2" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -5100,7 +5100,7 @@
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -5123,7 +5123,7 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -5146,7 +5146,7 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -5158,7 +5158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>530110</v>
       </c>
@@ -5169,7 +5169,7 @@
         <v>1354</v>
       </c>
       <c r="D6" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -5192,7 +5192,7 @@
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -5215,7 +5215,7 @@
         <v>939</v>
       </c>
       <c r="D8" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -5238,7 +5238,7 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -5261,7 +5261,7 @@
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -5285,7 +5285,7 @@
         <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -5309,7 +5309,7 @@
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -5333,7 +5333,7 @@
         <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -5357,7 +5357,7 @@
         <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -5381,7 +5381,7 @@
         <v>8</v>
       </c>
       <c r="D15" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -5405,7 +5405,7 @@
         <v>8</v>
       </c>
       <c r="D16" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -5429,7 +5429,7 @@
         <v>8</v>
       </c>
       <c r="D17" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -5453,7 +5453,7 @@
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -5477,7 +5477,7 @@
         <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -5501,7 +5501,7 @@
         <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -5525,7 +5525,7 @@
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -5549,7 +5549,7 @@
         <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -5573,7 +5573,7 @@
         <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -5597,7 +5597,7 @@
         <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -5621,7 +5621,7 @@
         <v>8</v>
       </c>
       <c r="D25" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -5645,7 +5645,7 @@
         <v>8</v>
       </c>
       <c r="D26" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -5669,7 +5669,7 @@
         <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -5693,7 +5693,7 @@
         <v>8</v>
       </c>
       <c r="D28" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -5717,7 +5717,7 @@
         <v>939</v>
       </c>
       <c r="D29" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -5741,7 +5741,7 @@
         <v>8</v>
       </c>
       <c r="D30" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -5765,7 +5765,7 @@
         <v>8</v>
       </c>
       <c r="D31" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -5788,7 +5788,7 @@
         <v>8</v>
       </c>
       <c r="D32" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -5811,7 +5811,7 @@
         <v>8</v>
       </c>
       <c r="D33" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -5834,7 +5834,7 @@
         <v>8</v>
       </c>
       <c r="D34" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -5857,7 +5857,7 @@
         <v>8</v>
       </c>
       <c r="D35" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E35">
         <v>1</v>
@@ -5880,7 +5880,7 @@
         <v>8</v>
       </c>
       <c r="D36" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E36">
         <v>1</v>
@@ -5903,7 +5903,7 @@
         <v>8</v>
       </c>
       <c r="D37" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E37">
         <v>1</v>
@@ -5926,7 +5926,7 @@
         <v>939</v>
       </c>
       <c r="D38" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -5949,7 +5949,7 @@
         <v>939</v>
       </c>
       <c r="D39" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -5972,7 +5972,7 @@
         <v>968</v>
       </c>
       <c r="D40" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E40">
         <v>1</v>
@@ -5995,7 +5995,7 @@
         <v>8</v>
       </c>
       <c r="D41" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -6018,7 +6018,7 @@
         <v>8</v>
       </c>
       <c r="D42" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E42">
         <v>1</v>
@@ -6041,7 +6041,7 @@
         <v>968</v>
       </c>
       <c r="D43" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E43">
         <v>1</v>
@@ -6064,7 +6064,7 @@
         <v>8</v>
       </c>
       <c r="D44" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -6087,7 +6087,7 @@
         <v>8</v>
       </c>
       <c r="D45" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E45">
         <v>1</v>
@@ -6110,7 +6110,7 @@
         <v>1355</v>
       </c>
       <c r="D46" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E46">
         <v>1</v>
@@ -6133,7 +6133,7 @@
         <v>968</v>
       </c>
       <c r="D47" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E47">
         <v>1</v>
@@ -6156,7 +6156,7 @@
         <v>1355</v>
       </c>
       <c r="D48" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -6179,7 +6179,7 @@
         <v>968</v>
       </c>
       <c r="D49" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E49">
         <v>1</v>
@@ -6202,7 +6202,7 @@
         <v>1355</v>
       </c>
       <c r="D50" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E50">
         <v>1</v>
@@ -6222,10 +6222,10 @@
         <v>57</v>
       </c>
       <c r="C51" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="D51" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E51">
         <v>1</v>
@@ -6245,10 +6245,10 @@
         <v>58</v>
       </c>
       <c r="C52" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="D52" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E52">
         <v>1</v>
@@ -6271,7 +6271,7 @@
         <v>1355</v>
       </c>
       <c r="D53" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -6294,7 +6294,7 @@
         <v>1355</v>
       </c>
       <c r="D54" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E54">
         <v>1</v>
@@ -6317,7 +6317,7 @@
         <v>1355</v>
       </c>
       <c r="D55" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E55">
         <v>1</v>
@@ -6340,7 +6340,7 @@
         <v>1355</v>
       </c>
       <c r="D56" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E56">
         <v>1</v>
@@ -6363,7 +6363,7 @@
         <v>1355</v>
       </c>
       <c r="D57" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E57">
         <v>1</v>
@@ -6386,7 +6386,7 @@
         <v>968</v>
       </c>
       <c r="D58" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E58">
         <v>1</v>
@@ -6409,7 +6409,7 @@
         <v>1355</v>
       </c>
       <c r="D59" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E59">
         <v>1</v>
@@ -6432,7 +6432,7 @@
         <v>1355</v>
       </c>
       <c r="D60" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E60">
         <v>1</v>
@@ -6455,7 +6455,7 @@
         <v>1355</v>
       </c>
       <c r="D61" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E61">
         <v>1</v>
@@ -6478,7 +6478,7 @@
         <v>1355</v>
       </c>
       <c r="D62" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E62">
         <v>1</v>
@@ -6501,7 +6501,7 @@
         <v>1355</v>
       </c>
       <c r="D63" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E63">
         <v>1</v>
@@ -6524,7 +6524,7 @@
         <v>1355</v>
       </c>
       <c r="D64" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E64">
         <v>1</v>
@@ -6547,7 +6547,7 @@
         <v>1355</v>
       </c>
       <c r="D65" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E65">
         <v>1</v>
@@ -6570,7 +6570,7 @@
         <v>1355</v>
       </c>
       <c r="D66" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -6593,7 +6593,7 @@
         <v>1355</v>
       </c>
       <c r="D67" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E67">
         <v>1</v>
@@ -6616,7 +6616,7 @@
         <v>968</v>
       </c>
       <c r="D68" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E68">
         <v>1</v>
@@ -6639,7 +6639,7 @@
         <v>1355</v>
       </c>
       <c r="D69" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E69">
         <v>1</v>
@@ -6662,7 +6662,7 @@
         <v>968</v>
       </c>
       <c r="D70" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E70">
         <v>1</v>
@@ -6685,7 +6685,7 @@
         <v>968</v>
       </c>
       <c r="D71" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -6708,7 +6708,7 @@
         <v>1355</v>
       </c>
       <c r="D72" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -6728,10 +6728,10 @@
         <v>79</v>
       </c>
       <c r="C73" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="D73" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E73">
         <v>1</v>
@@ -6754,7 +6754,7 @@
         <v>968</v>
       </c>
       <c r="D74" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E74">
         <v>1</v>
@@ -6777,7 +6777,7 @@
         <v>968</v>
       </c>
       <c r="D75" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E75">
         <v>1</v>
@@ -6800,7 +6800,7 @@
         <v>81</v>
       </c>
       <c r="D76" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E76">
         <v>1</v>
@@ -6823,7 +6823,7 @@
         <v>968</v>
       </c>
       <c r="D77" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E77">
         <v>1</v>
@@ -6846,7 +6846,7 @@
         <v>1355</v>
       </c>
       <c r="D78" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E78">
         <v>1</v>
@@ -6869,7 +6869,7 @@
         <v>1355</v>
       </c>
       <c r="D79" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E79">
         <v>1</v>
@@ -6892,7 +6892,7 @@
         <v>1355</v>
       </c>
       <c r="D80" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E80">
         <v>1</v>
@@ -6915,7 +6915,7 @@
         <v>81</v>
       </c>
       <c r="D81" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E81">
         <v>1</v>
@@ -6938,7 +6938,7 @@
         <v>968</v>
       </c>
       <c r="D82" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E82">
         <v>1</v>
@@ -6961,7 +6961,7 @@
         <v>968</v>
       </c>
       <c r="D83" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E83">
         <v>1</v>
@@ -6984,7 +6984,7 @@
         <v>1355</v>
       </c>
       <c r="D84" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E84">
         <v>1</v>
@@ -7007,7 +7007,7 @@
         <v>1355</v>
       </c>
       <c r="D85" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E85">
         <v>1</v>
@@ -7030,7 +7030,7 @@
         <v>1355</v>
       </c>
       <c r="D86" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E86">
         <v>1</v>
@@ -7053,7 +7053,7 @@
         <v>1355</v>
       </c>
       <c r="D87" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E87">
         <v>1</v>
@@ -7076,7 +7076,7 @@
         <v>1355</v>
       </c>
       <c r="D88" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E88">
         <v>1</v>
@@ -7099,7 +7099,7 @@
         <v>1355</v>
       </c>
       <c r="D89" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E89">
         <v>1</v>
@@ -7122,7 +7122,7 @@
         <v>968</v>
       </c>
       <c r="D90" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E90">
         <v>1</v>
@@ -7145,7 +7145,7 @@
         <v>1355</v>
       </c>
       <c r="D91" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E91">
         <v>1</v>
@@ -7168,7 +7168,7 @@
         <v>1355</v>
       </c>
       <c r="D92" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E92">
         <v>1</v>
@@ -7191,7 +7191,7 @@
         <v>1355</v>
       </c>
       <c r="D93" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E93">
         <v>1</v>
@@ -7214,7 +7214,7 @@
         <v>1355</v>
       </c>
       <c r="D94" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -7237,7 +7237,7 @@
         <v>1355</v>
       </c>
       <c r="D95" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E95">
         <v>1</v>
@@ -7260,7 +7260,7 @@
         <v>1355</v>
       </c>
       <c r="D96" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E96">
         <v>1</v>
@@ -7283,7 +7283,7 @@
         <v>1355</v>
       </c>
       <c r="D97" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E97">
         <v>1</v>
@@ -7306,7 +7306,7 @@
         <v>1355</v>
       </c>
       <c r="D98" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -7329,7 +7329,7 @@
         <v>1355</v>
       </c>
       <c r="D99" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E99">
         <v>1</v>
@@ -7352,7 +7352,7 @@
         <v>1355</v>
       </c>
       <c r="D100" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E100">
         <v>1</v>
@@ -7375,7 +7375,7 @@
         <v>1355</v>
       </c>
       <c r="D101" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E101">
         <v>1</v>
@@ -7398,7 +7398,7 @@
         <v>1355</v>
       </c>
       <c r="D102" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E102">
         <v>1</v>
@@ -7421,7 +7421,7 @@
         <v>968</v>
       </c>
       <c r="D103" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E103">
         <v>1</v>
@@ -7444,7 +7444,7 @@
         <v>1355</v>
       </c>
       <c r="D104" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E104">
         <v>1</v>
@@ -7467,7 +7467,7 @@
         <v>1355</v>
       </c>
       <c r="D105" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E105">
         <v>1</v>
@@ -7490,7 +7490,7 @@
         <v>1355</v>
       </c>
       <c r="D106" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E106">
         <v>1</v>
@@ -7513,7 +7513,7 @@
         <v>1355</v>
       </c>
       <c r="D107" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E107">
         <v>1</v>
@@ -7536,7 +7536,7 @@
         <v>1355</v>
       </c>
       <c r="D108" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E108">
         <v>1</v>
@@ -7559,7 +7559,7 @@
         <v>1355</v>
       </c>
       <c r="D109" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E109">
         <v>1</v>
@@ -7582,7 +7582,7 @@
         <v>1355</v>
       </c>
       <c r="D110" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E110">
         <v>1</v>
@@ -7605,7 +7605,7 @@
         <v>1355</v>
       </c>
       <c r="D111" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E111">
         <v>1</v>
@@ -7628,7 +7628,7 @@
         <v>1355</v>
       </c>
       <c r="D112" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E112">
         <v>1</v>
@@ -7651,7 +7651,7 @@
         <v>1355</v>
       </c>
       <c r="D113" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E113">
         <v>1</v>
@@ -7674,7 +7674,7 @@
         <v>1355</v>
       </c>
       <c r="D114" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E114">
         <v>1</v>
@@ -7697,7 +7697,7 @@
         <v>968</v>
       </c>
       <c r="D115" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E115">
         <v>1</v>
@@ -7720,7 +7720,7 @@
         <v>1355</v>
       </c>
       <c r="D116" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E116">
         <v>1</v>
@@ -7743,7 +7743,7 @@
         <v>968</v>
       </c>
       <c r="D117" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E117">
         <v>1</v>
@@ -7766,7 +7766,7 @@
         <v>1355</v>
       </c>
       <c r="D118" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E118">
         <v>1</v>
@@ -7789,7 +7789,7 @@
         <v>1122</v>
       </c>
       <c r="D119" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E119">
         <v>1</v>
@@ -7812,7 +7812,7 @@
         <v>1355</v>
       </c>
       <c r="D120" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E120">
         <v>1</v>
@@ -7835,7 +7835,7 @@
         <v>1355</v>
       </c>
       <c r="D121" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E121">
         <v>1</v>
@@ -7858,7 +7858,7 @@
         <v>1355</v>
       </c>
       <c r="D122" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E122">
         <v>1</v>
@@ -7881,7 +7881,7 @@
         <v>968</v>
       </c>
       <c r="D123" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E123">
         <v>1</v>
@@ -7904,7 +7904,7 @@
         <v>968</v>
       </c>
       <c r="D124" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E124">
         <v>1</v>
@@ -7927,7 +7927,7 @@
         <v>1355</v>
       </c>
       <c r="D125" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E125">
         <v>1</v>
@@ -7950,7 +7950,7 @@
         <v>1355</v>
       </c>
       <c r="D126" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E126">
         <v>1</v>
@@ -7973,7 +7973,7 @@
         <v>968</v>
       </c>
       <c r="D127" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E127">
         <v>1</v>
@@ -7996,7 +7996,7 @@
         <v>1355</v>
       </c>
       <c r="D128" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E128">
         <v>1</v>
@@ -8019,7 +8019,7 @@
         <v>1355</v>
       </c>
       <c r="D129" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E129">
         <v>1</v>
@@ -8042,7 +8042,7 @@
         <v>1355</v>
       </c>
       <c r="D130" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E130">
         <v>1</v>
@@ -8065,7 +8065,7 @@
         <v>1355</v>
       </c>
       <c r="D131" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E131">
         <v>1</v>
@@ -8088,7 +8088,7 @@
         <v>968</v>
       </c>
       <c r="D132" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E132">
         <v>1</v>
@@ -8111,7 +8111,7 @@
         <v>1355</v>
       </c>
       <c r="D133" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E133">
         <v>1</v>
@@ -8134,7 +8134,7 @@
         <v>968</v>
       </c>
       <c r="D134" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E134">
         <v>1</v>
@@ -8157,7 +8157,7 @@
         <v>1355</v>
       </c>
       <c r="D135" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E135">
         <v>1</v>
@@ -8180,7 +8180,7 @@
         <v>968</v>
       </c>
       <c r="D136" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E136">
         <v>1</v>
@@ -8203,7 +8203,7 @@
         <v>1355</v>
       </c>
       <c r="D137" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E137">
         <v>1</v>
@@ -8226,7 +8226,7 @@
         <v>968</v>
       </c>
       <c r="D138" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E138">
         <v>1</v>
@@ -8249,7 +8249,7 @@
         <v>968</v>
       </c>
       <c r="D139" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E139">
         <v>1</v>
@@ -8272,7 +8272,7 @@
         <v>1354</v>
       </c>
       <c r="D140" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E140">
         <v>1</v>
@@ -8295,7 +8295,7 @@
         <v>968</v>
       </c>
       <c r="D141" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E141">
         <v>1</v>
@@ -8315,10 +8315,10 @@
         <v>149</v>
       </c>
       <c r="C142" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="D142" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E142">
         <v>1</v>
@@ -8341,7 +8341,7 @@
         <v>1354</v>
       </c>
       <c r="D143" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E143">
         <v>1</v>
@@ -8364,7 +8364,7 @@
         <v>1122</v>
       </c>
       <c r="D144" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E144">
         <v>1</v>
@@ -8387,7 +8387,7 @@
         <v>968</v>
       </c>
       <c r="D145" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E145">
         <v>1</v>
@@ -8407,10 +8407,10 @@
         <v>153</v>
       </c>
       <c r="C146" t="s">
-        <v>1356</v>
+        <v>1371</v>
       </c>
       <c r="D146" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E146">
         <v>1</v>
@@ -8433,7 +8433,7 @@
         <v>968</v>
       </c>
       <c r="D147" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E147">
         <v>1</v>
@@ -8456,7 +8456,7 @@
         <v>968</v>
       </c>
       <c r="D148" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E148">
         <v>1</v>
@@ -8479,7 +8479,7 @@
         <v>968</v>
       </c>
       <c r="D149" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E149">
         <v>1</v>
@@ -8502,7 +8502,7 @@
         <v>968</v>
       </c>
       <c r="D150" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E150">
         <v>1</v>
@@ -8525,7 +8525,7 @@
         <v>968</v>
       </c>
       <c r="D151" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E151">
         <v>1</v>
@@ -8548,7 +8548,7 @@
         <v>1355</v>
       </c>
       <c r="D152" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E152">
         <v>1</v>
@@ -8571,7 +8571,7 @@
         <v>968</v>
       </c>
       <c r="D153" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E153">
         <v>1</v>
@@ -8594,7 +8594,7 @@
         <v>1355</v>
       </c>
       <c r="D154" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E154">
         <v>1</v>
@@ -8617,7 +8617,7 @@
         <v>1355</v>
       </c>
       <c r="D155" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E155">
         <v>1</v>
@@ -8640,7 +8640,7 @@
         <v>1355</v>
       </c>
       <c r="D156" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E156">
         <v>1</v>
@@ -8663,7 +8663,7 @@
         <v>1355</v>
       </c>
       <c r="D157" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E157">
         <v>1</v>
@@ -8686,7 +8686,7 @@
         <v>1355</v>
       </c>
       <c r="D158" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E158">
         <v>1</v>
@@ -8709,7 +8709,7 @@
         <v>1122</v>
       </c>
       <c r="D159" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E159">
         <v>1</v>
@@ -8732,7 +8732,7 @@
         <v>1122</v>
       </c>
       <c r="D160" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E160">
         <v>1</v>
@@ -8755,7 +8755,7 @@
         <v>1122</v>
       </c>
       <c r="D161" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E161">
         <v>1</v>
@@ -8775,10 +8775,10 @@
         <v>169</v>
       </c>
       <c r="C162" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="D162" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E162">
         <v>1</v>
@@ -8801,7 +8801,7 @@
         <v>1355</v>
       </c>
       <c r="D163" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E163">
         <v>1</v>
@@ -8824,7 +8824,7 @@
         <v>1355</v>
       </c>
       <c r="D164" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E164">
         <v>1</v>
@@ -8847,7 +8847,7 @@
         <v>1355</v>
       </c>
       <c r="D165" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E165">
         <v>1</v>
@@ -8870,7 +8870,7 @@
         <v>1355</v>
       </c>
       <c r="D166" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E166">
         <v>1</v>
@@ -8893,7 +8893,7 @@
         <v>1355</v>
       </c>
       <c r="D167" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E167">
         <v>1</v>
@@ -8916,7 +8916,7 @@
         <v>1355</v>
       </c>
       <c r="D168" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E168">
         <v>1</v>
@@ -8939,7 +8939,7 @@
         <v>1355</v>
       </c>
       <c r="D169" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E169">
         <v>1</v>
@@ -8962,7 +8962,7 @@
         <v>1355</v>
       </c>
       <c r="D170" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E170">
         <v>1</v>
@@ -8982,10 +8982,10 @@
         <v>178</v>
       </c>
       <c r="C171" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="D171" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E171">
         <v>1</v>
@@ -9005,10 +9005,10 @@
         <v>179</v>
       </c>
       <c r="C172" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="D172" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E172">
         <v>1</v>
@@ -9028,10 +9028,10 @@
         <v>180</v>
       </c>
       <c r="C173" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="D173" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E173">
         <v>1</v>
@@ -9051,10 +9051,10 @@
         <v>181</v>
       </c>
       <c r="C174" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="D174" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E174">
         <v>1</v>
@@ -9077,7 +9077,7 @@
         <v>1355</v>
       </c>
       <c r="D175" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E175">
         <v>1</v>
@@ -9100,7 +9100,7 @@
         <v>1355</v>
       </c>
       <c r="D176" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E176">
         <v>1</v>
@@ -9123,7 +9123,7 @@
         <v>1355</v>
       </c>
       <c r="D177" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E177">
         <v>1</v>
@@ -9146,7 +9146,7 @@
         <v>1355</v>
       </c>
       <c r="D178" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E178">
         <v>1</v>
@@ -9169,7 +9169,7 @@
         <v>187</v>
       </c>
       <c r="D179" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E179">
         <v>1</v>
@@ -9192,7 +9192,7 @@
         <v>1355</v>
       </c>
       <c r="D180" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E180">
         <v>1</v>
@@ -9215,7 +9215,7 @@
         <v>190</v>
       </c>
       <c r="D181" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E181">
         <v>1</v>
@@ -9238,7 +9238,7 @@
         <v>190</v>
       </c>
       <c r="D182" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E182">
         <v>1</v>
@@ -9261,7 +9261,7 @@
         <v>190</v>
       </c>
       <c r="D183" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E183">
         <v>1</v>
@@ -9284,7 +9284,7 @@
         <v>190</v>
       </c>
       <c r="D184" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E184">
         <v>1</v>
@@ -9307,7 +9307,7 @@
         <v>190</v>
       </c>
       <c r="D185" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E185">
         <v>1</v>
@@ -9330,7 +9330,7 @@
         <v>968</v>
       </c>
       <c r="D186" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E186">
         <v>1</v>
@@ -9353,7 +9353,7 @@
         <v>968</v>
       </c>
       <c r="D187" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E187">
         <v>1</v>
@@ -9376,7 +9376,7 @@
         <v>187</v>
       </c>
       <c r="D188" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E188">
         <v>1</v>
@@ -9399,7 +9399,7 @@
         <v>968</v>
       </c>
       <c r="D189" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E189">
         <v>1</v>
@@ -9422,7 +9422,7 @@
         <v>968</v>
       </c>
       <c r="D190" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E190">
         <v>1</v>
@@ -9445,7 +9445,7 @@
         <v>968</v>
       </c>
       <c r="D191" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E191">
         <v>1</v>
@@ -9465,10 +9465,10 @@
         <v>158</v>
       </c>
       <c r="C192" t="s">
-        <v>1359</v>
+        <v>1374</v>
       </c>
       <c r="D192" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E192">
         <v>1</v>
@@ -9488,10 +9488,10 @@
         <v>1350</v>
       </c>
       <c r="C193" t="s">
-        <v>1359</v>
+        <v>1374</v>
       </c>
       <c r="D193" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -9514,7 +9514,7 @@
         <v>200</v>
       </c>
       <c r="D194" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E194">
         <v>1</v>
@@ -9534,10 +9534,10 @@
         <v>1351</v>
       </c>
       <c r="C195" t="s">
-        <v>1359</v>
+        <v>1374</v>
       </c>
       <c r="D195" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E195">
         <v>0</v>
@@ -9560,7 +9560,7 @@
         <v>200</v>
       </c>
       <c r="D196" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E196">
         <v>1</v>
@@ -9572,7 +9572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>530902</v>
       </c>
@@ -9580,10 +9580,10 @@
         <v>156</v>
       </c>
       <c r="C197" t="s">
-        <v>1357</v>
+        <v>1372</v>
       </c>
       <c r="D197" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E197">
         <v>1</v>
@@ -9606,7 +9606,7 @@
         <v>200</v>
       </c>
       <c r="D198" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E198">
         <v>1</v>
@@ -9618,7 +9618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>530210</v>
       </c>
@@ -9626,10 +9626,10 @@
         <v>195</v>
       </c>
       <c r="C199" t="s">
-        <v>1357</v>
+        <v>1372</v>
       </c>
       <c r="D199" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E199">
         <v>1</v>
@@ -9641,7 +9641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>470111</v>
       </c>
@@ -9649,10 +9649,10 @@
         <v>80</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="D200" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E200">
         <v>1</v>
@@ -9664,7 +9664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>470112</v>
       </c>
@@ -9672,10 +9672,10 @@
         <v>82</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="D201" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E201">
         <v>1</v>
@@ -9698,7 +9698,7 @@
         <v>200</v>
       </c>
       <c r="D202" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E202">
         <v>1</v>
@@ -9721,7 +9721,7 @@
         <v>200</v>
       </c>
       <c r="D203" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E203">
         <v>1</v>
@@ -9733,7 +9733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>470114</v>
       </c>
@@ -9741,10 +9741,10 @@
         <v>84</v>
       </c>
       <c r="C204" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="D204" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E204">
         <v>1</v>
@@ -9756,7 +9756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>480100</v>
       </c>
@@ -9764,11 +9764,11 @@
         <v>89</v>
       </c>
       <c r="C205" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D205" t="s">
         <v>1364</v>
       </c>
-      <c r="D205" t="s">
-        <v>1368</v>
-      </c>
       <c r="E205">
         <v>1</v>
       </c>
@@ -9779,7 +9779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>480110</v>
       </c>
@@ -9787,11 +9787,11 @@
         <v>90</v>
       </c>
       <c r="C206" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D206" t="s">
         <v>1364</v>
       </c>
-      <c r="D206" t="s">
-        <v>1368</v>
-      </c>
       <c r="E206">
         <v>1</v>
       </c>
@@ -9802,7 +9802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>490000</v>
       </c>
@@ -9810,11 +9810,11 @@
         <v>97</v>
       </c>
       <c r="C207" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D207" t="s">
         <v>1364</v>
       </c>
-      <c r="D207" t="s">
-        <v>1368</v>
-      </c>
       <c r="E207">
         <v>1</v>
       </c>
@@ -9825,7 +9825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>490315</v>
       </c>
@@ -9833,11 +9833,11 @@
         <v>110</v>
       </c>
       <c r="C208" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D208" t="s">
         <v>1364</v>
       </c>
-      <c r="D208" t="s">
-        <v>1368</v>
-      </c>
       <c r="E208">
         <v>1</v>
       </c>
@@ -9848,7 +9848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>620114</v>
       </c>
@@ -9856,11 +9856,11 @@
         <v>160</v>
       </c>
       <c r="C209" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D209" t="s">
         <v>1364</v>
       </c>
-      <c r="D209" t="s">
-        <v>1368</v>
-      </c>
       <c r="E209">
         <v>1</v>
       </c>
@@ -9871,7 +9871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>490100</v>
       </c>
@@ -9879,11 +9879,11 @@
         <v>1348</v>
       </c>
       <c r="C210" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D210" t="s">
         <v>1364</v>
       </c>
-      <c r="D210" t="s">
-        <v>1368</v>
-      </c>
       <c r="E210">
         <v>0</v>
       </c>
@@ -9894,7 +9894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>500110</v>
       </c>
@@ -9902,11 +9902,11 @@
         <v>122</v>
       </c>
       <c r="C211" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D211" t="s">
         <v>1364</v>
       </c>
-      <c r="D211" t="s">
-        <v>1368</v>
-      </c>
       <c r="E211">
         <v>1</v>
       </c>
@@ -9917,7 +9917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>510115</v>
       </c>
@@ -9925,10 +9925,10 @@
         <v>124</v>
       </c>
       <c r="C212" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D212" t="s">
         <v>1364</v>
-      </c>
-      <c r="D212" t="s">
-        <v>1368</v>
       </c>
       <c r="E212">
         <v>1</v>
@@ -9951,7 +9951,7 @@
         <v>200</v>
       </c>
       <c r="D213" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E213">
         <v>1</v>
@@ -9963,7 +9963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>520310</v>
       </c>
@@ -9971,10 +9971,10 @@
         <v>130</v>
       </c>
       <c r="C214" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D214" t="s">
         <v>1364</v>
-      </c>
-      <c r="D214" t="s">
-        <v>1368</v>
       </c>
       <c r="E214">
         <v>1</v>
@@ -9997,7 +9997,7 @@
         <v>200</v>
       </c>
       <c r="D215" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E215">
         <v>1</v>
@@ -10020,7 +10020,7 @@
         <v>200</v>
       </c>
       <c r="D216" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E216">
         <v>1</v>
@@ -10043,7 +10043,7 @@
         <v>200</v>
       </c>
       <c r="D217" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E217">
         <v>1</v>
@@ -10055,7 +10055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>520410</v>
       </c>
@@ -10063,10 +10063,10 @@
         <v>131</v>
       </c>
       <c r="C218" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D218" t="s">
         <v>1364</v>
-      </c>
-      <c r="D218" t="s">
-        <v>1368</v>
       </c>
       <c r="E218">
         <v>1</v>
@@ -10089,7 +10089,7 @@
         <v>200</v>
       </c>
       <c r="D219" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E219">
         <v>1</v>
@@ -10112,7 +10112,7 @@
         <v>200</v>
       </c>
       <c r="D220" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E220">
         <v>1</v>
@@ -10124,7 +10124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>520516</v>
       </c>
@@ -10132,10 +10132,10 @@
         <v>134</v>
       </c>
       <c r="C221" t="s">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="D221" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E221">
         <v>1</v>
@@ -10158,7 +10158,7 @@
         <v>200</v>
       </c>
       <c r="D222" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E222">
         <v>1</v>
@@ -10170,7 +10170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>520531</v>
       </c>
@@ -10178,10 +10178,10 @@
         <v>139</v>
       </c>
       <c r="C223" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="D223" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E223">
         <v>1</v>
@@ -10193,7 +10193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>520541</v>
       </c>
@@ -10201,10 +10201,10 @@
         <v>141</v>
       </c>
       <c r="C224" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="D224" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E224">
         <v>1</v>
@@ -10227,7 +10227,7 @@
         <v>200</v>
       </c>
       <c r="D225" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E225">
         <v>1</v>
@@ -10239,7 +10239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>520550</v>
       </c>
@@ -10247,10 +10247,10 @@
         <v>143</v>
       </c>
       <c r="C226" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="D226" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E226">
         <v>1</v>
@@ -10262,7 +10262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>530903</v>
       </c>
@@ -10270,10 +10270,10 @@
         <v>157</v>
       </c>
       <c r="C227" t="s">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="D227" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E227">
         <v>1</v>
@@ -10296,7 +10296,7 @@
         <v>200</v>
       </c>
       <c r="D228" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E228">
         <v>1</v>
@@ -10319,7 +10319,7 @@
         <v>200</v>
       </c>
       <c r="D229" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E229">
         <v>1</v>
@@ -10331,7 +10331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>450350</v>
       </c>
@@ -10339,10 +10339,10 @@
         <v>64</v>
       </c>
       <c r="C230" t="s">
-        <v>1366</v>
+        <v>1362</v>
       </c>
       <c r="D230" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E230">
         <v>1</v>
@@ -10365,7 +10365,7 @@
         <v>200</v>
       </c>
       <c r="D231" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E231">
         <v>1</v>
@@ -10388,7 +10388,7 @@
         <v>200</v>
       </c>
       <c r="D232" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E232">
         <v>1</v>
@@ -10411,7 +10411,7 @@
         <v>200</v>
       </c>
       <c r="D233" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E233">
         <v>1</v>
@@ -10434,7 +10434,7 @@
         <v>200</v>
       </c>
       <c r="D234" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E234">
         <v>1</v>
@@ -10457,7 +10457,7 @@
         <v>200</v>
       </c>
       <c r="D235" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E235">
         <v>1</v>
@@ -10469,7 +10469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>450110</v>
       </c>
@@ -10477,10 +10477,10 @@
         <v>53</v>
       </c>
       <c r="C236" t="s">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="D236" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E236">
         <v>1</v>
@@ -10503,7 +10503,7 @@
         <v>200</v>
       </c>
       <c r="D237" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E237">
         <v>1</v>
@@ -10515,7 +10515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>450210</v>
       </c>
@@ -10523,10 +10523,10 @@
         <v>55</v>
       </c>
       <c r="C238" t="s">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="D238" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E238">
         <v>1</v>
@@ -10549,7 +10549,7 @@
         <v>200</v>
       </c>
       <c r="D239" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E239">
         <v>1</v>
@@ -10561,7 +10561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>460110</v>
       </c>
@@ -10569,10 +10569,10 @@
         <v>74</v>
       </c>
       <c r="C240" t="s">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="D240" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E240">
         <v>1</v>
@@ -10595,7 +10595,7 @@
         <v>200</v>
       </c>
       <c r="D241" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E241">
         <v>1</v>
@@ -10618,7 +10618,7 @@
         <v>200</v>
       </c>
       <c r="D242" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E242">
         <v>1</v>
@@ -10630,7 +10630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>460901</v>
       </c>
@@ -10638,10 +10638,10 @@
         <v>76</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="D243" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E243">
         <v>1</v>
@@ -10664,7 +10664,7 @@
         <v>200</v>
       </c>
       <c r="D244" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E244">
         <v>1</v>
@@ -10687,7 +10687,7 @@
         <v>748</v>
       </c>
       <c r="D245" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E245">
         <v>1</v>
@@ -10710,7 +10710,7 @@
         <v>748</v>
       </c>
       <c r="D246" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E246">
         <v>1</v>
@@ -10733,7 +10733,7 @@
         <v>200</v>
       </c>
       <c r="D247" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E247">
         <v>1</v>
@@ -10756,7 +10756,7 @@
         <v>200</v>
       </c>
       <c r="D248" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E248">
         <v>1</v>
@@ -10779,7 +10779,7 @@
         <v>748</v>
       </c>
       <c r="D249" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E249">
         <v>1</v>
@@ -10802,7 +10802,7 @@
         <v>748</v>
       </c>
       <c r="D250" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E250">
         <v>1</v>
@@ -10825,7 +10825,7 @@
         <v>748</v>
       </c>
       <c r="D251" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E251">
         <v>1</v>
@@ -10848,7 +10848,7 @@
         <v>200</v>
       </c>
       <c r="D252" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E252">
         <v>1</v>
@@ -10871,7 +10871,7 @@
         <v>748</v>
       </c>
       <c r="D253" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E253">
         <v>1</v>
@@ -10894,7 +10894,7 @@
         <v>748</v>
       </c>
       <c r="D254" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E254">
         <v>1</v>
@@ -10917,7 +10917,7 @@
         <v>200</v>
       </c>
       <c r="D255" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E255">
         <v>1</v>
@@ -10940,7 +10940,7 @@
         <v>748</v>
       </c>
       <c r="D256" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E256">
         <v>1</v>
@@ -10963,7 +10963,7 @@
         <v>748</v>
       </c>
       <c r="D257" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E257">
         <v>1</v>
@@ -10986,7 +10986,7 @@
         <v>200</v>
       </c>
       <c r="D258" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E258">
         <v>1</v>
@@ -11009,7 +11009,7 @@
         <v>748</v>
       </c>
       <c r="D259" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E259">
         <v>1</v>
@@ -11032,7 +11032,7 @@
         <v>748</v>
       </c>
       <c r="D260" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E260">
         <v>1</v>
@@ -11055,7 +11055,7 @@
         <v>748</v>
       </c>
       <c r="D261" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E261">
         <v>1</v>
@@ -11078,7 +11078,7 @@
         <v>748</v>
       </c>
       <c r="D262" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E262">
         <v>1</v>
@@ -11101,7 +11101,7 @@
         <v>200</v>
       </c>
       <c r="D263" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E263">
         <v>1</v>
@@ -11124,7 +11124,7 @@
         <v>748</v>
       </c>
       <c r="D264" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E264">
         <v>1</v>
@@ -11147,7 +11147,7 @@
         <v>200</v>
       </c>
       <c r="D265" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E265">
         <v>1</v>
@@ -11170,7 +11170,7 @@
         <v>200</v>
       </c>
       <c r="D266" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E266">
         <v>1</v>
@@ -11193,7 +11193,7 @@
         <v>200</v>
       </c>
       <c r="D267" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E267">
         <v>1</v>
@@ -11216,7 +11216,7 @@
         <v>748</v>
       </c>
       <c r="D268" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E268">
         <v>1</v>
@@ -11239,7 +11239,7 @@
         <v>200</v>
       </c>
       <c r="D269" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E269">
         <v>1</v>
@@ -11262,7 +11262,7 @@
         <v>200</v>
       </c>
       <c r="D270" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E270">
         <v>1</v>
@@ -11285,7 +11285,7 @@
         <v>200</v>
       </c>
       <c r="D271" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E271">
         <v>1</v>
@@ -11308,7 +11308,7 @@
         <v>200</v>
       </c>
       <c r="D272" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E272">
         <v>1</v>
@@ -11331,7 +11331,7 @@
         <v>200</v>
       </c>
       <c r="D273" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E273">
         <v>1</v>
@@ -11354,7 +11354,7 @@
         <v>200</v>
       </c>
       <c r="D274" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E274">
         <v>1</v>
@@ -11377,7 +11377,7 @@
         <v>200</v>
       </c>
       <c r="D275" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E275">
         <v>1</v>
@@ -11400,7 +11400,7 @@
         <v>200</v>
       </c>
       <c r="D276" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E276">
         <v>1</v>
@@ -11423,7 +11423,7 @@
         <v>200</v>
       </c>
       <c r="D277" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E277">
         <v>1</v>
@@ -11446,7 +11446,7 @@
         <v>200</v>
       </c>
       <c r="D278" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E278">
         <v>1</v>
@@ -11469,7 +11469,7 @@
         <v>200</v>
       </c>
       <c r="D279" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E279">
         <v>1</v>
@@ -11492,7 +11492,7 @@
         <v>200</v>
       </c>
       <c r="D280" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E280">
         <v>1</v>
@@ -11515,7 +11515,7 @@
         <v>748</v>
       </c>
       <c r="D281" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E281">
         <v>1</v>
@@ -11538,7 +11538,7 @@
         <v>200</v>
       </c>
       <c r="D282" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E282">
         <v>1</v>
@@ -11561,7 +11561,7 @@
         <v>200</v>
       </c>
       <c r="D283" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E283">
         <v>1</v>
@@ -11584,7 +11584,7 @@
         <v>748</v>
       </c>
       <c r="D284" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E284">
         <v>1</v>
@@ -11607,7 +11607,7 @@
         <v>748</v>
       </c>
       <c r="D285" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E285">
         <v>1</v>
@@ -11630,7 +11630,7 @@
         <v>200</v>
       </c>
       <c r="D286" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E286">
         <v>1</v>
@@ -11653,7 +11653,7 @@
         <v>200</v>
       </c>
       <c r="D287" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E287">
         <v>1</v>
@@ -11676,7 +11676,7 @@
         <v>748</v>
       </c>
       <c r="D288" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E288">
         <v>1</v>
@@ -11699,7 +11699,7 @@
         <v>748</v>
       </c>
       <c r="D289" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E289">
         <v>1</v>
@@ -11722,7 +11722,7 @@
         <v>200</v>
       </c>
       <c r="D290" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E290">
         <v>1</v>
@@ -11745,7 +11745,7 @@
         <v>748</v>
       </c>
       <c r="D291" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E291">
         <v>1</v>
@@ -11768,7 +11768,7 @@
         <v>748</v>
       </c>
       <c r="D292" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E292">
         <v>1</v>
@@ -11791,7 +11791,7 @@
         <v>748</v>
       </c>
       <c r="D293" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E293">
         <v>1</v>
@@ -11814,7 +11814,7 @@
         <v>200</v>
       </c>
       <c r="D294" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E294">
         <v>1</v>
@@ -11837,7 +11837,7 @@
         <v>200</v>
       </c>
       <c r="D295" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E295">
         <v>1</v>
@@ -11860,7 +11860,7 @@
         <v>200</v>
       </c>
       <c r="D296" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E296">
         <v>1</v>
@@ -11883,7 +11883,7 @@
         <v>748</v>
       </c>
       <c r="D297" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E297">
         <v>1</v>
@@ -11906,7 +11906,7 @@
         <v>200</v>
       </c>
       <c r="D298" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E298">
         <v>1</v>
@@ -11929,7 +11929,7 @@
         <v>748</v>
       </c>
       <c r="D299" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E299">
         <v>1</v>
@@ -11952,7 +11952,7 @@
         <v>200</v>
       </c>
       <c r="D300" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E300">
         <v>1</v>
@@ -11975,7 +11975,7 @@
         <v>200</v>
       </c>
       <c r="D301" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E301">
         <v>1</v>
@@ -11998,7 +11998,7 @@
         <v>748</v>
       </c>
       <c r="D302" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E302">
         <v>1</v>
@@ -12021,7 +12021,7 @@
         <v>748</v>
       </c>
       <c r="D303" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E303">
         <v>1</v>
@@ -12044,7 +12044,7 @@
         <v>748</v>
       </c>
       <c r="D304" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E304">
         <v>1</v>
@@ -12067,7 +12067,7 @@
         <v>748</v>
       </c>
       <c r="D305" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E305">
         <v>1</v>
@@ -12090,7 +12090,7 @@
         <v>748</v>
       </c>
       <c r="D306" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E306">
         <v>1</v>
@@ -12113,7 +12113,7 @@
         <v>748</v>
       </c>
       <c r="D307" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E307">
         <v>1</v>
@@ -12136,7 +12136,7 @@
         <v>748</v>
       </c>
       <c r="D308" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E308">
         <v>1</v>
@@ -12159,7 +12159,7 @@
         <v>748</v>
       </c>
       <c r="D309" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E309">
         <v>1</v>
@@ -12182,7 +12182,7 @@
         <v>748</v>
       </c>
       <c r="D310" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E310">
         <v>1</v>
@@ -12205,7 +12205,7 @@
         <v>748</v>
       </c>
       <c r="D311" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E311">
         <v>1</v>
@@ -12228,7 +12228,7 @@
         <v>200</v>
       </c>
       <c r="D312" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E312">
         <v>1</v>
@@ -12251,7 +12251,7 @@
         <v>748</v>
       </c>
       <c r="D313" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E313">
         <v>1</v>
@@ -12274,7 +12274,7 @@
         <v>748</v>
       </c>
       <c r="D314" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E314">
         <v>1</v>
@@ -12297,7 +12297,7 @@
         <v>748</v>
       </c>
       <c r="D315" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E315">
         <v>1</v>
@@ -12320,7 +12320,7 @@
         <v>748</v>
       </c>
       <c r="D316" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E316">
         <v>1</v>
@@ -12343,7 +12343,7 @@
         <v>200</v>
       </c>
       <c r="D317" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E317">
         <v>1</v>
@@ -12366,7 +12366,7 @@
         <v>200</v>
       </c>
       <c r="D318" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E318">
         <v>1</v>
@@ -12389,7 +12389,7 @@
         <v>200</v>
       </c>
       <c r="D319" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E319">
         <v>1</v>
@@ -12412,7 +12412,7 @@
         <v>200</v>
       </c>
       <c r="D320" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E320">
         <v>1</v>
@@ -12435,7 +12435,7 @@
         <v>200</v>
       </c>
       <c r="D321" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E321">
         <v>1</v>
@@ -12458,7 +12458,7 @@
         <v>200</v>
       </c>
       <c r="D322" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E322">
         <v>1</v>
@@ -12481,7 +12481,7 @@
         <v>200</v>
       </c>
       <c r="D323" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E323">
         <v>1</v>
@@ -12504,7 +12504,7 @@
         <v>200</v>
       </c>
       <c r="D324" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E324">
         <v>1</v>
@@ -12527,7 +12527,7 @@
         <v>200</v>
       </c>
       <c r="D325" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E325">
         <v>1</v>
@@ -12550,7 +12550,7 @@
         <v>200</v>
       </c>
       <c r="D326" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E326">
         <v>1</v>
@@ -12573,7 +12573,7 @@
         <v>200</v>
       </c>
       <c r="D327" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E327">
         <v>1</v>
@@ -12596,7 +12596,7 @@
         <v>200</v>
       </c>
       <c r="D328" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E328">
         <v>1</v>
@@ -12619,7 +12619,7 @@
         <v>200</v>
       </c>
       <c r="D329" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E329">
         <v>1</v>
@@ -12642,7 +12642,7 @@
         <v>200</v>
       </c>
       <c r="D330" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E330">
         <v>1</v>
@@ -12665,7 +12665,7 @@
         <v>200</v>
       </c>
       <c r="D331" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E331">
         <v>1</v>
@@ -12688,7 +12688,7 @@
         <v>200</v>
       </c>
       <c r="D332" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E332">
         <v>1</v>
@@ -12711,7 +12711,7 @@
         <v>200</v>
       </c>
       <c r="D333" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E333">
         <v>1</v>
@@ -12734,7 +12734,7 @@
         <v>200</v>
       </c>
       <c r="D334" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E334">
         <v>1</v>
@@ -12757,7 +12757,7 @@
         <v>200</v>
       </c>
       <c r="D335" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E335">
         <v>1</v>
@@ -12780,7 +12780,7 @@
         <v>200</v>
       </c>
       <c r="D336" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E336">
         <v>1</v>
@@ -12803,7 +12803,7 @@
         <v>200</v>
       </c>
       <c r="D337" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E337">
         <v>1</v>
@@ -12826,7 +12826,7 @@
         <v>200</v>
       </c>
       <c r="D338" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E338">
         <v>1</v>
@@ -12849,7 +12849,7 @@
         <v>200</v>
       </c>
       <c r="D339" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E339">
         <v>1</v>
@@ -12872,7 +12872,7 @@
         <v>200</v>
       </c>
       <c r="D340" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E340">
         <v>1</v>
@@ -12895,7 +12895,7 @@
         <v>200</v>
       </c>
       <c r="D341" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E341">
         <v>1</v>
@@ -12918,7 +12918,7 @@
         <v>200</v>
       </c>
       <c r="D342" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E342">
         <v>1</v>
@@ -12941,7 +12941,7 @@
         <v>200</v>
       </c>
       <c r="D343" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E343">
         <v>1</v>
@@ -12964,7 +12964,7 @@
         <v>200</v>
       </c>
       <c r="D344" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E344">
         <v>1</v>
@@ -12987,7 +12987,7 @@
         <v>200</v>
       </c>
       <c r="D345" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E345">
         <v>1</v>
@@ -13010,7 +13010,7 @@
         <v>200</v>
       </c>
       <c r="D346" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E346">
         <v>1</v>
@@ -13033,7 +13033,7 @@
         <v>200</v>
       </c>
       <c r="D347" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E347">
         <v>1</v>
@@ -13056,7 +13056,7 @@
         <v>748</v>
       </c>
       <c r="D348" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E348">
         <v>1</v>
@@ -13079,7 +13079,7 @@
         <v>200</v>
       </c>
       <c r="D349" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E349">
         <v>1</v>
@@ -13102,7 +13102,7 @@
         <v>200</v>
       </c>
       <c r="D350" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E350">
         <v>1</v>
@@ -13125,7 +13125,7 @@
         <v>200</v>
       </c>
       <c r="D351" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E351">
         <v>1</v>
@@ -13148,7 +13148,7 @@
         <v>200</v>
       </c>
       <c r="D352" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E352">
         <v>1</v>
@@ -13171,7 +13171,7 @@
         <v>200</v>
       </c>
       <c r="D353" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E353">
         <v>1</v>
@@ -13194,7 +13194,7 @@
         <v>200</v>
       </c>
       <c r="D354" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E354">
         <v>1</v>
@@ -13217,7 +13217,7 @@
         <v>200</v>
       </c>
       <c r="D355" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E355">
         <v>1</v>
@@ -13240,7 +13240,7 @@
         <v>200</v>
       </c>
       <c r="D356" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E356">
         <v>1</v>
@@ -13263,7 +13263,7 @@
         <v>200</v>
       </c>
       <c r="D357" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E357">
         <v>1</v>
@@ -13286,7 +13286,7 @@
         <v>200</v>
       </c>
       <c r="D358" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E358">
         <v>1</v>
@@ -13309,7 +13309,7 @@
         <v>200</v>
       </c>
       <c r="D359" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E359">
         <v>1</v>
@@ -13332,7 +13332,7 @@
         <v>200</v>
       </c>
       <c r="D360" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E360">
         <v>1</v>
@@ -13355,7 +13355,7 @@
         <v>200</v>
       </c>
       <c r="D361" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E361">
         <v>1</v>
@@ -13378,7 +13378,7 @@
         <v>200</v>
       </c>
       <c r="D362" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E362">
         <v>1</v>
@@ -13401,7 +13401,7 @@
         <v>200</v>
       </c>
       <c r="D363" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E363">
         <v>1</v>
@@ -13424,7 +13424,7 @@
         <v>200</v>
       </c>
       <c r="D364" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E364">
         <v>1</v>
@@ -13447,7 +13447,7 @@
         <v>200</v>
       </c>
       <c r="D365" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E365">
         <v>1</v>
@@ -13470,7 +13470,7 @@
         <v>200</v>
       </c>
       <c r="D366" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E366">
         <v>1</v>
@@ -13493,7 +13493,7 @@
         <v>200</v>
       </c>
       <c r="D367" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E367">
         <v>1</v>
@@ -13516,7 +13516,7 @@
         <v>200</v>
       </c>
       <c r="D368" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E368">
         <v>1</v>
@@ -13539,7 +13539,7 @@
         <v>748</v>
       </c>
       <c r="D369" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E369">
         <v>0</v>
@@ -13562,7 +13562,7 @@
         <v>748</v>
       </c>
       <c r="D370" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E370">
         <v>0</v>
@@ -13585,7 +13585,7 @@
         <v>748</v>
       </c>
       <c r="D371" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E371">
         <v>0</v>
@@ -13654,7 +13654,7 @@
         <v>748</v>
       </c>
       <c r="D374" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E374">
         <v>0</v>
@@ -13677,7 +13677,7 @@
         <v>748</v>
       </c>
       <c r="D375" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E375">
         <v>0</v>
@@ -13723,7 +13723,7 @@
         <v>748</v>
       </c>
       <c r="D377" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E377">
         <v>0</v>
@@ -13746,7 +13746,7 @@
         <v>748</v>
       </c>
       <c r="D378" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E378">
         <v>0</v>
@@ -13930,7 +13930,7 @@
         <v>748</v>
       </c>
       <c r="D386" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E386">
         <v>0</v>
@@ -14091,7 +14091,7 @@
         <v>748</v>
       </c>
       <c r="D393" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E393">
         <v>0</v>
@@ -14114,7 +14114,7 @@
         <v>1101</v>
       </c>
       <c r="D394" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E394">
         <v>1</v>
@@ -14505,7 +14505,7 @@
         <v>1101</v>
       </c>
       <c r="D411" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E411">
         <v>1</v>
@@ -14620,7 +14620,7 @@
         <v>8</v>
       </c>
       <c r="D416" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E416">
         <v>1</v>
@@ -14689,7 +14689,7 @@
         <v>8</v>
       </c>
       <c r="D419" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E419">
         <v>1</v>
@@ -14781,7 +14781,7 @@
         <v>8</v>
       </c>
       <c r="D423" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E423">
         <v>1</v>
@@ -14873,7 +14873,7 @@
         <v>8</v>
       </c>
       <c r="D427" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E427">
         <v>1</v>
@@ -14988,7 +14988,7 @@
         <v>8</v>
       </c>
       <c r="D432" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E432">
         <v>1</v>
@@ -15057,7 +15057,7 @@
         <v>8</v>
       </c>
       <c r="D435" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E435">
         <v>1</v>
@@ -15126,7 +15126,7 @@
         <v>8</v>
       </c>
       <c r="D438" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E438">
         <v>1</v>
@@ -15195,7 +15195,7 @@
         <v>8</v>
       </c>
       <c r="D441" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E441">
         <v>1</v>
@@ -15218,7 +15218,7 @@
         <v>200</v>
       </c>
       <c r="D442" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E442">
         <v>1</v>
@@ -15425,7 +15425,7 @@
         <v>200</v>
       </c>
       <c r="D451" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E451">
         <v>1</v>
@@ -15517,7 +15517,7 @@
         <v>200</v>
       </c>
       <c r="D455" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E455">
         <v>1</v>
@@ -15724,7 +15724,7 @@
         <v>200</v>
       </c>
       <c r="D464" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E464">
         <v>1</v>
@@ -15839,7 +15839,7 @@
         <v>200</v>
       </c>
       <c r="D469" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E469">
         <v>1</v>
@@ -15954,7 +15954,7 @@
         <v>200</v>
       </c>
       <c r="D474" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E474">
         <v>1</v>
@@ -16069,7 +16069,7 @@
         <v>200</v>
       </c>
       <c r="D479" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E479">
         <v>1</v>
@@ -16184,7 +16184,7 @@
         <v>200</v>
       </c>
       <c r="D484" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E484">
         <v>1</v>
@@ -16299,7 +16299,7 @@
         <v>200</v>
       </c>
       <c r="D489" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E489">
         <v>1</v>
@@ -16322,7 +16322,7 @@
         <v>200</v>
       </c>
       <c r="D490" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E490">
         <v>1</v>
@@ -16368,7 +16368,7 @@
         <v>200</v>
       </c>
       <c r="D492" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E492">
         <v>1</v>
@@ -16391,7 +16391,7 @@
         <v>200</v>
       </c>
       <c r="D493" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E493">
         <v>1</v>
@@ -16414,7 +16414,7 @@
         <v>200</v>
       </c>
       <c r="D494" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E494">
         <v>1</v>
@@ -16483,7 +16483,7 @@
         <v>200</v>
       </c>
       <c r="D497" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E497">
         <v>1</v>
@@ -16506,7 +16506,7 @@
         <v>200</v>
       </c>
       <c r="D498" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E498">
         <v>1</v>
@@ -16529,7 +16529,7 @@
         <v>200</v>
       </c>
       <c r="D499" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E499">
         <v>1</v>
@@ -16552,7 +16552,7 @@
         <v>200</v>
       </c>
       <c r="D500" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E500">
         <v>1</v>
@@ -16575,7 +16575,7 @@
         <v>200</v>
       </c>
       <c r="D501" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E501">
         <v>1</v>
@@ -16598,7 +16598,7 @@
         <v>200</v>
       </c>
       <c r="D502" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E502">
         <v>1</v>
@@ -16621,7 +16621,7 @@
         <v>200</v>
       </c>
       <c r="D503" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E503">
         <v>1</v>
@@ -16644,7 +16644,7 @@
         <v>200</v>
       </c>
       <c r="D504" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E504">
         <v>1</v>
@@ -16667,7 +16667,7 @@
         <v>200</v>
       </c>
       <c r="D505" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E505">
         <v>1</v>
@@ -16690,7 +16690,7 @@
         <v>200</v>
       </c>
       <c r="D506" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E506">
         <v>1</v>
@@ -16874,7 +16874,7 @@
         <v>200</v>
       </c>
       <c r="D514" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E514">
         <v>1</v>
@@ -16966,7 +16966,7 @@
         <v>200</v>
       </c>
       <c r="D518" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E518">
         <v>1</v>
@@ -17035,7 +17035,7 @@
         <v>200</v>
       </c>
       <c r="D521" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E521">
         <v>1</v>
@@ -17104,7 +17104,7 @@
         <v>200</v>
       </c>
       <c r="D524" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E524">
         <v>1</v>
@@ -17173,7 +17173,7 @@
         <v>200</v>
       </c>
       <c r="D527" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E527">
         <v>1</v>
@@ -17242,7 +17242,7 @@
         <v>200</v>
       </c>
       <c r="D530" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E530">
         <v>1</v>
@@ -17265,7 +17265,7 @@
         <v>200</v>
       </c>
       <c r="D531" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E531">
         <v>1</v>
@@ -17311,7 +17311,7 @@
         <v>200</v>
       </c>
       <c r="D533" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E533">
         <v>1</v>
@@ -17334,7 +17334,7 @@
         <v>200</v>
       </c>
       <c r="D534" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E534">
         <v>1</v>
@@ -17357,7 +17357,7 @@
         <v>200</v>
       </c>
       <c r="D535" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E535">
         <v>1</v>
@@ -17380,7 +17380,7 @@
         <v>200</v>
       </c>
       <c r="D536" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E536">
         <v>1</v>
@@ -17518,7 +17518,7 @@
         <v>200</v>
       </c>
       <c r="D542" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E542">
         <v>1</v>
@@ -17587,7 +17587,7 @@
         <v>200</v>
       </c>
       <c r="D545" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E545">
         <v>1</v>
@@ -17656,7 +17656,7 @@
         <v>200</v>
       </c>
       <c r="D548" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E548">
         <v>1</v>
@@ -17702,7 +17702,7 @@
         <v>200</v>
       </c>
       <c r="D550" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E550">
         <v>1</v>
@@ -17771,7 +17771,7 @@
         <v>200</v>
       </c>
       <c r="D553" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E553">
         <v>1</v>
@@ -17794,7 +17794,7 @@
         <v>200</v>
       </c>
       <c r="D554" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E554">
         <v>1</v>
@@ -17817,7 +17817,7 @@
         <v>200</v>
       </c>
       <c r="D555" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E555">
         <v>1</v>
@@ -17840,7 +17840,7 @@
         <v>200</v>
       </c>
       <c r="D556" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E556">
         <v>1</v>
@@ -17863,7 +17863,7 @@
         <v>200</v>
       </c>
       <c r="D557" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E557">
         <v>1</v>
@@ -17886,7 +17886,7 @@
         <v>200</v>
       </c>
       <c r="D558" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E558">
         <v>1</v>
@@ -17909,7 +17909,7 @@
         <v>200</v>
       </c>
       <c r="D559" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E559">
         <v>1</v>
@@ -17932,7 +17932,7 @@
         <v>200</v>
       </c>
       <c r="D560" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E560">
         <v>1</v>
@@ -17955,7 +17955,7 @@
         <v>200</v>
       </c>
       <c r="D561" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E561">
         <v>1</v>
@@ -17978,7 +17978,7 @@
         <v>200</v>
       </c>
       <c r="D562" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E562">
         <v>1</v>
@@ -18162,7 +18162,7 @@
         <v>200</v>
       </c>
       <c r="D570" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E570">
         <v>1</v>
@@ -18185,7 +18185,7 @@
         <v>200</v>
       </c>
       <c r="D571" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E571">
         <v>1</v>
@@ -18254,7 +18254,7 @@
         <v>200</v>
       </c>
       <c r="D574" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E574">
         <v>1</v>
@@ -18277,7 +18277,7 @@
         <v>200</v>
       </c>
       <c r="D575" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E575">
         <v>1</v>
@@ -18300,7 +18300,7 @@
         <v>200</v>
       </c>
       <c r="D576" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E576">
         <v>1</v>
@@ -18323,7 +18323,7 @@
         <v>200</v>
       </c>
       <c r="D577" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E577">
         <v>1</v>
@@ -18346,7 +18346,7 @@
         <v>200</v>
       </c>
       <c r="D578" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E578">
         <v>1</v>
@@ -18415,7 +18415,7 @@
         <v>200</v>
       </c>
       <c r="D581" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E581">
         <v>1</v>
@@ -18438,7 +18438,7 @@
         <v>200</v>
       </c>
       <c r="D582" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E582">
         <v>1</v>
@@ -18461,7 +18461,7 @@
         <v>200</v>
       </c>
       <c r="D583" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E583">
         <v>1</v>
@@ -18507,7 +18507,7 @@
         <v>200</v>
       </c>
       <c r="D585" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E585">
         <v>1</v>
@@ -18530,7 +18530,7 @@
         <v>200</v>
       </c>
       <c r="D586" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E586">
         <v>1</v>
@@ -18553,7 +18553,7 @@
         <v>200</v>
       </c>
       <c r="D587" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E587">
         <v>1</v>
@@ -18599,7 +18599,7 @@
         <v>200</v>
       </c>
       <c r="D589" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E589">
         <v>1</v>
@@ -18622,7 +18622,7 @@
         <v>200</v>
       </c>
       <c r="D590" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E590">
         <v>1</v>
@@ -18645,7 +18645,7 @@
         <v>200</v>
       </c>
       <c r="D591" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E591">
         <v>1</v>
@@ -18668,7 +18668,7 @@
         <v>200</v>
       </c>
       <c r="D592" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E592">
         <v>1</v>
@@ -18691,7 +18691,7 @@
         <v>200</v>
       </c>
       <c r="D593" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E593">
         <v>1</v>
@@ -18714,7 +18714,7 @@
         <v>200</v>
       </c>
       <c r="D594" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E594">
         <v>1</v>
@@ -18737,7 +18737,7 @@
         <v>200</v>
       </c>
       <c r="D595" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E595">
         <v>1</v>
@@ -18760,7 +18760,7 @@
         <v>200</v>
       </c>
       <c r="D596" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E596">
         <v>1</v>
@@ -18783,7 +18783,7 @@
         <v>200</v>
       </c>
       <c r="D597" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E597">
         <v>1</v>
@@ -18875,7 +18875,7 @@
         <v>200</v>
       </c>
       <c r="D601" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E601">
         <v>0</v>
@@ -18921,7 +18921,7 @@
         <v>200</v>
       </c>
       <c r="D603" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E603">
         <v>0</v>
@@ -18944,7 +18944,7 @@
         <v>200</v>
       </c>
       <c r="D604" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E604">
         <v>0</v>
@@ -20715,7 +20715,7 @@
         <v>200</v>
       </c>
       <c r="D681" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E681">
         <v>0</v>
@@ -20738,7 +20738,7 @@
         <v>200</v>
       </c>
       <c r="D682" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E682">
         <v>0</v>
@@ -20761,7 +20761,7 @@
         <v>200</v>
       </c>
       <c r="D683" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E683">
         <v>0</v>
@@ -20784,7 +20784,7 @@
         <v>200</v>
       </c>
       <c r="D684" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E684">
         <v>0</v>
@@ -20807,7 +20807,7 @@
         <v>748</v>
       </c>
       <c r="D685" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E685">
         <v>1</v>
@@ -20830,7 +20830,7 @@
         <v>748</v>
       </c>
       <c r="D686" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E686">
         <v>1</v>
@@ -20853,7 +20853,7 @@
         <v>748</v>
       </c>
       <c r="D687" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E687">
         <v>1</v>
@@ -20899,7 +20899,7 @@
         <v>748</v>
       </c>
       <c r="D689" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E689">
         <v>1</v>
@@ -20922,7 +20922,7 @@
         <v>748</v>
       </c>
       <c r="D690" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E690">
         <v>1</v>
@@ -20945,7 +20945,7 @@
         <v>748</v>
       </c>
       <c r="D691" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E691">
         <v>1</v>
@@ -20991,7 +20991,7 @@
         <v>748</v>
       </c>
       <c r="D693" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E693">
         <v>1</v>
@@ -21014,7 +21014,7 @@
         <v>748</v>
       </c>
       <c r="D694" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E694">
         <v>1</v>
@@ -21129,7 +21129,7 @@
         <v>748</v>
       </c>
       <c r="D699" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E699">
         <v>1</v>
@@ -21175,7 +21175,7 @@
         <v>748</v>
       </c>
       <c r="D701" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E701">
         <v>1</v>
@@ -21198,7 +21198,7 @@
         <v>748</v>
       </c>
       <c r="D702" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E702">
         <v>1</v>
@@ -21221,7 +21221,7 @@
         <v>748</v>
       </c>
       <c r="D703" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E703">
         <v>1</v>
@@ -21244,7 +21244,7 @@
         <v>748</v>
       </c>
       <c r="D704" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E704">
         <v>1</v>
@@ -21290,7 +21290,7 @@
         <v>748</v>
       </c>
       <c r="D706" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E706">
         <v>1</v>
@@ -21313,7 +21313,7 @@
         <v>748</v>
       </c>
       <c r="D707" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E707">
         <v>1</v>
@@ -21336,7 +21336,7 @@
         <v>748</v>
       </c>
       <c r="D708" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E708">
         <v>1</v>
@@ -21359,7 +21359,7 @@
         <v>748</v>
       </c>
       <c r="D709" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E709">
         <v>1</v>
@@ -21382,7 +21382,7 @@
         <v>748</v>
       </c>
       <c r="D710" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E710">
         <v>1</v>
@@ -21451,7 +21451,7 @@
         <v>748</v>
       </c>
       <c r="D713" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E713">
         <v>1</v>
@@ -21497,7 +21497,7 @@
         <v>748</v>
       </c>
       <c r="D715" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E715">
         <v>1</v>
@@ -21543,7 +21543,7 @@
         <v>748</v>
       </c>
       <c r="D717" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E717">
         <v>1</v>
@@ -21566,7 +21566,7 @@
         <v>748</v>
       </c>
       <c r="D718" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E718">
         <v>1</v>
@@ -21589,7 +21589,7 @@
         <v>748</v>
       </c>
       <c r="D719" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E719">
         <v>1</v>
@@ -21612,7 +21612,7 @@
         <v>748</v>
       </c>
       <c r="D720" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E720">
         <v>1</v>
@@ -21635,7 +21635,7 @@
         <v>748</v>
       </c>
       <c r="D721" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E721">
         <v>1</v>
@@ -21658,7 +21658,7 @@
         <v>748</v>
       </c>
       <c r="D722" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E722">
         <v>1</v>
@@ -21681,7 +21681,7 @@
         <v>748</v>
       </c>
       <c r="D723" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E723">
         <v>1</v>
@@ -21704,7 +21704,7 @@
         <v>748</v>
       </c>
       <c r="D724" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E724">
         <v>1</v>
@@ -21727,7 +21727,7 @@
         <v>748</v>
       </c>
       <c r="D725" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E725">
         <v>1</v>
@@ -21750,7 +21750,7 @@
         <v>748</v>
       </c>
       <c r="D726" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E726">
         <v>1</v>
@@ -21773,7 +21773,7 @@
         <v>748</v>
       </c>
       <c r="D727" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E727">
         <v>1</v>
@@ -21865,7 +21865,7 @@
         <v>748</v>
       </c>
       <c r="D731" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E731">
         <v>1</v>
@@ -21888,7 +21888,7 @@
         <v>748</v>
       </c>
       <c r="D732" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E732">
         <v>1</v>
@@ -21980,7 +21980,7 @@
         <v>748</v>
       </c>
       <c r="D736" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E736">
         <v>1</v>
@@ -22003,7 +22003,7 @@
         <v>748</v>
       </c>
       <c r="D737" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E737">
         <v>1</v>
@@ -22049,7 +22049,7 @@
         <v>748</v>
       </c>
       <c r="D739" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E739">
         <v>1</v>
@@ -22072,7 +22072,7 @@
         <v>748</v>
       </c>
       <c r="D740" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E740">
         <v>1</v>
@@ -22095,7 +22095,7 @@
         <v>748</v>
       </c>
       <c r="D741" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E741">
         <v>1</v>
@@ -22302,7 +22302,7 @@
         <v>748</v>
       </c>
       <c r="D750" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E750">
         <v>1</v>
@@ -22325,7 +22325,7 @@
         <v>748</v>
       </c>
       <c r="D751" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E751">
         <v>1</v>
@@ -22348,7 +22348,7 @@
         <v>748</v>
       </c>
       <c r="D752" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E752">
         <v>1</v>
@@ -22371,7 +22371,7 @@
         <v>748</v>
       </c>
       <c r="D753" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E753">
         <v>1</v>
@@ -22394,7 +22394,7 @@
         <v>748</v>
       </c>
       <c r="D754" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E754">
         <v>1</v>
@@ -22440,7 +22440,7 @@
         <v>748</v>
       </c>
       <c r="D756" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E756">
         <v>1</v>
@@ -22463,7 +22463,7 @@
         <v>748</v>
       </c>
       <c r="D757" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E757">
         <v>1</v>
@@ -22486,7 +22486,7 @@
         <v>748</v>
       </c>
       <c r="D758" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E758">
         <v>1</v>
@@ -22509,7 +22509,7 @@
         <v>748</v>
       </c>
       <c r="D759" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E759">
         <v>1</v>
@@ -22532,7 +22532,7 @@
         <v>748</v>
       </c>
       <c r="D760" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E760">
         <v>1</v>
@@ -22555,7 +22555,7 @@
         <v>748</v>
       </c>
       <c r="D761" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E761">
         <v>1</v>
@@ -22578,7 +22578,7 @@
         <v>748</v>
       </c>
       <c r="D762" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E762">
         <v>1</v>
@@ -22601,7 +22601,7 @@
         <v>748</v>
       </c>
       <c r="D763" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E763">
         <v>1</v>
@@ -22624,7 +22624,7 @@
         <v>748</v>
       </c>
       <c r="D764" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E764">
         <v>1</v>
@@ -22647,7 +22647,7 @@
         <v>748</v>
       </c>
       <c r="D765" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E765">
         <v>1</v>
@@ -22877,7 +22877,7 @@
         <v>748</v>
       </c>
       <c r="D775" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E775">
         <v>1</v>
@@ -22900,7 +22900,7 @@
         <v>748</v>
       </c>
       <c r="D776" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E776">
         <v>1</v>
@@ -22923,7 +22923,7 @@
         <v>748</v>
       </c>
       <c r="D777" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E777">
         <v>1</v>
@@ -22992,7 +22992,7 @@
         <v>1122</v>
       </c>
       <c r="D780" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E780">
         <v>1</v>
@@ -23015,7 +23015,7 @@
         <v>1122</v>
       </c>
       <c r="D781" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E781">
         <v>1</v>
@@ -23038,7 +23038,7 @@
         <v>1122</v>
       </c>
       <c r="D782" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E782">
         <v>1</v>
@@ -23061,7 +23061,7 @@
         <v>1122</v>
       </c>
       <c r="D783" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E783">
         <v>1</v>
@@ -23107,7 +23107,7 @@
         <v>1122</v>
       </c>
       <c r="D785" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E785">
         <v>1</v>
@@ -23130,7 +23130,7 @@
         <v>1122</v>
       </c>
       <c r="D786" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E786">
         <v>1</v>
@@ -23153,7 +23153,7 @@
         <v>1122</v>
       </c>
       <c r="D787" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E787">
         <v>1</v>
@@ -23176,7 +23176,7 @@
         <v>1122</v>
       </c>
       <c r="D788" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E788">
         <v>1</v>
@@ -23199,7 +23199,7 @@
         <v>1122</v>
       </c>
       <c r="D789" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E789">
         <v>1</v>
@@ -23222,7 +23222,7 @@
         <v>1122</v>
       </c>
       <c r="D790" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E790">
         <v>1</v>
@@ -23245,7 +23245,7 @@
         <v>1122</v>
       </c>
       <c r="D791" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E791">
         <v>1</v>
@@ -23268,7 +23268,7 @@
         <v>1122</v>
       </c>
       <c r="D792" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E792">
         <v>1</v>
@@ -23406,7 +23406,7 @@
         <v>1122</v>
       </c>
       <c r="D798" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E798">
         <v>1</v>
@@ -23429,7 +23429,7 @@
         <v>1122</v>
       </c>
       <c r="D799" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E799">
         <v>1</v>
@@ -23544,7 +23544,7 @@
         <v>1122</v>
       </c>
       <c r="D804" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E804">
         <v>1</v>
@@ -23636,7 +23636,7 @@
         <v>1122</v>
       </c>
       <c r="D808" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E808">
         <v>1</v>
@@ -23705,7 +23705,7 @@
         <v>1122</v>
       </c>
       <c r="D811" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E811">
         <v>1</v>
@@ -23728,7 +23728,7 @@
         <v>1122</v>
       </c>
       <c r="D812" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E812">
         <v>1</v>
@@ -23751,7 +23751,7 @@
         <v>1122</v>
       </c>
       <c r="D813" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E813">
         <v>1</v>
@@ -23820,7 +23820,7 @@
         <v>1122</v>
       </c>
       <c r="D816" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E816">
         <v>1</v>
@@ -23843,7 +23843,7 @@
         <v>1122</v>
       </c>
       <c r="D817" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E817">
         <v>1</v>
@@ -23889,7 +23889,7 @@
         <v>1122</v>
       </c>
       <c r="D819" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E819">
         <v>1</v>
@@ -24119,7 +24119,7 @@
         <v>1122</v>
       </c>
       <c r="D829" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E829">
         <v>1</v>
@@ -24142,7 +24142,7 @@
         <v>1122</v>
       </c>
       <c r="D830" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E830">
         <v>1</v>
@@ -24165,7 +24165,7 @@
         <v>1122</v>
       </c>
       <c r="D831" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E831">
         <v>1</v>
@@ -24188,7 +24188,7 @@
         <v>1122</v>
       </c>
       <c r="D832" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E832">
         <v>1</v>
@@ -24211,7 +24211,7 @@
         <v>1122</v>
       </c>
       <c r="D833" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E833">
         <v>1</v>
@@ -24234,7 +24234,7 @@
         <v>1122</v>
       </c>
       <c r="D834" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E834">
         <v>1</v>
@@ -24257,7 +24257,7 @@
         <v>1122</v>
       </c>
       <c r="D835" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E835">
         <v>1</v>
@@ -24280,7 +24280,7 @@
         <v>1122</v>
       </c>
       <c r="D836" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E836">
         <v>1</v>
@@ -24303,7 +24303,7 @@
         <v>1122</v>
       </c>
       <c r="D837" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E837">
         <v>1</v>
@@ -24349,7 +24349,7 @@
         <v>1122</v>
       </c>
       <c r="D839" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E839">
         <v>1</v>
@@ -24372,7 +24372,7 @@
         <v>1122</v>
       </c>
       <c r="D840" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E840">
         <v>1</v>
@@ -24395,7 +24395,7 @@
         <v>1122</v>
       </c>
       <c r="D841" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E841">
         <v>1</v>
@@ -24441,7 +24441,7 @@
         <v>1122</v>
       </c>
       <c r="D843" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E843">
         <v>1</v>
@@ -24464,7 +24464,7 @@
         <v>1122</v>
       </c>
       <c r="D844" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E844">
         <v>1</v>
@@ -24487,7 +24487,7 @@
         <v>1122</v>
       </c>
       <c r="D845" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E845">
         <v>1</v>
@@ -24510,7 +24510,7 @@
         <v>1122</v>
       </c>
       <c r="D846" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E846">
         <v>1</v>
@@ -24533,7 +24533,7 @@
         <v>1122</v>
       </c>
       <c r="D847" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E847">
         <v>1</v>
@@ -24556,7 +24556,7 @@
         <v>1122</v>
       </c>
       <c r="D848" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E848">
         <v>1</v>
@@ -24579,7 +24579,7 @@
         <v>1122</v>
       </c>
       <c r="D849" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E849">
         <v>1</v>
@@ -24602,7 +24602,7 @@
         <v>1122</v>
       </c>
       <c r="D850" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E850">
         <v>1</v>
@@ -24625,7 +24625,7 @@
         <v>1122</v>
       </c>
       <c r="D851" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E851">
         <v>1</v>
@@ -24648,7 +24648,7 @@
         <v>1122</v>
       </c>
       <c r="D852" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E852">
         <v>1</v>
@@ -24671,7 +24671,7 @@
         <v>1122</v>
       </c>
       <c r="D853" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E853">
         <v>1</v>
@@ -24694,7 +24694,7 @@
         <v>1122</v>
       </c>
       <c r="D854" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E854">
         <v>1</v>
@@ -24717,7 +24717,7 @@
         <v>1122</v>
       </c>
       <c r="D855" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E855">
         <v>1</v>
@@ -24740,7 +24740,7 @@
         <v>1122</v>
       </c>
       <c r="D856" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E856">
         <v>1</v>
@@ -24763,7 +24763,7 @@
         <v>1122</v>
       </c>
       <c r="D857" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E857">
         <v>1</v>
@@ -24786,7 +24786,7 @@
         <v>1122</v>
       </c>
       <c r="D858" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E858">
         <v>1</v>
@@ -24809,7 +24809,7 @@
         <v>1122</v>
       </c>
       <c r="D859" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E859">
         <v>1</v>
@@ -24832,7 +24832,7 @@
         <v>1122</v>
       </c>
       <c r="D860" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E860">
         <v>1</v>
@@ -24855,7 +24855,7 @@
         <v>1122</v>
       </c>
       <c r="D861" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E861">
         <v>1</v>
@@ -24878,7 +24878,7 @@
         <v>1122</v>
       </c>
       <c r="D862" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E862">
         <v>1</v>
@@ -24901,7 +24901,7 @@
         <v>1122</v>
       </c>
       <c r="D863" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E863">
         <v>1</v>
@@ -24924,7 +24924,7 @@
         <v>1122</v>
       </c>
       <c r="D864" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E864">
         <v>1</v>
@@ -24947,7 +24947,7 @@
         <v>1122</v>
       </c>
       <c r="D865" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E865">
         <v>1</v>
@@ -24970,7 +24970,7 @@
         <v>1122</v>
       </c>
       <c r="D866" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E866">
         <v>1</v>
@@ -24993,7 +24993,7 @@
         <v>1122</v>
       </c>
       <c r="D867" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E867">
         <v>1</v>
@@ -25016,7 +25016,7 @@
         <v>1122</v>
       </c>
       <c r="D868" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E868">
         <v>1</v>
@@ -25039,7 +25039,7 @@
         <v>1122</v>
       </c>
       <c r="D869" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E869">
         <v>1</v>
@@ -25062,7 +25062,7 @@
         <v>1122</v>
       </c>
       <c r="D870" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E870">
         <v>1</v>
@@ -25085,7 +25085,7 @@
         <v>939</v>
       </c>
       <c r="D871" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E871">
         <v>1</v>
@@ -25108,7 +25108,7 @@
         <v>939</v>
       </c>
       <c r="D872" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E872">
         <v>1</v>
@@ -25131,7 +25131,7 @@
         <v>939</v>
       </c>
       <c r="D873" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E873">
         <v>1</v>
@@ -25177,7 +25177,7 @@
         <v>939</v>
       </c>
       <c r="D875" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E875">
         <v>1</v>
@@ -25200,7 +25200,7 @@
         <v>939</v>
       </c>
       <c r="D876" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E876">
         <v>1</v>
@@ -25223,7 +25223,7 @@
         <v>939</v>
       </c>
       <c r="D877" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E877">
         <v>1</v>
@@ -25246,7 +25246,7 @@
         <v>939</v>
       </c>
       <c r="D878" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E878">
         <v>1</v>
@@ -25269,7 +25269,7 @@
         <v>939</v>
       </c>
       <c r="D879" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E879">
         <v>1</v>
@@ -25292,7 +25292,7 @@
         <v>939</v>
       </c>
       <c r="D880" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E880">
         <v>1</v>
@@ -25315,7 +25315,7 @@
         <v>939</v>
       </c>
       <c r="D881" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E881">
         <v>1</v>
@@ -25338,7 +25338,7 @@
         <v>939</v>
       </c>
       <c r="D882" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E882">
         <v>1</v>
@@ -25361,7 +25361,7 @@
         <v>939</v>
       </c>
       <c r="D883" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E883">
         <v>1</v>
@@ -25384,7 +25384,7 @@
         <v>939</v>
       </c>
       <c r="D884" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E884">
         <v>1</v>
@@ -25407,7 +25407,7 @@
         <v>939</v>
       </c>
       <c r="D885" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E885">
         <v>1</v>
@@ -25430,7 +25430,7 @@
         <v>939</v>
       </c>
       <c r="D886" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E886">
         <v>1</v>
@@ -25453,7 +25453,7 @@
         <v>939</v>
       </c>
       <c r="D887" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E887">
         <v>1</v>
@@ -25476,7 +25476,7 @@
         <v>939</v>
       </c>
       <c r="D888" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E888">
         <v>1</v>
@@ -25499,7 +25499,7 @@
         <v>939</v>
       </c>
       <c r="D889" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E889">
         <v>1</v>
@@ -25522,7 +25522,7 @@
         <v>939</v>
       </c>
       <c r="D890" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E890">
         <v>1</v>
@@ -25545,7 +25545,7 @@
         <v>939</v>
       </c>
       <c r="D891" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E891">
         <v>1</v>
@@ -25568,7 +25568,7 @@
         <v>939</v>
       </c>
       <c r="D892" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E892">
         <v>1</v>
@@ -25591,7 +25591,7 @@
         <v>939</v>
       </c>
       <c r="D893" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E893">
         <v>1</v>
@@ -25614,7 +25614,7 @@
         <v>939</v>
       </c>
       <c r="D894" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E894">
         <v>1</v>
@@ -25637,7 +25637,7 @@
         <v>939</v>
       </c>
       <c r="D895" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E895">
         <v>1</v>
@@ -25660,7 +25660,7 @@
         <v>939</v>
       </c>
       <c r="D896" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E896">
         <v>1</v>
@@ -25683,7 +25683,7 @@
         <v>939</v>
       </c>
       <c r="D897" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E897">
         <v>1</v>
@@ -25752,7 +25752,7 @@
         <v>968</v>
       </c>
       <c r="D900" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E900">
         <v>1</v>
@@ -25775,7 +25775,7 @@
         <v>968</v>
       </c>
       <c r="D901" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E901">
         <v>1</v>
@@ -25798,7 +25798,7 @@
         <v>968</v>
       </c>
       <c r="D902" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E902">
         <v>1</v>
@@ -25821,7 +25821,7 @@
         <v>968</v>
       </c>
       <c r="D903" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E903">
         <v>1</v>
@@ -25890,7 +25890,7 @@
         <v>968</v>
       </c>
       <c r="D906" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E906">
         <v>1</v>
@@ -25913,7 +25913,7 @@
         <v>968</v>
       </c>
       <c r="D907" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E907">
         <v>1</v>
@@ -25936,7 +25936,7 @@
         <v>968</v>
       </c>
       <c r="D908" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E908">
         <v>1</v>
@@ -26097,7 +26097,7 @@
         <v>968</v>
       </c>
       <c r="D915" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E915">
         <v>1</v>
@@ -26166,7 +26166,7 @@
         <v>968</v>
       </c>
       <c r="D918" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E918">
         <v>1</v>
@@ -26189,7 +26189,7 @@
         <v>968</v>
       </c>
       <c r="D919" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E919">
         <v>1</v>
@@ -26212,7 +26212,7 @@
         <v>968</v>
       </c>
       <c r="D920" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E920">
         <v>1</v>
@@ -26235,7 +26235,7 @@
         <v>968</v>
       </c>
       <c r="D921" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E921">
         <v>1</v>
@@ -26327,7 +26327,7 @@
         <v>968</v>
       </c>
       <c r="D925" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E925">
         <v>1</v>
@@ -26350,7 +26350,7 @@
         <v>968</v>
       </c>
       <c r="D926" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E926">
         <v>1</v>
@@ -26419,7 +26419,7 @@
         <v>968</v>
       </c>
       <c r="D929" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E929">
         <v>1</v>
@@ -26511,7 +26511,7 @@
         <v>968</v>
       </c>
       <c r="D933" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E933">
         <v>1</v>
@@ -26534,7 +26534,7 @@
         <v>968</v>
       </c>
       <c r="D934" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E934">
         <v>1</v>
@@ -26557,7 +26557,7 @@
         <v>968</v>
       </c>
       <c r="D935" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E935">
         <v>1</v>
@@ -26672,7 +26672,7 @@
         <v>968</v>
       </c>
       <c r="D940" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E940">
         <v>1</v>
@@ -26718,7 +26718,7 @@
         <v>968</v>
       </c>
       <c r="D942" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E942">
         <v>1</v>
@@ -26741,7 +26741,7 @@
         <v>968</v>
       </c>
       <c r="D943" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E943">
         <v>1</v>
@@ -26758,7 +26758,7 @@
         <v>250210</v>
       </c>
       <c r="B944" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="C944" t="s">
         <v>433</v>
@@ -26787,7 +26787,7 @@
         <v>1075</v>
       </c>
       <c r="D945" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E945">
         <v>1</v>
@@ -26810,7 +26810,7 @@
         <v>968</v>
       </c>
       <c r="D946" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E946">
         <v>1</v>
@@ -26833,7 +26833,7 @@
         <v>968</v>
       </c>
       <c r="D947" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E947">
         <v>1</v>
@@ -26856,7 +26856,7 @@
         <v>1075</v>
       </c>
       <c r="D948" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E948">
         <v>1</v>
@@ -26879,7 +26879,7 @@
         <v>968</v>
       </c>
       <c r="D949" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E949">
         <v>1</v>
@@ -26902,7 +26902,7 @@
         <v>968</v>
       </c>
       <c r="D950" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E950">
         <v>1</v>
@@ -26925,7 +26925,7 @@
         <v>1075</v>
       </c>
       <c r="D951" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E951">
         <v>1</v>
@@ -26948,7 +26948,7 @@
         <v>1075</v>
       </c>
       <c r="D952" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E952">
         <v>1</v>
@@ -26971,7 +26971,7 @@
         <v>968</v>
       </c>
       <c r="D953" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E953">
         <v>1</v>
@@ -26994,7 +26994,7 @@
         <v>968</v>
       </c>
       <c r="D954" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E954">
         <v>1</v>
@@ -27017,7 +27017,7 @@
         <v>968</v>
       </c>
       <c r="D955" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E955">
         <v>1</v>
@@ -27040,7 +27040,7 @@
         <v>1075</v>
       </c>
       <c r="D956" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E956">
         <v>1</v>
@@ -27063,7 +27063,7 @@
         <v>1075</v>
       </c>
       <c r="D957" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E957">
         <v>1</v>
@@ -27086,7 +27086,7 @@
         <v>968</v>
       </c>
       <c r="D958" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E958">
         <v>1</v>
@@ -27109,7 +27109,7 @@
         <v>1075</v>
       </c>
       <c r="D959" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E959">
         <v>1</v>
@@ -27132,7 +27132,7 @@
         <v>968</v>
       </c>
       <c r="D960" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E960">
         <v>1</v>
@@ -27155,7 +27155,7 @@
         <v>968</v>
       </c>
       <c r="D961" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E961">
         <v>1</v>
@@ -27178,7 +27178,7 @@
         <v>1075</v>
       </c>
       <c r="D962" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E962">
         <v>0</v>
@@ -27201,7 +27201,7 @@
         <v>968</v>
       </c>
       <c r="D963" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E963">
         <v>1</v>
@@ -27224,7 +27224,7 @@
         <v>1075</v>
       </c>
       <c r="D964" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E964">
         <v>0</v>
@@ -27247,7 +27247,7 @@
         <v>1046</v>
       </c>
       <c r="D965" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E965">
         <v>1</v>
@@ -27270,7 +27270,7 @@
         <v>1046</v>
       </c>
       <c r="D966" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E966">
         <v>1</v>
@@ -27293,7 +27293,7 @@
         <v>1046</v>
       </c>
       <c r="D967" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E967">
         <v>1</v>
@@ -27316,7 +27316,7 @@
         <v>1046</v>
       </c>
       <c r="D968" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E968">
         <v>1</v>
@@ -27339,7 +27339,7 @@
         <v>968</v>
       </c>
       <c r="D969" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E969">
         <v>1</v>
@@ -27362,7 +27362,7 @@
         <v>968</v>
       </c>
       <c r="D970" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E970">
         <v>1</v>
@@ -27385,7 +27385,7 @@
         <v>968</v>
       </c>
       <c r="D971" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E971">
         <v>1</v>
@@ -27408,7 +27408,7 @@
         <v>968</v>
       </c>
       <c r="D972" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E972">
         <v>1</v>
@@ -27431,7 +27431,7 @@
         <v>968</v>
       </c>
       <c r="D973" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E973">
         <v>1</v>
@@ -27454,7 +27454,7 @@
         <v>968</v>
       </c>
       <c r="D974" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E974">
         <v>1</v>
@@ -27477,7 +27477,7 @@
         <v>968</v>
       </c>
       <c r="D975" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E975">
         <v>1</v>
@@ -27500,7 +27500,7 @@
         <v>1046</v>
       </c>
       <c r="D976" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E976">
         <v>1</v>
@@ -27523,7 +27523,7 @@
         <v>1046</v>
       </c>
       <c r="D977" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E977">
         <v>1</v>
@@ -27546,7 +27546,7 @@
         <v>1046</v>
       </c>
       <c r="D978" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E978">
         <v>1</v>
@@ -27569,7 +27569,7 @@
         <v>1046</v>
       </c>
       <c r="D979" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E979">
         <v>1</v>
@@ -27592,7 +27592,7 @@
         <v>1046</v>
       </c>
       <c r="D980" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E980">
         <v>1</v>
@@ -27615,7 +27615,7 @@
         <v>1046</v>
       </c>
       <c r="D981" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E981">
         <v>1</v>
@@ -27638,7 +27638,7 @@
         <v>1046</v>
       </c>
       <c r="D982" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E982">
         <v>1</v>
@@ -27661,7 +27661,7 @@
         <v>1046</v>
       </c>
       <c r="D983" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E983">
         <v>1</v>
@@ -27684,7 +27684,7 @@
         <v>1046</v>
       </c>
       <c r="D984" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E984">
         <v>1</v>
@@ -27707,7 +27707,7 @@
         <v>1046</v>
       </c>
       <c r="D985" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E985">
         <v>1</v>
@@ -27730,7 +27730,7 @@
         <v>1046</v>
       </c>
       <c r="D986" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E986">
         <v>1</v>
@@ -27753,7 +27753,7 @@
         <v>1046</v>
       </c>
       <c r="D987" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E987">
         <v>1</v>
@@ -27776,7 +27776,7 @@
         <v>1046</v>
       </c>
       <c r="D988" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E988">
         <v>1</v>
@@ -27799,7 +27799,7 @@
         <v>1046</v>
       </c>
       <c r="D989" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E989">
         <v>1</v>
@@ -27822,7 +27822,7 @@
         <v>1046</v>
       </c>
       <c r="D990" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E990">
         <v>1</v>
@@ -27845,7 +27845,7 @@
         <v>1046</v>
       </c>
       <c r="D991" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E991">
         <v>1</v>
@@ -27868,7 +27868,7 @@
         <v>1046</v>
       </c>
       <c r="D992" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E992">
         <v>1</v>
@@ -27891,7 +27891,7 @@
         <v>1046</v>
       </c>
       <c r="D993" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E993">
         <v>1</v>
@@ -27914,7 +27914,7 @@
         <v>1046</v>
       </c>
       <c r="D994" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E994">
         <v>1</v>
@@ -27937,7 +27937,7 @@
         <v>1046</v>
       </c>
       <c r="D995" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E995">
         <v>1</v>
@@ -27960,7 +27960,7 @@
         <v>1046</v>
       </c>
       <c r="D996" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E996">
         <v>1</v>
@@ -27983,7 +27983,7 @@
         <v>1046</v>
       </c>
       <c r="D997" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E997">
         <v>1</v>
@@ -28006,7 +28006,7 @@
         <v>1046</v>
       </c>
       <c r="D998" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E998">
         <v>0</v>
@@ -28018,7 +28018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="999" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="999" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A999">
         <v>460902</v>
       </c>
@@ -28026,10 +28026,10 @@
         <v>77</v>
       </c>
       <c r="C999" t="s">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="D999" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E999">
         <v>1</v>
@@ -28052,7 +28052,7 @@
         <v>1046</v>
       </c>
       <c r="D1000" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E1000">
         <v>1</v>
@@ -28064,7 +28064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1001" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1001" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1001">
         <v>520902</v>
       </c>
@@ -28072,10 +28072,10 @@
         <v>146</v>
       </c>
       <c r="C1001" t="s">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="D1001" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E1001">
         <v>1</v>
@@ -28098,7 +28098,7 @@
         <v>1122</v>
       </c>
       <c r="D1002" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1002">
         <v>1</v>
@@ -28121,7 +28121,7 @@
         <v>1046</v>
       </c>
       <c r="D1003" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E1003">
         <v>1</v>
@@ -28144,7 +28144,7 @@
         <v>1075</v>
       </c>
       <c r="D1004" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E1004">
         <v>1</v>
@@ -28167,7 +28167,7 @@
         <v>1075</v>
       </c>
       <c r="D1005" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E1005">
         <v>1</v>
@@ -28190,7 +28190,7 @@
         <v>1122</v>
       </c>
       <c r="D1006" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1006">
         <v>1</v>
@@ -28213,7 +28213,7 @@
         <v>1075</v>
       </c>
       <c r="D1007" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E1007">
         <v>1</v>
@@ -28236,7 +28236,7 @@
         <v>1075</v>
       </c>
       <c r="D1008" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E1008">
         <v>1</v>
@@ -28259,7 +28259,7 @@
         <v>1122</v>
       </c>
       <c r="D1009" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1009">
         <v>1</v>
@@ -28282,7 +28282,7 @@
         <v>1122</v>
       </c>
       <c r="D1010" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1010">
         <v>1</v>
@@ -28305,7 +28305,7 @@
         <v>1122</v>
       </c>
       <c r="D1011" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1011">
         <v>1</v>
@@ -28328,7 +28328,7 @@
         <v>1122</v>
       </c>
       <c r="D1012" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1012">
         <v>1</v>
@@ -28351,7 +28351,7 @@
         <v>1122</v>
       </c>
       <c r="D1013" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1013">
         <v>1</v>
@@ -28374,7 +28374,7 @@
         <v>1122</v>
       </c>
       <c r="D1014" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1014">
         <v>1</v>
@@ -28397,7 +28397,7 @@
         <v>1075</v>
       </c>
       <c r="D1015" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E1015">
         <v>1</v>
@@ -28420,7 +28420,7 @@
         <v>1075</v>
       </c>
       <c r="D1016" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="E1016">
         <v>1</v>
@@ -28443,7 +28443,7 @@
         <v>1122</v>
       </c>
       <c r="D1017" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1017">
         <v>1</v>
@@ -28466,7 +28466,7 @@
         <v>1122</v>
       </c>
       <c r="D1018" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1018">
         <v>1</v>
@@ -28489,7 +28489,7 @@
         <v>1089</v>
       </c>
       <c r="D1019" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E1019">
         <v>1</v>
@@ -28512,7 +28512,7 @@
         <v>1089</v>
       </c>
       <c r="D1020" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E1020">
         <v>1</v>
@@ -28535,7 +28535,7 @@
         <v>1089</v>
       </c>
       <c r="D1021" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E1021">
         <v>1</v>
@@ -28558,7 +28558,7 @@
         <v>1089</v>
       </c>
       <c r="D1022" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E1022">
         <v>1</v>
@@ -28581,7 +28581,7 @@
         <v>1122</v>
       </c>
       <c r="D1023" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1023">
         <v>1</v>
@@ -28604,7 +28604,7 @@
         <v>1089</v>
       </c>
       <c r="D1024" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E1024">
         <v>1</v>
@@ -28627,7 +28627,7 @@
         <v>1089</v>
       </c>
       <c r="D1025" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E1025">
         <v>1</v>
@@ -28650,7 +28650,7 @@
         <v>1122</v>
       </c>
       <c r="D1026" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1026">
         <v>1</v>
@@ -28673,7 +28673,7 @@
         <v>1122</v>
       </c>
       <c r="D1027" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1027">
         <v>1</v>
@@ -28696,7 +28696,7 @@
         <v>1122</v>
       </c>
       <c r="D1028" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1028">
         <v>1</v>
@@ -28719,7 +28719,7 @@
         <v>1101</v>
       </c>
       <c r="D1029" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E1029">
         <v>1</v>
@@ -28742,7 +28742,7 @@
         <v>1101</v>
       </c>
       <c r="D1030" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E1030">
         <v>1</v>
@@ -28765,7 +28765,7 @@
         <v>1122</v>
       </c>
       <c r="D1031" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1031">
         <v>1</v>
@@ -28788,7 +28788,7 @@
         <v>1101</v>
       </c>
       <c r="D1032" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E1032">
         <v>1</v>
@@ -28811,7 +28811,7 @@
         <v>1101</v>
       </c>
       <c r="D1033" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E1033">
         <v>1</v>
@@ -28834,7 +28834,7 @@
         <v>1101</v>
       </c>
       <c r="D1034" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E1034">
         <v>1</v>
@@ -28857,7 +28857,7 @@
         <v>1101</v>
       </c>
       <c r="D1035" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E1035">
         <v>1</v>
@@ -28880,7 +28880,7 @@
         <v>1101</v>
       </c>
       <c r="D1036" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E1036">
         <v>1</v>
@@ -28903,7 +28903,7 @@
         <v>1101</v>
       </c>
       <c r="D1037" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E1037">
         <v>1</v>
@@ -28926,7 +28926,7 @@
         <v>1112</v>
       </c>
       <c r="D1038" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1038">
         <v>1</v>
@@ -28949,7 +28949,7 @@
         <v>1112</v>
       </c>
       <c r="D1039" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1039">
         <v>1</v>
@@ -28972,7 +28972,7 @@
         <v>1112</v>
       </c>
       <c r="D1040" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1040">
         <v>1</v>
@@ -28995,7 +28995,7 @@
         <v>1112</v>
       </c>
       <c r="D1041" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1041">
         <v>1</v>
@@ -29018,7 +29018,7 @@
         <v>1112</v>
       </c>
       <c r="D1042" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1042">
         <v>1</v>
@@ -29041,7 +29041,7 @@
         <v>1112</v>
       </c>
       <c r="D1043" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1043">
         <v>1</v>
@@ -29064,7 +29064,7 @@
         <v>1112</v>
       </c>
       <c r="D1044" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1044">
         <v>1</v>
@@ -29087,7 +29087,7 @@
         <v>1112</v>
       </c>
       <c r="D1045" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1045">
         <v>1</v>
@@ -29110,7 +29110,7 @@
         <v>1122</v>
       </c>
       <c r="D1046" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1046">
         <v>1</v>
@@ -29133,7 +29133,7 @@
         <v>1122</v>
       </c>
       <c r="D1047" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1047">
         <v>1</v>
@@ -29156,7 +29156,7 @@
         <v>1122</v>
       </c>
       <c r="D1048" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1048">
         <v>1</v>
@@ -29179,7 +29179,7 @@
         <v>1122</v>
       </c>
       <c r="D1049" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1049">
         <v>1</v>
@@ -29202,7 +29202,7 @@
         <v>1122</v>
       </c>
       <c r="D1050" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1050">
         <v>1</v>
@@ -29225,7 +29225,7 @@
         <v>1122</v>
       </c>
       <c r="D1051" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1051">
         <v>1</v>
@@ -29248,7 +29248,7 @@
         <v>1122</v>
       </c>
       <c r="D1052" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1052">
         <v>1</v>
@@ -29271,7 +29271,7 @@
         <v>1122</v>
       </c>
       <c r="D1053" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1053">
         <v>1</v>
@@ -29294,7 +29294,7 @@
         <v>1122</v>
       </c>
       <c r="D1054" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1054">
         <v>1</v>
@@ -29317,7 +29317,7 @@
         <v>1122</v>
       </c>
       <c r="D1055" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1055">
         <v>1</v>
@@ -29340,7 +29340,7 @@
         <v>1122</v>
       </c>
       <c r="D1056" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1056">
         <v>1</v>
@@ -29363,7 +29363,7 @@
         <v>1122</v>
       </c>
       <c r="D1057" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1057">
         <v>1</v>
@@ -29386,7 +29386,7 @@
         <v>1122</v>
       </c>
       <c r="D1058" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1058">
         <v>1</v>
@@ -29409,7 +29409,7 @@
         <v>1122</v>
       </c>
       <c r="D1059" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1059">
         <v>1</v>
@@ -29432,7 +29432,7 @@
         <v>1122</v>
       </c>
       <c r="D1060" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1060">
         <v>1</v>
@@ -29455,7 +29455,7 @@
         <v>1122</v>
       </c>
       <c r="D1061" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1061">
         <v>1</v>
@@ -29478,7 +29478,7 @@
         <v>1122</v>
       </c>
       <c r="D1062" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1062">
         <v>1</v>
@@ -29501,7 +29501,7 @@
         <v>1122</v>
       </c>
       <c r="D1063" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1063">
         <v>1</v>
@@ -29524,7 +29524,7 @@
         <v>1122</v>
       </c>
       <c r="D1064" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1064">
         <v>1</v>
@@ -29547,7 +29547,7 @@
         <v>1122</v>
       </c>
       <c r="D1065" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1065">
         <v>1</v>
@@ -29570,7 +29570,7 @@
         <v>1122</v>
       </c>
       <c r="D1066" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1066">
         <v>1</v>
@@ -29593,7 +29593,7 @@
         <v>1122</v>
       </c>
       <c r="D1067" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1067">
         <v>1</v>
@@ -29616,7 +29616,7 @@
         <v>1122</v>
       </c>
       <c r="D1068" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1068">
         <v>1</v>
@@ -29639,7 +29639,7 @@
         <v>1122</v>
       </c>
       <c r="D1069" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1069">
         <v>1</v>
@@ -29662,7 +29662,7 @@
         <v>1122</v>
       </c>
       <c r="D1070" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1070">
         <v>1</v>
@@ -29685,7 +29685,7 @@
         <v>1122</v>
       </c>
       <c r="D1071" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1071">
         <v>1</v>
@@ -29708,7 +29708,7 @@
         <v>1122</v>
       </c>
       <c r="D1072" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1072">
         <v>1</v>
@@ -29731,7 +29731,7 @@
         <v>1122</v>
       </c>
       <c r="D1073" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1073">
         <v>1</v>
@@ -29754,7 +29754,7 @@
         <v>1122</v>
       </c>
       <c r="D1074" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1074">
         <v>1</v>
@@ -29777,7 +29777,7 @@
         <v>1122</v>
       </c>
       <c r="D1075" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1075">
         <v>1</v>
@@ -29800,7 +29800,7 @@
         <v>1122</v>
       </c>
       <c r="D1076" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1076">
         <v>1</v>
@@ -29823,7 +29823,7 @@
         <v>1122</v>
       </c>
       <c r="D1077" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1077">
         <v>1</v>
@@ -29846,7 +29846,7 @@
         <v>1122</v>
       </c>
       <c r="D1078" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1078">
         <v>1</v>
@@ -29869,7 +29869,7 @@
         <v>1122</v>
       </c>
       <c r="D1079" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1079">
         <v>1</v>
@@ -29892,7 +29892,7 @@
         <v>1122</v>
       </c>
       <c r="D1080" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1080">
         <v>1</v>
@@ -29915,7 +29915,7 @@
         <v>1122</v>
       </c>
       <c r="D1081" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1081">
         <v>1</v>
@@ -29938,7 +29938,7 @@
         <v>1122</v>
       </c>
       <c r="D1082" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1082">
         <v>1</v>
@@ -29961,7 +29961,7 @@
         <v>1122</v>
       </c>
       <c r="D1083" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1083">
         <v>1</v>
@@ -29984,7 +29984,7 @@
         <v>1122</v>
       </c>
       <c r="D1084" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1084">
         <v>1</v>
@@ -30007,7 +30007,7 @@
         <v>1122</v>
       </c>
       <c r="D1085" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1085">
         <v>1</v>
@@ -30030,7 +30030,7 @@
         <v>1122</v>
       </c>
       <c r="D1086" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1086">
         <v>1</v>
@@ -30053,7 +30053,7 @@
         <v>1122</v>
       </c>
       <c r="D1087" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1087">
         <v>1</v>
@@ -30076,7 +30076,7 @@
         <v>1122</v>
       </c>
       <c r="D1088" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1088">
         <v>1</v>
@@ -30099,7 +30099,7 @@
         <v>1122</v>
       </c>
       <c r="D1089" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1089">
         <v>1</v>
@@ -30122,7 +30122,7 @@
         <v>1122</v>
       </c>
       <c r="D1090" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1090">
         <v>1</v>
@@ -30145,7 +30145,7 @@
         <v>1122</v>
       </c>
       <c r="D1091" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1091">
         <v>1</v>
@@ -30168,7 +30168,7 @@
         <v>1122</v>
       </c>
       <c r="D1092" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1092">
         <v>1</v>
@@ -30191,7 +30191,7 @@
         <v>1122</v>
       </c>
       <c r="D1093" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1093">
         <v>1</v>
@@ -30214,7 +30214,7 @@
         <v>1122</v>
       </c>
       <c r="D1094" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1094">
         <v>1</v>
@@ -30237,7 +30237,7 @@
         <v>1122</v>
       </c>
       <c r="D1095" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1095">
         <v>1</v>
@@ -30260,7 +30260,7 @@
         <v>1122</v>
       </c>
       <c r="D1096" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1096">
         <v>1</v>
@@ -30283,7 +30283,7 @@
         <v>1122</v>
       </c>
       <c r="D1097" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1097">
         <v>1</v>
@@ -30306,7 +30306,7 @@
         <v>1122</v>
       </c>
       <c r="D1098" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1098">
         <v>1</v>
@@ -30329,7 +30329,7 @@
         <v>1122</v>
       </c>
       <c r="D1099" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1099">
         <v>1</v>
@@ -30352,7 +30352,7 @@
         <v>1122</v>
       </c>
       <c r="D1100" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1100">
         <v>1</v>
@@ -30375,7 +30375,7 @@
         <v>1122</v>
       </c>
       <c r="D1101" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1101">
         <v>1</v>
@@ -30398,7 +30398,7 @@
         <v>1122</v>
       </c>
       <c r="D1102" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1102">
         <v>1</v>
@@ -30421,7 +30421,7 @@
         <v>1122</v>
       </c>
       <c r="D1103" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1103">
         <v>1</v>
@@ -30444,7 +30444,7 @@
         <v>1122</v>
       </c>
       <c r="D1104" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1104">
         <v>1</v>
@@ -30467,7 +30467,7 @@
         <v>1122</v>
       </c>
       <c r="D1105" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1105">
         <v>1</v>
@@ -30490,7 +30490,7 @@
         <v>845</v>
       </c>
       <c r="D1106" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1106">
         <v>1</v>
@@ -30513,7 +30513,7 @@
         <v>845</v>
       </c>
       <c r="D1107" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1107">
         <v>1</v>
@@ -30536,7 +30536,7 @@
         <v>845</v>
       </c>
       <c r="D1108" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1108">
         <v>1</v>
@@ -30559,7 +30559,7 @@
         <v>845</v>
       </c>
       <c r="D1109" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1109">
         <v>1</v>
@@ -30582,7 +30582,7 @@
         <v>845</v>
       </c>
       <c r="D1110" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1110">
         <v>1</v>
@@ -30605,7 +30605,7 @@
         <v>845</v>
       </c>
       <c r="D1111" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1111">
         <v>1</v>
@@ -30628,7 +30628,7 @@
         <v>845</v>
       </c>
       <c r="D1112" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1112">
         <v>1</v>
@@ -30651,7 +30651,7 @@
         <v>845</v>
       </c>
       <c r="D1113" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1113">
         <v>1</v>
@@ -30674,7 +30674,7 @@
         <v>845</v>
       </c>
       <c r="D1114" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1114">
         <v>1</v>
@@ -30697,7 +30697,7 @@
         <v>845</v>
       </c>
       <c r="D1115" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1115">
         <v>1</v>
@@ -30720,7 +30720,7 @@
         <v>845</v>
       </c>
       <c r="D1116" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1116">
         <v>1</v>
@@ -30743,7 +30743,7 @@
         <v>845</v>
       </c>
       <c r="D1117" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1117">
         <v>1</v>
@@ -30766,7 +30766,7 @@
         <v>845</v>
       </c>
       <c r="D1118" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1118">
         <v>1</v>
@@ -30789,7 +30789,7 @@
         <v>1122</v>
       </c>
       <c r="D1119" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1119">
         <v>1</v>
@@ -30812,7 +30812,7 @@
         <v>1122</v>
       </c>
       <c r="D1120" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1120">
         <v>1</v>
@@ -30835,7 +30835,7 @@
         <v>1122</v>
       </c>
       <c r="D1121" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1121">
         <v>1</v>
@@ -30858,7 +30858,7 @@
         <v>1122</v>
       </c>
       <c r="D1122" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1122">
         <v>1</v>
@@ -30881,7 +30881,7 @@
         <v>1122</v>
       </c>
       <c r="D1123" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1123">
         <v>1</v>
@@ -30904,7 +30904,7 @@
         <v>1122</v>
       </c>
       <c r="D1124" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1124">
         <v>1</v>
@@ -30927,7 +30927,7 @@
         <v>1122</v>
       </c>
       <c r="D1125" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1125">
         <v>1</v>
@@ -30950,7 +30950,7 @@
         <v>1122</v>
       </c>
       <c r="D1126" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1126">
         <v>1</v>
@@ -30973,7 +30973,7 @@
         <v>1122</v>
       </c>
       <c r="D1127" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1127">
         <v>1</v>
@@ -30996,7 +30996,7 @@
         <v>1122</v>
       </c>
       <c r="D1128" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1128">
         <v>1</v>
@@ -31019,7 +31019,7 @@
         <v>1122</v>
       </c>
       <c r="D1129" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1129">
         <v>1</v>
@@ -31042,7 +31042,7 @@
         <v>1122</v>
       </c>
       <c r="D1130" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1130">
         <v>1</v>
@@ -31065,7 +31065,7 @@
         <v>1122</v>
       </c>
       <c r="D1131" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1131">
         <v>1</v>
@@ -31088,7 +31088,7 @@
         <v>1122</v>
       </c>
       <c r="D1132" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1132">
         <v>1</v>
@@ -31111,7 +31111,7 @@
         <v>1122</v>
       </c>
       <c r="D1133" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1133">
         <v>1</v>
@@ -31134,7 +31134,7 @@
         <v>1122</v>
       </c>
       <c r="D1134" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1134">
         <v>1</v>
@@ -31157,7 +31157,7 @@
         <v>1122</v>
       </c>
       <c r="D1135" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1135">
         <v>1</v>
@@ -31180,7 +31180,7 @@
         <v>1122</v>
       </c>
       <c r="D1136" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1136">
         <v>1</v>
@@ -31203,7 +31203,7 @@
         <v>1122</v>
       </c>
       <c r="D1137" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1137">
         <v>1</v>
@@ -31226,7 +31226,7 @@
         <v>1122</v>
       </c>
       <c r="D1138" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1138">
         <v>1</v>
@@ -31249,7 +31249,7 @@
         <v>1122</v>
       </c>
       <c r="D1139" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1139">
         <v>1</v>
@@ -31269,10 +31269,10 @@
         <v>126</v>
       </c>
       <c r="C1140" t="s">
-        <v>1362</v>
+        <v>1358</v>
       </c>
       <c r="D1140" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E1140">
         <v>1</v>
@@ -31292,10 +31292,10 @@
         <v>168</v>
       </c>
       <c r="C1141" t="s">
-        <v>1362</v>
+        <v>1358</v>
       </c>
       <c r="D1141" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E1141">
         <v>1</v>
@@ -31318,7 +31318,7 @@
         <v>845</v>
       </c>
       <c r="D1142" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1142">
         <v>1</v>
@@ -31341,7 +31341,7 @@
         <v>845</v>
       </c>
       <c r="D1143" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1143">
         <v>1</v>
@@ -31364,7 +31364,7 @@
         <v>845</v>
       </c>
       <c r="D1144" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1144">
         <v>1</v>
@@ -31387,7 +31387,7 @@
         <v>845</v>
       </c>
       <c r="D1145" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1145">
         <v>1</v>
@@ -31410,7 +31410,7 @@
         <v>845</v>
       </c>
       <c r="D1146" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1146">
         <v>1</v>
@@ -31433,7 +31433,7 @@
         <v>845</v>
       </c>
       <c r="D1147" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1147">
         <v>1</v>
@@ -31456,7 +31456,7 @@
         <v>845</v>
       </c>
       <c r="D1148" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1148">
         <v>1</v>
@@ -31479,7 +31479,7 @@
         <v>845</v>
       </c>
       <c r="D1149" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1149">
         <v>1</v>
@@ -31502,7 +31502,7 @@
         <v>845</v>
       </c>
       <c r="D1150" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1150">
         <v>1</v>
@@ -31525,7 +31525,7 @@
         <v>845</v>
       </c>
       <c r="D1151" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1151">
         <v>1</v>
@@ -31548,7 +31548,7 @@
         <v>845</v>
       </c>
       <c r="D1152" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1152">
         <v>1</v>
@@ -31571,7 +31571,7 @@
         <v>845</v>
       </c>
       <c r="D1153" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1153">
         <v>1</v>
@@ -31594,7 +31594,7 @@
         <v>845</v>
       </c>
       <c r="D1154" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1154">
         <v>1</v>
@@ -31617,7 +31617,7 @@
         <v>845</v>
       </c>
       <c r="D1155" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1155">
         <v>1</v>
@@ -31640,7 +31640,7 @@
         <v>845</v>
       </c>
       <c r="D1156" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1156">
         <v>1</v>
@@ -31663,7 +31663,7 @@
         <v>845</v>
       </c>
       <c r="D1157" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1157">
         <v>1</v>
@@ -31686,7 +31686,7 @@
         <v>845</v>
       </c>
       <c r="D1158" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1158">
         <v>1</v>
@@ -31709,7 +31709,7 @@
         <v>845</v>
       </c>
       <c r="D1159" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1159">
         <v>1</v>
@@ -31732,7 +31732,7 @@
         <v>845</v>
       </c>
       <c r="D1160" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1160">
         <v>1</v>
@@ -31755,7 +31755,7 @@
         <v>845</v>
       </c>
       <c r="D1161" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1161">
         <v>1</v>
@@ -31778,7 +31778,7 @@
         <v>845</v>
       </c>
       <c r="D1162" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1162">
         <v>1</v>
@@ -31801,7 +31801,7 @@
         <v>845</v>
       </c>
       <c r="D1163" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1163">
         <v>1</v>
@@ -31824,7 +31824,7 @@
         <v>845</v>
       </c>
       <c r="D1164" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1164">
         <v>1</v>
@@ -31847,7 +31847,7 @@
         <v>845</v>
       </c>
       <c r="D1165" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1165">
         <v>1</v>
@@ -31870,7 +31870,7 @@
         <v>845</v>
       </c>
       <c r="D1166" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1166">
         <v>1</v>
@@ -31893,7 +31893,7 @@
         <v>845</v>
       </c>
       <c r="D1167" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1167">
         <v>1</v>
@@ -31916,7 +31916,7 @@
         <v>845</v>
       </c>
       <c r="D1168" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1168">
         <v>1</v>
@@ -31939,7 +31939,7 @@
         <v>845</v>
       </c>
       <c r="D1169" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1169">
         <v>1</v>
@@ -31962,7 +31962,7 @@
         <v>845</v>
       </c>
       <c r="D1170" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1170">
         <v>1</v>
@@ -31985,7 +31985,7 @@
         <v>845</v>
       </c>
       <c r="D1171" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1171">
         <v>1</v>
@@ -32008,7 +32008,7 @@
         <v>845</v>
       </c>
       <c r="D1172" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1172">
         <v>1</v>
@@ -32031,7 +32031,7 @@
         <v>845</v>
       </c>
       <c r="D1173" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1173">
         <v>1</v>
@@ -32054,7 +32054,7 @@
         <v>845</v>
       </c>
       <c r="D1174" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1174">
         <v>1</v>
@@ -32077,7 +32077,7 @@
         <v>845</v>
       </c>
       <c r="D1175" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1175">
         <v>1</v>
@@ -32100,7 +32100,7 @@
         <v>845</v>
       </c>
       <c r="D1176" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1176">
         <v>1</v>
@@ -32123,7 +32123,7 @@
         <v>845</v>
       </c>
       <c r="D1177" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1177">
         <v>1</v>
@@ -32146,7 +32146,7 @@
         <v>845</v>
       </c>
       <c r="D1178" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1178">
         <v>1</v>
@@ -32169,7 +32169,7 @@
         <v>845</v>
       </c>
       <c r="D1179" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1179">
         <v>1</v>
@@ -32192,7 +32192,7 @@
         <v>845</v>
       </c>
       <c r="D1180" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1180">
         <v>1</v>
@@ -32215,7 +32215,7 @@
         <v>845</v>
       </c>
       <c r="D1181" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1181">
         <v>1</v>
@@ -32238,7 +32238,7 @@
         <v>845</v>
       </c>
       <c r="D1182" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1182">
         <v>1</v>
@@ -32261,7 +32261,7 @@
         <v>845</v>
       </c>
       <c r="D1183" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1183">
         <v>1</v>
@@ -32284,7 +32284,7 @@
         <v>845</v>
       </c>
       <c r="D1184" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1184">
         <v>1</v>
@@ -32307,7 +32307,7 @@
         <v>845</v>
       </c>
       <c r="D1185" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1185">
         <v>1</v>
@@ -32330,7 +32330,7 @@
         <v>845</v>
       </c>
       <c r="D1186" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1186">
         <v>1</v>
@@ -32353,7 +32353,7 @@
         <v>845</v>
       </c>
       <c r="D1187" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1187">
         <v>1</v>
@@ -32376,7 +32376,7 @@
         <v>845</v>
       </c>
       <c r="D1188" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1188">
         <v>1</v>
@@ -32399,7 +32399,7 @@
         <v>845</v>
       </c>
       <c r="D1189" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1189">
         <v>1</v>
@@ -32422,7 +32422,7 @@
         <v>845</v>
       </c>
       <c r="D1190" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1190">
         <v>1</v>
@@ -32445,7 +32445,7 @@
         <v>845</v>
       </c>
       <c r="D1191" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1191">
         <v>1</v>
@@ -32468,7 +32468,7 @@
         <v>845</v>
       </c>
       <c r="D1192" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1192">
         <v>1</v>
@@ -32491,7 +32491,7 @@
         <v>845</v>
       </c>
       <c r="D1193" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1193">
         <v>1</v>
@@ -32514,7 +32514,7 @@
         <v>845</v>
       </c>
       <c r="D1194" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1194">
         <v>1</v>
@@ -32537,7 +32537,7 @@
         <v>845</v>
       </c>
       <c r="D1195" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1195">
         <v>1</v>
@@ -32560,7 +32560,7 @@
         <v>845</v>
       </c>
       <c r="D1196" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1196">
         <v>1</v>
@@ -32583,7 +32583,7 @@
         <v>845</v>
       </c>
       <c r="D1197" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1197">
         <v>1</v>
@@ -32606,7 +32606,7 @@
         <v>845</v>
       </c>
       <c r="D1198" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1198">
         <v>1</v>
@@ -32629,7 +32629,7 @@
         <v>845</v>
       </c>
       <c r="D1199" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1199">
         <v>1</v>
@@ -32652,7 +32652,7 @@
         <v>845</v>
       </c>
       <c r="D1200" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1200">
         <v>1</v>
@@ -32675,7 +32675,7 @@
         <v>845</v>
       </c>
       <c r="D1201" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1201">
         <v>1</v>
@@ -32698,7 +32698,7 @@
         <v>845</v>
       </c>
       <c r="D1202" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1202">
         <v>1</v>
@@ -32721,7 +32721,7 @@
         <v>845</v>
       </c>
       <c r="D1203" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1203">
         <v>1</v>
@@ -32744,7 +32744,7 @@
         <v>845</v>
       </c>
       <c r="D1204" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1204">
         <v>1</v>
@@ -32767,7 +32767,7 @@
         <v>845</v>
       </c>
       <c r="D1205" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1205">
         <v>1</v>
@@ -32790,7 +32790,7 @@
         <v>845</v>
       </c>
       <c r="D1206" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1206">
         <v>1</v>
@@ -32813,7 +32813,7 @@
         <v>845</v>
       </c>
       <c r="D1207" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1207">
         <v>1</v>
@@ -32836,7 +32836,7 @@
         <v>845</v>
       </c>
       <c r="D1208" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1208">
         <v>1</v>
@@ -32859,7 +32859,7 @@
         <v>845</v>
       </c>
       <c r="D1209" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1209">
         <v>1</v>
@@ -32882,7 +32882,7 @@
         <v>845</v>
       </c>
       <c r="D1210" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1210">
         <v>1</v>
@@ -32905,7 +32905,7 @@
         <v>845</v>
       </c>
       <c r="D1211" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1211">
         <v>1</v>
@@ -32928,7 +32928,7 @@
         <v>845</v>
       </c>
       <c r="D1212" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1212">
         <v>1</v>
@@ -32951,7 +32951,7 @@
         <v>845</v>
       </c>
       <c r="D1213" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1213">
         <v>1</v>
@@ -32974,7 +32974,7 @@
         <v>845</v>
       </c>
       <c r="D1214" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1214">
         <v>1</v>
@@ -32997,7 +32997,7 @@
         <v>845</v>
       </c>
       <c r="D1215" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1215">
         <v>1</v>
@@ -33021,7 +33021,7 @@
         <v>845</v>
       </c>
       <c r="D1216" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1216">
         <v>1</v>
@@ -33044,7 +33044,7 @@
         <v>845</v>
       </c>
       <c r="D1217" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1217">
         <v>1</v>
@@ -33067,7 +33067,7 @@
         <v>845</v>
       </c>
       <c r="D1218" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1218">
         <v>1</v>
@@ -33090,7 +33090,7 @@
         <v>845</v>
       </c>
       <c r="D1219" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1219">
         <v>1</v>
@@ -33113,7 +33113,7 @@
         <v>845</v>
       </c>
       <c r="D1220" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1220">
         <v>1</v>
@@ -33137,7 +33137,7 @@
         <v>845</v>
       </c>
       <c r="D1221" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1221">
         <v>1</v>
@@ -33161,7 +33161,7 @@
         <v>845</v>
       </c>
       <c r="D1222" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1222">
         <v>1</v>
@@ -33185,7 +33185,7 @@
         <v>845</v>
       </c>
       <c r="D1223" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1223">
         <v>1</v>
@@ -33209,7 +33209,7 @@
         <v>845</v>
       </c>
       <c r="D1224" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1224">
         <v>1</v>
@@ -33233,7 +33233,7 @@
         <v>1089</v>
       </c>
       <c r="D1225" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E1225">
         <v>1</v>
@@ -33257,7 +33257,7 @@
         <v>1089</v>
       </c>
       <c r="D1226" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E1226">
         <v>1</v>
@@ -33281,7 +33281,7 @@
         <v>1089</v>
       </c>
       <c r="D1227" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E1227">
         <v>1</v>
@@ -33305,7 +33305,7 @@
         <v>1089</v>
       </c>
       <c r="D1228" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E1228">
         <v>1</v>
@@ -33329,7 +33329,7 @@
         <v>1089</v>
       </c>
       <c r="D1229" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E1229">
         <v>1</v>
@@ -33342,7 +33342,7 @@
       </c>
       <c r="L1229" s="3"/>
     </row>
-    <row r="1230" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1230" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1230">
         <v>530901</v>
       </c>
@@ -33350,10 +33350,10 @@
         <v>155</v>
       </c>
       <c r="C1230" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="D1230" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E1230">
         <v>1</v>
@@ -33366,7 +33366,7 @@
       </c>
       <c r="L1230" s="3"/>
     </row>
-    <row r="1231" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1231" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1231">
         <v>530412</v>
       </c>
@@ -33374,10 +33374,10 @@
         <v>154</v>
       </c>
       <c r="C1231" t="s">
-        <v>1356</v>
+        <v>1371</v>
       </c>
       <c r="D1231" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E1231">
         <v>1</v>
@@ -33390,7 +33390,7 @@
       </c>
       <c r="L1231" s="3"/>
     </row>
-    <row r="1232" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1232" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1232">
         <v>530311</v>
       </c>
@@ -33398,10 +33398,10 @@
         <v>196</v>
       </c>
       <c r="C1232" t="s">
-        <v>1358</v>
+        <v>1373</v>
       </c>
       <c r="D1232" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E1232">
         <v>1</v>
@@ -33414,7 +33414,7 @@
       </c>
       <c r="L1232" s="3"/>
     </row>
-    <row r="1233" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1233" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1233">
         <v>530510</v>
       </c>
@@ -33422,10 +33422,10 @@
         <v>198</v>
       </c>
       <c r="C1233" t="s">
-        <v>1358</v>
+        <v>1373</v>
       </c>
       <c r="D1233" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E1233">
         <v>1</v>
@@ -33455,14 +33455,14 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G1233" xr:uid="{16315887-E99C-F647-BC9F-F16988AC1201}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Bike or Scooter or other Single Rider Travel"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="3">
       <filters>
         <filter val="Transportation"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="6">
-      <filters>
-        <filter val="1"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A119:G1207">
